--- a/data/ticker_availability.xlsx
+++ b/data/ticker_availability.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B722"/>
+  <dimension ref="A1:B790"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AEE</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -451,7 +451,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>BTI</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -461,7 +461,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>WRK</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -471,7 +471,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -481,7 +481,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WBA</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -491,7 +491,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>WAT</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -501,7 +501,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>TSCO</t>
+          <t>GIS</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -511,7 +511,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>URBN</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -521,7 +521,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>TGNA</t>
+          <t>CARR</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -531,7 +531,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>TGT</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -541,7 +541,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>UDR</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -551,7 +551,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>CBOE</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -561,7 +561,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>TPL</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -571,7 +571,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>CCE</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -581,7 +581,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>TJX</t>
+          <t>GDDY</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -591,7 +591,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>THC</t>
+          <t>TIF</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -601,7 +601,7 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>STLD</t>
+          <t>GAS</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -611,7 +611,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>SYF</t>
+          <t>FTV</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -621,7 +621,7 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>SYY</t>
+          <t>BSX</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -631,7 +631,7 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>TGT</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -641,7 +641,7 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -651,7 +651,7 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>AMCR</t>
+          <t>PCL</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -661,7 +661,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>BDK</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -671,7 +671,7 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>AN</t>
+          <t>NXPI</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -681,7 +681,7 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>SRCL</t>
+          <t>NYX</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -691,7 +691,7 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>QRVO</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -701,7 +701,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>ARG</t>
+          <t>HOG</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -711,7 +711,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>ATO</t>
+          <t>ULTA</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -721,7 +721,7 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>SWN</t>
+          <t>BIG</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -731,7 +731,7 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>SWKS</t>
+          <t>HLT</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -741,7 +741,7 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>STX</t>
+          <t>HII</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -751,7 +751,7 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>STT</t>
+          <t>OTIS</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -761,7 +761,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -771,7 +771,7 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>PLL</t>
+          <t>PBCT</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -781,7 +781,7 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>PEG</t>
+          <t>PBG</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -791,7 +791,7 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>BMC</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -801,7 +801,7 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>PBI</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -811,7 +811,7 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>RCL</t>
+          <t>PCAR</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -821,7 +821,7 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>RAI</t>
+          <t>PCG</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -831,7 +831,7 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>RRC</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -841,7 +841,7 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>QEP</t>
+          <t>FTR</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -851,7 +851,7 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>FTI</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -861,7 +861,7 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>BBWI</t>
+          <t>PKI</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -871,7 +871,7 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>PODD</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -881,7 +881,7 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>RHT</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -891,7 +891,7 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>CPWR</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -901,7 +901,7 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>RIG</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -911,7 +911,7 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>STLD</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -921,7 +921,7 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>NOV</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -931,7 +931,7 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>BXLT</t>
+          <t>SBAC</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -941,7 +941,7 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>MTB</t>
+          <t>DPZ</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -951,7 +951,7 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>MSI</t>
+          <t>SHLD</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -961,7 +961,7 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>MUR</t>
+          <t>CTXS</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -971,7 +971,7 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>NI</t>
+          <t>CVC</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -981,7 +981,7 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>NFX</t>
+          <t>DNB</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -991,7 +991,7 @@
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>NKTR</t>
+          <t>DLTR</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -1001,7 +1001,7 @@
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>PEAK</t>
+          <t>CZR</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -1011,7 +1011,7 @@
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>OMC</t>
+          <t>DISCA</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -1021,7 +1021,7 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>PDCO</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -1031,7 +1031,7 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>DAY</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -1041,7 +1041,7 @@
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>ORLY</t>
+          <t>ESRX</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -1051,7 +1051,7 @@
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -1061,7 +1061,7 @@
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>COTY</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -1071,7 +1071,7 @@
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>BDX</t>
+          <t>ESV</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -1081,7 +1081,7 @@
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>HSIC</t>
+          <t>CFN</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -1091,7 +1091,7 @@
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>HRS</t>
+          <t>TEG</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -1101,7 +1101,7 @@
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>TECH</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -1111,7 +1111,7 @@
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>CMCSA</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -1121,7 +1121,7 @@
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>FLIR</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -1131,7 +1131,7 @@
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>IPG</t>
+          <t>POM</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -1141,7 +1141,7 @@
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>CFG</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -1161,7 +1161,7 @@
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>NWS</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -1171,7 +1171,7 @@
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>PSA</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -1181,7 +1181,7 @@
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>KEYS</t>
+          <t>SYY</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -1191,7 +1191,7 @@
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>LDOS</t>
+          <t>CMI</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -1201,7 +1201,7 @@
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>CCEP</t>
+          <t>CMS</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -1211,7 +1211,7 @@
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>CBRE</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -1221,7 +1221,7 @@
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>LNT</t>
+          <t>PTV</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -1231,7 +1231,7 @@
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>LNC</t>
+          <t>SWKS</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -1241,7 +1241,7 @@
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>ETFC</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -1251,7 +1251,7 @@
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>LLTC</t>
+          <t>SW</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -1261,7 +1261,7 @@
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>MNK</t>
+          <t>PSX</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -1271,7 +1271,7 @@
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>NDAQ</t>
+          <t>HUM</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -1281,7 +1281,7 @@
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>MAS</t>
+          <t>HAR</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -1291,7 +1291,7 @@
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>KEY</t>
+          <t>SJM</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -1301,7 +1301,7 @@
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>LM</t>
+          <t>MAS</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -1311,7 +1311,7 @@
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>KMX</t>
+          <t>XLNX</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -1321,7 +1321,7 @@
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>AGN</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -1331,7 +1331,7 @@
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>FE</t>
+          <t>ANF</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -1341,7 +1341,7 @@
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -1351,7 +1351,7 @@
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>GEHC</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -1361,7 +1361,7 @@
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -1371,7 +1371,7 @@
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>CPRI</t>
+          <t>KRFT</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -1381,7 +1381,7 @@
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>XEC</t>
+          <t>KSS</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -1391,7 +1391,7 @@
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>XYL</t>
+          <t>WHR</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -1401,7 +1401,7 @@
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>KSU</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -1411,7 +1411,7 @@
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>MAC</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -1421,7 +1421,7 @@
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -1431,7 +1431,7 @@
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>HWM</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -1441,7 +1441,7 @@
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>ADI</t>
+          <t>AMCR</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -1451,7 +1451,7 @@
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>ADS</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -1461,7 +1461,7 @@
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -1471,7 +1471,7 @@
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>LYV</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -1481,7 +1481,7 @@
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -1491,7 +1491,7 @@
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>ENPH</t>
+          <t>AIG</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -1501,7 +1501,7 @@
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>LSI</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -1511,7 +1511,7 @@
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>EMC</t>
+          <t>MPWR</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -1521,7 +1521,7 @@
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -1531,7 +1531,7 @@
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>DAY</t>
+          <t>MTD</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -1541,7 +1541,7 @@
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>DNB</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -1551,7 +1551,7 @@
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>LH</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -1561,7 +1561,7 @@
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -1571,7 +1571,7 @@
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>ALGN</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -1581,7 +1581,7 @@
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>CTAS</t>
+          <t>MTB</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -1591,7 +1591,7 @@
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>ETSY</t>
+          <t>X</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -1601,7 +1601,7 @@
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>FLR</t>
+          <t>WLTW</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -1611,7 +1611,7 @@
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>FLIR</t>
+          <t>LHX</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -1621,7 +1621,7 @@
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>ETR</t>
+          <t>AOS</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -1631,7 +1631,7 @@
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>FLS</t>
+          <t>KORS</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -1641,7 +1641,7 @@
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>FDS</t>
+          <t>MCO</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -1651,7 +1651,7 @@
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>HII</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -1661,7 +1661,7 @@
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>CNX</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -1671,1257 +1671,1257 @@
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>BSX</t>
+          <t>AVY</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.000397456279809221</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>MMC</t>
+          <t>MLM</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.0226550079491256</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>ALLE</t>
+          <t>AWK</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.03815580286168521</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>FLT</t>
+          <t>AXON</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.04551724137931035</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>HST</t>
+          <t>IRM</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.0492845786963434</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>EMN</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.0512718600953895</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>AYE</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.05484896661367249</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>IPGP</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.0798494983277592</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>YUM</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.1196172248803828</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>BF-B</t>
+          <t>ZBH</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.1244038155802862</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>HSY</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.1629570747217806</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>RMD</t>
+          <t>MJN</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.1630144307856761</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>IRM</t>
+          <t>IDXX</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.1661367249602544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.2038950715421304</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>PNR</t>
+          <t>MKC</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.2559618441971383</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.3565182829888712</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>MOH</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.397456279809221</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>VTR</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.4268680445151034</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>NLSN</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.4359367023991833</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>BXP</t>
+          <t>ATVI</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.4503179650238474</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.4789348171701113</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>MAT</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.4789348171701113</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.4811932555123217</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>FAST</t>
+          <t>ITT</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.4976152623211447</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5560413354531002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>APH</t>
+          <t>NOV</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.564785373608903</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>AVB</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5814785373608903</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>CPRT</t>
+          <t>DISCK</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.6234718826405868</v>
+        <v>0.0005170630816959669</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>VRSK</t>
+          <t>CPB</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.6272061988807577</v>
+        <v>0.002119766825649179</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>GMCR</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.6685214626391097</v>
+        <v>0.004073319755600814</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>PPG</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.6951510333863276</v>
+        <v>0.0151033386327504</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.6999205087440381</v>
+        <v>0.01828298887122417</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>0.712241653418124</v>
+        <v>0.03418124006359301</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>STX</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0.71939586645469</v>
+        <v>0.06168521462639109</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>VAR</t>
+          <t>EFX</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0.7419558359621451</v>
+        <v>0.06942236354001059</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>PLL</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>0.7639109697933227</v>
+        <v>0.07508771929824562</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>SEE</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0.7881662149954833</v>
+        <v>0.08664546899841018</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>UHS</t>
+          <t>TIE</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>0.7917329093799682</v>
+        <v>0.08666666666666667</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>TECH</t>
+          <t>SWY</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>0.7988095238095239</v>
+        <v>0.09725490196078432</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>HOG</t>
+          <t>GENZ</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>0.8198983297022513</v>
+        <v>0.1139240506329114</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>CPRI</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>0.8239268680445151</v>
+        <v>0.1257976298997265</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>VRSK</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>0.9141494435612083</v>
+        <v>0.134739560912613</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>ROK</t>
+          <t>NDAQ</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>0.9205087440381559</v>
+        <v>0.1359300476947536</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>0.9499205087440381</v>
+        <v>0.144287193648602</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>LW</t>
+          <t>BCR</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>0.9561805101373446</v>
+        <v>0.1549925484351714</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>NWL</t>
+          <t>CAG</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>0.9676094890510949</v>
+        <v>0.1584525702172761</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>TEL</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0.9841017488076311</v>
+        <v>0.1613000300932892</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t>ZION</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>1</v>
+        <v>0.1777954425013248</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>IR</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>1</v>
+        <v>0.2088376020264565</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
         <is>
-          <t>ZBH</t>
+          <t>RMD</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>1</v>
+        <v>0.2089791555318012</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="inlineStr">
         <is>
-          <t>YUM</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>1</v>
+        <v>0.2310545839957605</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
         <is>
-          <t>YHOO</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>1</v>
+        <v>0.262586115527292</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="inlineStr">
         <is>
-          <t>XRX</t>
+          <t>HNZ</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>1</v>
+        <v>0.2827346465816918</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="inlineStr">
         <is>
-          <t>XRAY</t>
+          <t>AEE</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>1</v>
+        <v>0.2835188129305776</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>1</v>
+        <v>0.2845786963434022</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="inlineStr">
         <is>
-          <t>XLNX</t>
+          <t>VIAC</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>1</v>
+        <v>0.2913669064748202</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>1</v>
+        <v>0.3002119766825649</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="inlineStr">
         <is>
-          <t>XEL</t>
+          <t>HIG</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>1</v>
+        <v>0.3192898781134075</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="inlineStr">
         <is>
-          <t>WYNN</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>1</v>
+        <v>0.3244170096021948</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="inlineStr">
         <is>
-          <t>WYND</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>1</v>
+        <v>0.3269740328563858</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="inlineStr">
         <is>
-          <t>ADM</t>
+          <t>CHTR</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>1</v>
+        <v>0.3307839388145316</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>1</v>
+        <v>0.3317435082140964</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>BBT</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>1</v>
+        <v>0.3334666133546582</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="inlineStr">
         <is>
-          <t>ACGL</t>
+          <t>HPE</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>1</v>
+        <v>0.3365134431916739</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>DHI</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>1</v>
+        <v>0.3441971383147854</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="inlineStr">
         <is>
-          <t>ABMD</t>
+          <t>PETM</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>1</v>
+        <v>0.3721311475409836</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>WAT</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>1</v>
+        <v>0.3738738738738739</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>WM</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>1</v>
+        <v>0.3765235824059354</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>AME</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>1</v>
+        <v>0.3805496828752643</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
         <is>
-          <t>AAP</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>1</v>
+        <v>0.3860625331213566</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="inlineStr">
         <is>
-          <t>AAL</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>1</v>
+        <v>0.3892421833598304</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
         <is>
-          <t>DHI</t>
+          <t>AAL</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>1</v>
+        <v>0.3974091099038863</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="inlineStr">
         <is>
-          <t>DGX</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>1</v>
+        <v>0.3977212506624271</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="inlineStr">
         <is>
-          <t>DG</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>1</v>
+        <v>0.3990447242726878</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
         <is>
-          <t>DFS</t>
+          <t>SHW</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>1</v>
+        <v>0.4043455219925808</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>1</v>
+        <v>0.4666136724960254</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
         <is>
-          <t>DECK</t>
+          <t>AET</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>1</v>
+        <v>0.4701426024955437</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>1</v>
+        <v>0.4795972443031267</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="inlineStr">
         <is>
-          <t>CZR</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>1</v>
+        <v>0.4976152623211447</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="inlineStr">
         <is>
-          <t>CXO</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>1</v>
+        <v>0.505299417064123</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>1</v>
+        <v>0.5092739798622151</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="inlineStr">
         <is>
-          <t>CVS</t>
+          <t>ETN</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>1</v>
+        <v>0.5442501324854266</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="inlineStr">
         <is>
-          <t>CVC</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>1</v>
+        <v>0.5521766965428937</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="inlineStr">
         <is>
-          <t>DRI</t>
+          <t>TAP</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>1</v>
+        <v>0.5635930047694754</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="inlineStr">
         <is>
-          <t>DRE</t>
+          <t>HON</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>1</v>
+        <v>0.566507684154743</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="1" t="inlineStr">
         <is>
-          <t>DPZ</t>
+          <t>CEG</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>1</v>
+        <v>0.5696498054474708</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="inlineStr">
         <is>
-          <t>DOW</t>
+          <t>AEP</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>1</v>
+        <v>0.5731319554848967</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="inlineStr">
         <is>
-          <t>DOV</t>
+          <t>ROP</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>1</v>
+        <v>0.5832008479067302</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="inlineStr">
         <is>
-          <t>DOC</t>
+          <t>VNO</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>1</v>
+        <v>0.5956017104459377</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>1</v>
+        <v>0.5983041865394807</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="inlineStr">
         <is>
-          <t>DNR</t>
+          <t>EMN</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>1</v>
+        <v>0.6054583995760466</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="inlineStr">
         <is>
-          <t>DLTR</t>
+          <t>CSX</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>1</v>
+        <v>0.6065182829888712</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="inlineStr">
         <is>
-          <t>DLR</t>
+          <t>PNW</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>1</v>
+        <v>0.6094329623741388</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="inlineStr">
         <is>
-          <t>DISH</t>
+          <t>TJX</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>1</v>
+        <v>0.6197668256491786</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="inlineStr">
         <is>
-          <t>DISCK</t>
+          <t>TER</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>1</v>
+        <v>0.631376323387873</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="inlineStr">
         <is>
-          <t>DISCA</t>
+          <t>EMR</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>1</v>
+        <v>0.6332803391626921</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>CDNS</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>1</v>
+        <v>0.6390403489640131</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>1</v>
+        <v>0.6515633280339163</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="inlineStr">
         <is>
-          <t>EIX</t>
+          <t>AMG</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>1</v>
+        <v>0.6545981173062998</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>HOLX</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>1</v>
+        <v>0.6634920634920635</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="inlineStr">
         <is>
-          <t>EFX</t>
+          <t>CAH</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>LKQ</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>1</v>
+        <v>0.6746654360867559</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="inlineStr">
         <is>
-          <t>ECL</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>1</v>
+        <v>0.6801801801801802</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>IPG</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>1</v>
+        <v>0.6854795972443031</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>SCG</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>1</v>
+        <v>0.7108167770419426</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="inlineStr">
         <is>
-          <t>DXCM</t>
+          <t>WEC</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>1</v>
+        <v>0.7368839427662957</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>FLR</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>1</v>
+        <v>0.7387083157450401</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="inlineStr">
         <is>
-          <t>DWDP</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>1</v>
+        <v>0.7413884472708002</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>MSI</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>1</v>
+        <v>0.7678855325914149</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="inlineStr">
         <is>
-          <t>DVA</t>
+          <t>MET</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>1</v>
+        <v>0.7694753577106518</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="inlineStr">
         <is>
-          <t>DUK</t>
+          <t>SPG</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>1</v>
+        <v>0.7694753577106518</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="inlineStr">
         <is>
-          <t>DTV</t>
+          <t>LXK</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>1</v>
+        <v>0.784992784992785</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="inlineStr">
         <is>
-          <t>DTE</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>1</v>
+        <v>0.7946475887652358</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="inlineStr">
         <is>
-          <t>ESV</t>
+          <t>KIM</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>1</v>
+        <v>0.8420773714891362</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="inlineStr">
         <is>
-          <t>ESS</t>
+          <t>SNA</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>1</v>
+        <v>0.8481717011128775</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="inlineStr">
         <is>
-          <t>ESRX</t>
+          <t>SNI</t>
         </is>
       </c>
       <c r="B240" t="n">
-        <v>1</v>
+        <v>0.8551992225461613</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>TGNA</t>
         </is>
       </c>
       <c r="B241" t="n">
-        <v>1</v>
+        <v>0.8580610605249063</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="inlineStr">
         <is>
-          <t>ERIE</t>
+          <t>AZO</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>1</v>
+        <v>0.859830418653948</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="inlineStr">
         <is>
-          <t>EQT</t>
+          <t>LM</t>
         </is>
       </c>
       <c r="B243" t="n">
-        <v>1</v>
+        <v>0.8657487091222031</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="inlineStr">
         <is>
-          <t>EQR</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B244" t="n">
-        <v>1</v>
+        <v>0.870291702067403</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="inlineStr">
         <is>
-          <t>EPAM</t>
+          <t>CMCSA</t>
         </is>
       </c>
       <c r="B245" t="n">
-        <v>1</v>
+        <v>0.9364069952305246</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="1" t="inlineStr">
         <is>
-          <t>EOG</t>
+          <t>NTAP</t>
         </is>
       </c>
       <c r="B246" t="n">
-        <v>1</v>
+        <v>0.9703232644409115</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="1" t="inlineStr">
         <is>
-          <t>ENDP</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B247" t="n">
-        <v>1</v>
+        <v>0.9894011658717541</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="1" t="inlineStr">
         <is>
-          <t>CTXS</t>
+          <t>FLS</t>
         </is>
       </c>
       <c r="B248" t="n">
-        <v>1</v>
+        <v>0.9904357066950054</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="1" t="inlineStr">
         <is>
-          <t>CTVA</t>
+          <t>LDOS</t>
         </is>
       </c>
       <c r="B249" t="n">
-        <v>1</v>
+        <v>0.9995642701525055</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="1" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>VLTO</t>
         </is>
       </c>
       <c r="B250" t="n">
@@ -2931,7 +2931,7 @@
     <row r="251">
       <c r="A251" s="1" t="inlineStr">
         <is>
-          <t>CTRA</t>
+          <t>NFX</t>
         </is>
       </c>
       <c r="B251" t="n">
@@ -2941,7 +2941,7 @@
     <row r="252">
       <c r="A252" s="1" t="inlineStr">
         <is>
-          <t>CTLT</t>
+          <t>NOVL</t>
         </is>
       </c>
       <c r="B252" t="n">
@@ -2951,7 +2951,7 @@
     <row r="253">
       <c r="A253" s="1" t="inlineStr">
         <is>
-          <t>CTL</t>
+          <t>VRTX</t>
         </is>
       </c>
       <c r="B253" t="n">
@@ -2961,7 +2961,7 @@
     <row r="254">
       <c r="A254" s="1" t="inlineStr">
         <is>
-          <t>CSX</t>
+          <t>NKTR</t>
         </is>
       </c>
       <c r="B254" t="n">
@@ -2971,7 +2971,7 @@
     <row r="255">
       <c r="A255" s="1" t="inlineStr">
         <is>
-          <t>CSRA</t>
+          <t>NLOK</t>
         </is>
       </c>
       <c r="B255" t="n">
@@ -2981,7 +2981,7 @@
     <row r="256">
       <c r="A256" s="1" t="inlineStr">
         <is>
-          <t>CSGP</t>
+          <t>NLSN</t>
         </is>
       </c>
       <c r="B256" t="n">
@@ -2991,7 +2991,7 @@
     <row r="257">
       <c r="A257" s="1" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>VRSN</t>
         </is>
       </c>
       <c r="B257" t="n">
@@ -3001,7 +3001,7 @@
     <row r="258">
       <c r="A258" s="1" t="inlineStr">
         <is>
-          <t>CRL</t>
+          <t>VNT</t>
         </is>
       </c>
       <c r="B258" t="n">
@@ -3011,7 +3011,7 @@
     <row r="259">
       <c r="A259" s="1" t="inlineStr">
         <is>
-          <t>CPT</t>
+          <t>VMC</t>
         </is>
       </c>
       <c r="B259" t="n">
@@ -3021,7 +3021,7 @@
     <row r="260">
       <c r="A260" s="1" t="inlineStr">
         <is>
-          <t>FCPT</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B260" t="n">
@@ -3031,7 +3031,7 @@
     <row r="261">
       <c r="A261" s="1" t="inlineStr">
         <is>
-          <t>FBHS</t>
+          <t>ODP</t>
         </is>
       </c>
       <c r="B261" t="n">
@@ -3041,7 +3041,7 @@
     <row r="262">
       <c r="A262" s="1" t="inlineStr">
         <is>
-          <t>FANG</t>
+          <t>NRG</t>
         </is>
       </c>
       <c r="B262" t="n">
@@ -3051,7 +3051,7 @@
     <row r="263">
       <c r="A263" s="1" t="inlineStr">
         <is>
-          <t>EXR</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="B263" t="n">
@@ -3061,7 +3061,7 @@
     <row r="264">
       <c r="A264" s="1" t="inlineStr">
         <is>
-          <t>EXPE</t>
+          <t>ODFL</t>
         </is>
       </c>
       <c r="B264" t="n">
@@ -3071,7 +3071,7 @@
     <row r="265">
       <c r="A265" s="1" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B265" t="n">
@@ -3081,7 +3081,7 @@
     <row r="266">
       <c r="A266" s="1" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>URBN</t>
         </is>
       </c>
       <c r="B266" t="n">
@@ -3091,7 +3091,7 @@
     <row r="267">
       <c r="A267" s="1" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>NYT</t>
         </is>
       </c>
       <c r="B267" t="n">
@@ -3101,7 +3101,7 @@
     <row r="268">
       <c r="A268" s="1" t="inlineStr">
         <is>
-          <t>EVRG</t>
+          <t>URI</t>
         </is>
       </c>
       <c r="B268" t="n">
@@ -3111,7 +3111,7 @@
     <row r="269">
       <c r="A269" s="1" t="inlineStr">
         <is>
-          <t>EVHC</t>
+          <t>NWSA</t>
         </is>
       </c>
       <c r="B269" t="n">
@@ -3121,7 +3121,7 @@
     <row r="270">
       <c r="A270" s="1" t="inlineStr">
         <is>
-          <t>ETN</t>
+          <t>USB</t>
         </is>
       </c>
       <c r="B270" t="n">
@@ -3131,7 +3131,7 @@
     <row r="271">
       <c r="A271" s="1" t="inlineStr">
         <is>
-          <t>ETFC</t>
+          <t>UTX</t>
         </is>
       </c>
       <c r="B271" t="n">
@@ -3141,7 +3141,7 @@
     <row r="272">
       <c r="A272" s="1" t="inlineStr">
         <is>
-          <t>FMC</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B272" t="n">
@@ -3151,7 +3151,7 @@
     <row r="273">
       <c r="A273" s="1" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B273" t="n">
@@ -3161,7 +3161,7 @@
     <row r="274">
       <c r="A274" s="1" t="inlineStr">
         <is>
-          <t>FITB</t>
+          <t>VAR</t>
         </is>
       </c>
       <c r="B274" t="n">
@@ -3171,7 +3171,7 @@
     <row r="275">
       <c r="A275" s="1" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>VICI</t>
         </is>
       </c>
       <c r="B275" t="n">
@@ -3181,7 +3181,7 @@
     <row r="276">
       <c r="A276" s="1" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>NWL</t>
         </is>
       </c>
       <c r="B276" t="n">
@@ -3191,7 +3191,7 @@
     <row r="277">
       <c r="A277" s="1" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>NVR</t>
         </is>
       </c>
       <c r="B277" t="n">
@@ -3201,7 +3201,7 @@
     <row r="278">
       <c r="A278" s="1" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>NVLS</t>
         </is>
       </c>
       <c r="B278" t="n">
@@ -3211,7 +3211,7 @@
     <row r="279">
       <c r="A279" s="1" t="inlineStr">
         <is>
-          <t>FDX</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B279" t="n">
@@ -3221,7 +3221,7 @@
     <row r="280">
       <c r="A280" s="1" t="inlineStr">
         <is>
-          <t>FDO</t>
+          <t>NUE</t>
         </is>
       </c>
       <c r="B280" t="n">
@@ -3231,7 +3231,7 @@
     <row r="281">
       <c r="A281" s="1" t="inlineStr">
         <is>
-          <t>FCX</t>
+          <t>NTRS</t>
         </is>
       </c>
       <c r="B281" t="n">
@@ -3241,7 +3241,7 @@
     <row r="282">
       <c r="A282" s="1" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>OI</t>
         </is>
       </c>
       <c r="B282" t="n">
@@ -3251,7 +3251,7 @@
     <row r="283">
       <c r="A283" s="1" t="inlineStr">
         <is>
-          <t>GDDY</t>
+          <t>VIAV</t>
         </is>
       </c>
       <c r="B283" t="n">
@@ -3261,7 +3261,7 @@
     <row r="284">
       <c r="A284" s="1" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>NSM</t>
         </is>
       </c>
       <c r="B284" t="n">
@@ -3271,7 +3271,7 @@
     <row r="285">
       <c r="A285" s="1" t="inlineStr">
         <is>
-          <t>GAS</t>
+          <t>OKE</t>
         </is>
       </c>
       <c r="B285" t="n">
@@ -3281,7 +3281,7 @@
     <row r="286">
       <c r="A286" s="1" t="inlineStr">
         <is>
-          <t>FTV</t>
+          <t>NSC</t>
         </is>
       </c>
       <c r="B286" t="n">
@@ -3291,7 +3291,7 @@
     <row r="287">
       <c r="A287" s="1" t="inlineStr">
         <is>
-          <t>FTR</t>
+          <t>OGN</t>
         </is>
       </c>
       <c r="B287" t="n">
@@ -3301,7 +3301,7 @@
     <row r="288">
       <c r="A288" s="1" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>VFC</t>
         </is>
       </c>
       <c r="B288" t="n">
@@ -3311,7 +3311,7 @@
     <row r="289">
       <c r="A289" s="1" t="inlineStr">
         <is>
-          <t>FTI</t>
+          <t>SLM</t>
         </is>
       </c>
       <c r="B289" t="n">
@@ -3321,7 +3321,7 @@
     <row r="290">
       <c r="A290" s="1" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>NAVI</t>
         </is>
       </c>
       <c r="B290" t="n">
@@ -3331,7 +3331,7 @@
     <row r="291">
       <c r="A291" s="1" t="inlineStr">
         <is>
-          <t>FRT</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B291" t="n">
@@ -3341,7 +3341,7 @@
     <row r="292">
       <c r="A292" s="1" t="inlineStr">
         <is>
-          <t>FRC</t>
+          <t>MPC</t>
         </is>
       </c>
       <c r="B292" t="n">
@@ -3351,7 +3351,7 @@
     <row r="293">
       <c r="A293" s="1" t="inlineStr">
         <is>
-          <t>FOXA</t>
+          <t>MOS</t>
         </is>
       </c>
       <c r="B293" t="n">
@@ -3361,7 +3361,7 @@
     <row r="294">
       <c r="A294" s="1" t="inlineStr">
         <is>
-          <t>FOX</t>
+          <t>WU</t>
         </is>
       </c>
       <c r="B294" t="n">
@@ -3371,7 +3371,7 @@
     <row r="295">
       <c r="A295" s="1" t="inlineStr">
         <is>
-          <t>FOSL</t>
+          <t>MOLX</t>
         </is>
       </c>
       <c r="B295" t="n">
@@ -3381,7 +3381,7 @@
     <row r="296">
       <c r="A296" s="1" t="inlineStr">
         <is>
-          <t>GPS</t>
+          <t>WY</t>
         </is>
       </c>
       <c r="B296" t="n">
@@ -3391,7 +3391,7 @@
     <row r="297">
       <c r="A297" s="1" t="inlineStr">
         <is>
-          <t>GPN</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B297" t="n">
@@ -3401,7 +3401,7 @@
     <row r="298">
       <c r="A298" s="1" t="inlineStr">
         <is>
-          <t>GPC</t>
+          <t>MNST</t>
         </is>
       </c>
       <c r="B298" t="n">
@@ -3411,7 +3411,7 @@
     <row r="299">
       <c r="A299" s="1" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>MNK</t>
         </is>
       </c>
       <c r="B299" t="n">
@@ -3421,7 +3421,7 @@
     <row r="300">
       <c r="A300" s="1" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="B300" t="n">
@@ -3431,7 +3431,7 @@
     <row r="301">
       <c r="A301" s="1" t="inlineStr">
         <is>
-          <t>GNW</t>
+          <t>WYND</t>
         </is>
       </c>
       <c r="B301" t="n">
@@ -3441,7 +3441,7 @@
     <row r="302">
       <c r="A302" s="1" t="inlineStr">
         <is>
-          <t>GNRC</t>
+          <t>WYNN</t>
         </is>
       </c>
       <c r="B302" t="n">
@@ -3451,7 +3451,7 @@
     <row r="303">
       <c r="A303" s="1" t="inlineStr">
         <is>
-          <t>GME</t>
+          <t>XEC</t>
         </is>
       </c>
       <c r="B303" t="n">
@@ -3461,7 +3461,7 @@
     <row r="304">
       <c r="A304" s="1" t="inlineStr">
         <is>
-          <t>GMCR</t>
+          <t>XEL</t>
         </is>
       </c>
       <c r="B304" t="n">
@@ -3471,7 +3471,7 @@
     <row r="305">
       <c r="A305" s="1" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="B305" t="n">
@@ -3481,7 +3481,7 @@
     <row r="306">
       <c r="A306" s="1" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B306" t="n">
@@ -3491,7 +3491,7 @@
     <row r="307">
       <c r="A307" s="1" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>XRAY</t>
         </is>
       </c>
       <c r="B307" t="n">
@@ -3501,7 +3501,7 @@
     <row r="308">
       <c r="A308" s="1" t="inlineStr">
         <is>
-          <t>GIS</t>
+          <t>MMI</t>
         </is>
       </c>
       <c r="B308" t="n">
@@ -3511,7 +3511,7 @@
     <row r="309">
       <c r="A309" s="1" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>MMC</t>
         </is>
       </c>
       <c r="B309" t="n">
@@ -3521,7 +3521,7 @@
     <row r="310">
       <c r="A310" s="1" t="inlineStr">
         <is>
-          <t>CPGX</t>
+          <t>XRX</t>
         </is>
       </c>
       <c r="B310" t="n">
@@ -3531,7 +3531,7 @@
     <row r="311">
       <c r="A311" s="1" t="inlineStr">
         <is>
-          <t>CPB</t>
+          <t>XTO</t>
         </is>
       </c>
       <c r="B311" t="n">
@@ -3541,7 +3541,7 @@
     <row r="312">
       <c r="A312" s="1" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>XYL</t>
         </is>
       </c>
       <c r="B312" t="n">
@@ -3551,7 +3551,7 @@
     <row r="313">
       <c r="A313" s="1" t="inlineStr">
         <is>
-          <t>COTY</t>
+          <t>MKTX</t>
         </is>
       </c>
       <c r="B313" t="n">
@@ -3561,7 +3561,7 @@
     <row r="314">
       <c r="A314" s="1" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>YHOO</t>
         </is>
       </c>
       <c r="B314" t="n">
@@ -3571,7 +3571,7 @@
     <row r="315">
       <c r="A315" s="1" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="B315" t="n">
@@ -3581,7 +3581,7 @@
     <row r="316">
       <c r="A316" s="1" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="B316" t="n">
@@ -3591,7 +3591,7 @@
     <row r="317">
       <c r="A317" s="1" t="inlineStr">
         <is>
-          <t>COO</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="B317" t="n">
@@ -3601,7 +3601,7 @@
     <row r="318">
       <c r="A318" s="1" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>WST</t>
         </is>
       </c>
       <c r="B318" t="n">
@@ -3611,7 +3611,7 @@
     <row r="319">
       <c r="A319" s="1" t="inlineStr">
         <is>
-          <t>COG</t>
+          <t>WRK</t>
         </is>
       </c>
       <c r="B319" t="n">
@@ -3621,7 +3621,7 @@
     <row r="320">
       <c r="A320" s="1" t="inlineStr">
         <is>
-          <t>COF</t>
+          <t>MRO</t>
         </is>
       </c>
       <c r="B320" t="n">
@@ -3631,7 +3631,7 @@
     <row r="321">
       <c r="A321" s="1" t="inlineStr">
         <is>
-          <t>CNP</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="B321" t="n">
@@ -3641,7 +3641,7 @@
     <row r="322">
       <c r="A322" s="1" t="inlineStr">
         <is>
-          <t>CNC</t>
+          <t>NDSN</t>
         </is>
       </c>
       <c r="B322" t="n">
@@ -3651,7 +3651,7 @@
     <row r="323">
       <c r="A323" s="1" t="inlineStr">
         <is>
-          <t>CMS</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B323" t="n">
@@ -3661,7 +3661,7 @@
     <row r="324">
       <c r="A324" s="1" t="inlineStr">
         <is>
-          <t>HIG</t>
+          <t>VTRS</t>
         </is>
       </c>
       <c r="B324" t="n">
@@ -3671,7 +3671,7 @@
     <row r="325">
       <c r="A325" s="1" t="inlineStr">
         <is>
-          <t>HFC</t>
+          <t>NCLH</t>
         </is>
       </c>
       <c r="B325" t="n">
@@ -3681,7 +3681,7 @@
     <row r="326">
       <c r="A326" s="1" t="inlineStr">
         <is>
-          <t>HES</t>
+          <t>NBR</t>
         </is>
       </c>
       <c r="B326" t="n">
@@ -3691,7 +3691,7 @@
     <row r="327">
       <c r="A327" s="1" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>NBL</t>
         </is>
       </c>
       <c r="B327" t="n">
@@ -3701,7 +3701,7 @@
     <row r="328">
       <c r="A328" s="1" t="inlineStr">
         <is>
-          <t>HCP</t>
+          <t>UNM</t>
         </is>
       </c>
       <c r="B328" t="n">
@@ -3711,7 +3711,7 @@
     <row r="329">
       <c r="A329" s="1" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>MYL</t>
         </is>
       </c>
       <c r="B329" t="n">
@@ -3721,7 +3721,7 @@
     <row r="330">
       <c r="A330" s="1" t="inlineStr">
         <is>
-          <t>HBI</t>
+          <t>MXIM</t>
         </is>
       </c>
       <c r="B330" t="n">
@@ -3731,7 +3731,7 @@
     <row r="331">
       <c r="A331" s="1" t="inlineStr">
         <is>
-          <t>HBAN</t>
+          <t>MWW</t>
         </is>
       </c>
       <c r="B331" t="n">
@@ -3741,7 +3741,7 @@
     <row r="332">
       <c r="A332" s="1" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>MWV</t>
         </is>
       </c>
       <c r="B332" t="n">
@@ -3751,7 +3751,7 @@
     <row r="333">
       <c r="A333" s="1" t="inlineStr">
         <is>
-          <t>HAR</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="B333" t="n">
@@ -3761,7 +3761,7 @@
     <row r="334">
       <c r="A334" s="1" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>MUR</t>
         </is>
       </c>
       <c r="B334" t="n">
@@ -3771,7 +3771,7 @@
     <row r="335">
       <c r="A335" s="1" t="inlineStr">
         <is>
-          <t>GWW</t>
+          <t>WAB</t>
         </is>
       </c>
       <c r="B335" t="n">
@@ -3781,7 +3781,7 @@
     <row r="336">
       <c r="A336" s="1" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>MTCH</t>
         </is>
       </c>
       <c r="B336" t="n">
@@ -3791,7 +3791,7 @@
     <row r="337">
       <c r="A337" s="1" t="inlineStr">
         <is>
-          <t>HUM</t>
+          <t>WBA</t>
         </is>
       </c>
       <c r="B337" t="n">
@@ -3801,7 +3801,7 @@
     <row r="338">
       <c r="A338" s="1" t="inlineStr">
         <is>
-          <t>HUBB</t>
+          <t>WBD</t>
         </is>
       </c>
       <c r="B338" t="n">
@@ -3811,7 +3811,7 @@
     <row r="339">
       <c r="A339" s="1" t="inlineStr">
         <is>
-          <t>HRL</t>
+          <t>WELL</t>
         </is>
       </c>
       <c r="B339" t="n">
@@ -3821,7 +3821,7 @@
     <row r="340">
       <c r="A340" s="1" t="inlineStr">
         <is>
-          <t>HRB</t>
+          <t>WMB</t>
         </is>
       </c>
       <c r="B340" t="n">
@@ -3831,7 +3831,7 @@
     <row r="341">
       <c r="A341" s="1" t="inlineStr">
         <is>
-          <t>HPQ</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="B341" t="n">
@@ -3841,7 +3841,7 @@
     <row r="342">
       <c r="A342" s="1" t="inlineStr">
         <is>
-          <t>HPE</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B342" t="n">
@@ -3851,7 +3851,7 @@
     <row r="343">
       <c r="A343" s="1" t="inlineStr">
         <is>
-          <t>HOT</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="B343" t="n">
@@ -3861,7 +3861,7 @@
     <row r="344">
       <c r="A344" s="1" t="inlineStr">
         <is>
-          <t>HON</t>
+          <t>WPX</t>
         </is>
       </c>
       <c r="B344" t="n">
@@ -3871,7 +3871,7 @@
     <row r="345">
       <c r="A345" s="1" t="inlineStr">
         <is>
-          <t>HOLX</t>
+          <t>WRB</t>
         </is>
       </c>
       <c r="B345" t="n">
@@ -3881,7 +3881,7 @@
     <row r="346">
       <c r="A346" s="1" t="inlineStr">
         <is>
-          <t>HLT</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B346" t="n">
@@ -3891,7 +3891,7 @@
     <row r="347">
       <c r="A347" s="1" t="inlineStr">
         <is>
-          <t>IQV</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B347" t="n">
@@ -3901,7 +3901,7 @@
     <row r="348">
       <c r="A348" s="1" t="inlineStr">
         <is>
-          <t>IPGP</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B348" t="n">
@@ -3911,7 +3911,7 @@
     <row r="349">
       <c r="A349" s="1" t="inlineStr">
         <is>
-          <t>IP</t>
+          <t>UAA</t>
         </is>
       </c>
       <c r="B349" t="n">
@@ -3921,7 +3921,7 @@
     <row r="350">
       <c r="A350" s="1" t="inlineStr">
         <is>
-          <t>INVH</t>
+          <t>UDR</t>
         </is>
       </c>
       <c r="B350" t="n">
@@ -3931,7 +3931,7 @@
     <row r="351">
       <c r="A351" s="1" t="inlineStr">
         <is>
-          <t>INFO</t>
+          <t>ROST</t>
         </is>
       </c>
       <c r="B351" t="n">
@@ -3941,7 +3941,7 @@
     <row r="352">
       <c r="A352" s="1" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>ROL</t>
         </is>
       </c>
       <c r="B352" t="n">
@@ -3951,7 +3951,7 @@
     <row r="353">
       <c r="A353" s="1" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>ROK</t>
         </is>
       </c>
       <c r="B353" t="n">
@@ -3961,7 +3961,7 @@
     <row r="354">
       <c r="A354" s="1" t="inlineStr">
         <is>
-          <t>IFF</t>
+          <t>STT</t>
         </is>
       </c>
       <c r="B354" t="n">
@@ -3971,7 +3971,7 @@
     <row r="355">
       <c r="A355" s="1" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>RL</t>
         </is>
       </c>
       <c r="B355" t="n">
@@ -3981,7 +3981,7 @@
     <row r="356">
       <c r="A356" s="1" t="inlineStr">
         <is>
-          <t>IDXX</t>
+          <t>RJF</t>
         </is>
       </c>
       <c r="B356" t="n">
@@ -3991,7 +3991,7 @@
     <row r="357">
       <c r="A357" s="1" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>STZ</t>
         </is>
       </c>
       <c r="B357" t="n">
@@ -4001,7 +4001,7 @@
     <row r="358">
       <c r="A358" s="1" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>SUN</t>
         </is>
       </c>
       <c r="B358" t="n">
@@ -4011,7 +4011,7 @@
     <row r="359">
       <c r="A359" s="1" t="inlineStr">
         <is>
-          <t>HWM</t>
+          <t>RHI</t>
         </is>
       </c>
       <c r="B359" t="n">
@@ -4021,7 +4021,7 @@
     <row r="360">
       <c r="A360" s="1" t="inlineStr">
         <is>
-          <t>CMI</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="B360" t="n">
@@ -4031,7 +4031,7 @@
     <row r="361">
       <c r="A361" s="1" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B361" t="n">
@@ -4041,7 +4041,7 @@
     <row r="362">
       <c r="A362" s="1" t="inlineStr">
         <is>
-          <t>CMCSK</t>
+          <t>SUNEQ</t>
         </is>
       </c>
       <c r="B362" t="n">
@@ -4051,7 +4051,7 @@
     <row r="363">
       <c r="A363" s="1" t="inlineStr">
         <is>
-          <t>CLX</t>
+          <t>RRC</t>
         </is>
       </c>
       <c r="B363" t="n">
@@ -4061,7 +4061,7 @@
     <row r="364">
       <c r="A364" s="1" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>SVU</t>
         </is>
       </c>
       <c r="B364" t="n">
@@ -4071,7 +4071,7 @@
     <row r="365">
       <c r="A365" s="1" t="inlineStr">
         <is>
-          <t>CINF</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="B365" t="n">
@@ -4081,7 +4081,7 @@
     <row r="366">
       <c r="A366" s="1" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>SWN</t>
         </is>
       </c>
       <c r="B366" t="n">
@@ -4091,7 +4091,7 @@
     <row r="367">
       <c r="A367" s="1" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="B367" t="n">
@@ -4101,7 +4101,7 @@
     <row r="368">
       <c r="A368" s="1" t="inlineStr">
         <is>
-          <t>CHRW</t>
+          <t>RDC</t>
         </is>
       </c>
       <c r="B368" t="n">
@@ -4111,7 +4111,7 @@
     <row r="369">
       <c r="A369" s="1" t="inlineStr">
         <is>
-          <t>CHK</t>
+          <t>RCL</t>
         </is>
       </c>
       <c r="B369" t="n">
@@ -4121,7 +4121,7 @@
     <row r="370">
       <c r="A370" s="1" t="inlineStr">
         <is>
-          <t>CHD</t>
+          <t>R</t>
         </is>
       </c>
       <c r="B370" t="n">
@@ -4131,7 +4131,7 @@
     <row r="371">
       <c r="A371" s="1" t="inlineStr">
         <is>
-          <t>CFN</t>
+          <t>QRVO</t>
         </is>
       </c>
       <c r="B371" t="n">
@@ -4141,7 +4141,7 @@
     <row r="372">
       <c r="A372" s="1" t="inlineStr">
         <is>
-          <t>JNPR</t>
+          <t>QLGC</t>
         </is>
       </c>
       <c r="B372" t="n">
@@ -4151,7 +4151,7 @@
     <row r="373">
       <c r="A373" s="1" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>QEP</t>
         </is>
       </c>
       <c r="B373" t="n">
@@ -4161,7 +4161,7 @@
     <row r="374">
       <c r="A374" s="1" t="inlineStr">
         <is>
-          <t>JEF</t>
+          <t>SYF</t>
         </is>
       </c>
       <c r="B374" t="n">
@@ -4171,7 +4171,7 @@
     <row r="375">
       <c r="A375" s="1" t="inlineStr">
         <is>
-          <t>JEC</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="B375" t="n">
@@ -4181,7 +4181,7 @@
     <row r="376">
       <c r="A376" s="1" t="inlineStr">
         <is>
-          <t>JCI</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B376" t="n">
@@ -4191,7 +4191,7 @@
     <row r="377">
       <c r="A377" s="1" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>REG</t>
         </is>
       </c>
       <c r="B377" t="n">
@@ -4201,7 +4201,7 @@
     <row r="378">
       <c r="A378" s="1" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>PXD</t>
         </is>
       </c>
       <c r="B378" t="n">
@@ -4211,7 +4211,7 @@
     <row r="379">
       <c r="A379" s="1" t="inlineStr">
         <is>
-          <t>IVZ</t>
+          <t>RRD</t>
         </is>
       </c>
       <c r="B379" t="n">
@@ -4221,7 +4221,7 @@
     <row r="380">
       <c r="A380" s="1" t="inlineStr">
         <is>
-          <t>ITW</t>
+          <t>STJ</t>
         </is>
       </c>
       <c r="B380" t="n">
@@ -4231,7 +4231,7 @@
     <row r="381">
       <c r="A381" s="1" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="B381" t="n">
@@ -4241,7 +4241,7 @@
     <row r="382">
       <c r="A382" s="1" t="inlineStr">
         <is>
-          <t>IR</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B382" t="n">
@@ -4251,7 +4251,7 @@
     <row r="383">
       <c r="A383" s="1" t="inlineStr">
         <is>
-          <t>KRFT</t>
+          <t>SIVB</t>
         </is>
       </c>
       <c r="B383" t="n">
@@ -4261,7 +4261,7 @@
     <row r="384">
       <c r="A384" s="1" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SNPS</t>
         </is>
       </c>
       <c r="B384" t="n">
@@ -4271,7 +4271,7 @@
     <row r="385">
       <c r="A385" s="1" t="inlineStr">
         <is>
-          <t>KORS</t>
+          <t>SII</t>
         </is>
       </c>
       <c r="B385" t="n">
@@ -4281,7 +4281,7 @@
     <row r="386">
       <c r="A386" s="1" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>SO</t>
         </is>
       </c>
       <c r="B386" t="n">
@@ -4291,7 +4291,7 @@
     <row r="387">
       <c r="A387" s="1" t="inlineStr">
         <is>
-          <t>KMI</t>
+          <t>SOLV</t>
         </is>
       </c>
       <c r="B387" t="n">
@@ -4301,7 +4301,7 @@
     <row r="388">
       <c r="A388" s="1" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>SIG</t>
         </is>
       </c>
       <c r="B388" t="n">
@@ -4311,7 +4311,7 @@
     <row r="389">
       <c r="A389" s="1" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>SIAL</t>
         </is>
       </c>
       <c r="B389" t="n">
@@ -4321,7 +4321,7 @@
     <row r="390">
       <c r="A390" s="1" t="inlineStr">
         <is>
-          <t>KKR</t>
+          <t>SPLS</t>
         </is>
       </c>
       <c r="B390" t="n">
@@ -4331,7 +4331,7 @@
     <row r="391">
       <c r="A391" s="1" t="inlineStr">
         <is>
-          <t>KIM</t>
+          <t>SRCL</t>
         </is>
       </c>
       <c r="B391" t="n">
@@ -4341,7 +4341,7 @@
     <row r="392">
       <c r="A392" s="1" t="inlineStr">
         <is>
-          <t>KHC</t>
+          <t>SRE</t>
         </is>
       </c>
       <c r="B392" t="n">
@@ -4351,7 +4351,7 @@
     <row r="393">
       <c r="A393" s="1" t="inlineStr">
         <is>
-          <t>KDP</t>
+          <t>STR</t>
         </is>
       </c>
       <c r="B393" t="n">
@@ -4361,7 +4361,7 @@
     <row r="394">
       <c r="A394" s="1" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>SEE</t>
         </is>
       </c>
       <c r="B394" t="n">
@@ -4371,7 +4371,7 @@
     <row r="395">
       <c r="A395" s="1" t="inlineStr">
         <is>
-          <t>JWN</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B395" t="n">
@@ -4381,7 +4381,7 @@
     <row r="396">
       <c r="A396" s="1" t="inlineStr">
         <is>
-          <t>LKQ</t>
+          <t>STE</t>
         </is>
       </c>
       <c r="B396" t="n">
@@ -4391,7 +4391,7 @@
     <row r="397">
       <c r="A397" s="1" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="B397" t="n">
@@ -4401,7 +4401,7 @@
     <row r="398">
       <c r="A398" s="1" t="inlineStr">
         <is>
-          <t>LII</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B398" t="n">
@@ -4411,7 +4411,7 @@
     <row r="399">
       <c r="A399" s="1" t="inlineStr">
         <is>
-          <t>LHX</t>
+          <t>SBNY</t>
         </is>
       </c>
       <c r="B399" t="n">
@@ -4421,7 +4421,7 @@
     <row r="400">
       <c r="A400" s="1" t="inlineStr">
         <is>
-          <t>LH</t>
+          <t>STI</t>
         </is>
       </c>
       <c r="B400" t="n">
@@ -4431,7 +4431,7 @@
     <row r="401">
       <c r="A401" s="1" t="inlineStr">
         <is>
-          <t>LEN</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B401" t="n">
@@ -4441,7 +4441,7 @@
     <row r="402">
       <c r="A402" s="1" t="inlineStr">
         <is>
-          <t>LEG</t>
+          <t>RX</t>
         </is>
       </c>
       <c r="B402" t="n">
@@ -4451,7 +4451,7 @@
     <row r="403">
       <c r="A403" s="1" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="B403" t="n">
@@ -4461,7 +4461,7 @@
     <row r="404">
       <c r="A404" s="1" t="inlineStr">
         <is>
-          <t>KVUE</t>
+          <t>RVTY</t>
         </is>
       </c>
       <c r="B404" t="n">
@@ -4471,7 +4471,7 @@
     <row r="405">
       <c r="A405" s="1" t="inlineStr">
         <is>
-          <t>KSU</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B405" t="n">
@@ -4481,7 +4481,7 @@
     <row r="406">
       <c r="A406" s="1" t="inlineStr">
         <is>
-          <t>KSS</t>
+          <t>RSHCQ</t>
         </is>
       </c>
       <c r="B406" t="n">
@@ -4491,7 +4491,7 @@
     <row r="407">
       <c r="A407" s="1" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>SEDG</t>
         </is>
       </c>
       <c r="B407" t="n">
@@ -4501,7 +4501,7 @@
     <row r="408">
       <c r="A408" s="1" t="inlineStr">
         <is>
-          <t>CERN</t>
+          <t>PX</t>
         </is>
       </c>
       <c r="B408" t="n">
@@ -4511,7 +4511,7 @@
     <row r="409">
       <c r="A409" s="1" t="inlineStr">
         <is>
-          <t>CELG</t>
+          <t>PWR</t>
         </is>
       </c>
       <c r="B409" t="n">
@@ -4521,7 +4521,7 @@
     <row r="410">
       <c r="A410" s="1" t="inlineStr">
         <is>
-          <t>CEG</t>
+          <t>PVH</t>
         </is>
       </c>
       <c r="B410" t="n">
@@ -4531,7 +4531,7 @@
     <row r="411">
       <c r="A411" s="1" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>TRMB</t>
         </is>
       </c>
       <c r="B411" t="n">
@@ -4541,7 +4541,7 @@
     <row r="412">
       <c r="A412" s="1" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="B412" t="n">
@@ -4551,7 +4551,7 @@
     <row r="413">
       <c r="A413" s="1" t="inlineStr">
         <is>
-          <t>CDNS</t>
+          <t>PEG</t>
         </is>
       </c>
       <c r="B413" t="n">
@@ -4561,7 +4561,7 @@
     <row r="414">
       <c r="A414" s="1" t="inlineStr">
         <is>
-          <t>CDAY</t>
+          <t>PEAK</t>
         </is>
       </c>
       <c r="B414" t="n">
@@ -4571,7 +4571,7 @@
     <row r="415">
       <c r="A415" s="1" t="inlineStr">
         <is>
-          <t>CCL</t>
+          <t>PDCO</t>
         </is>
       </c>
       <c r="B415" t="n">
@@ -4581,7 +4581,7 @@
     <row r="416">
       <c r="A416" s="1" t="inlineStr">
         <is>
-          <t>CCI</t>
+          <t>TRV</t>
         </is>
       </c>
       <c r="B416" t="n">
@@ -4591,7 +4591,7 @@
     <row r="417">
       <c r="A417" s="1" t="inlineStr">
         <is>
-          <t>CCE</t>
+          <t>TSCO</t>
         </is>
       </c>
       <c r="B417" t="n">
@@ -4601,7 +4601,7 @@
     <row r="418">
       <c r="A418" s="1" t="inlineStr">
         <is>
-          <t>CBOE</t>
+          <t>TSN</t>
         </is>
       </c>
       <c r="B418" t="n">
@@ -4611,7 +4611,7 @@
     <row r="419">
       <c r="A419" s="1" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>TSS</t>
         </is>
       </c>
       <c r="B419" t="n">
@@ -4621,7 +4621,7 @@
     <row r="420">
       <c r="A420" s="1" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>TT</t>
         </is>
       </c>
       <c r="B420" t="n">
@@ -4631,7 +4631,7 @@
     <row r="421">
       <c r="A421" s="1" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>TTWO</t>
         </is>
       </c>
       <c r="B421" t="n">
@@ -4641,7 +4641,7 @@
     <row r="422">
       <c r="A422" s="1" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>TWX</t>
         </is>
       </c>
       <c r="B422" t="n">
@@ -4651,7 +4651,7 @@
     <row r="423">
       <c r="A423" s="1" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>TRIP</t>
         </is>
       </c>
       <c r="B423" t="n">
@@ -4661,7 +4661,7 @@
     <row r="424">
       <c r="A424" s="1" t="inlineStr">
         <is>
-          <t>LYV</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B424" t="n">
@@ -4671,7 +4671,7 @@
     <row r="425">
       <c r="A425" s="1" t="inlineStr">
         <is>
-          <t>LYB</t>
+          <t>TYL</t>
         </is>
       </c>
       <c r="B425" t="n">
@@ -4681,7 +4681,7 @@
     <row r="426">
       <c r="A426" s="1" t="inlineStr">
         <is>
-          <t>LVS</t>
+          <t>PAYC</t>
         </is>
       </c>
       <c r="B426" t="n">
@@ -4691,7 +4691,7 @@
     <row r="427">
       <c r="A427" s="1" t="inlineStr">
         <is>
-          <t>LUV</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B427" t="n">
@@ -4701,7 +4701,7 @@
     <row r="428">
       <c r="A428" s="1" t="inlineStr">
         <is>
-          <t>LUMN</t>
+          <t>PARA</t>
         </is>
       </c>
       <c r="B428" t="n">
@@ -4711,7 +4711,7 @@
     <row r="429">
       <c r="A429" s="1" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B429" t="n">
@@ -4721,7 +4721,7 @@
     <row r="430">
       <c r="A430" s="1" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B430" t="n">
@@ -4731,7 +4731,7 @@
     <row r="431">
       <c r="A431" s="1" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>UAL</t>
         </is>
       </c>
       <c r="B431" t="n">
@@ -4741,7 +4741,7 @@
     <row r="432">
       <c r="A432" s="1" t="inlineStr">
         <is>
-          <t>LO</t>
+          <t>ORLY</t>
         </is>
       </c>
       <c r="B432" t="n">
@@ -4751,7 +4751,7 @@
     <row r="433">
       <c r="A433" s="1" t="inlineStr">
         <is>
-          <t>MJN</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B433" t="n">
@@ -4761,7 +4761,7 @@
     <row r="434">
       <c r="A434" s="1" t="inlineStr">
         <is>
-          <t>MHK</t>
+          <t>ON</t>
         </is>
       </c>
       <c r="B434" t="n">
@@ -4771,7 +4771,7 @@
     <row r="435">
       <c r="A435" s="1" t="inlineStr">
         <is>
-          <t>MGM</t>
+          <t>OMC</t>
         </is>
       </c>
       <c r="B435" t="n">
@@ -4781,7 +4781,7 @@
     <row r="436">
       <c r="A436" s="1" t="inlineStr">
         <is>
-          <t>MET</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="B436" t="n">
@@ -4791,7 +4791,7 @@
     <row r="437">
       <c r="A437" s="1" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="B437" t="n">
@@ -4801,7 +4801,7 @@
     <row r="438">
       <c r="A438" s="1" t="inlineStr">
         <is>
-          <t>MDLZ</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="B438" t="n">
@@ -4811,7 +4811,7 @@
     <row r="439">
       <c r="A439" s="1" t="inlineStr">
         <is>
-          <t>MCO</t>
+          <t>TPR</t>
         </is>
       </c>
       <c r="B439" t="n">
@@ -4821,7 +4821,7 @@
     <row r="440">
       <c r="A440" s="1" t="inlineStr">
         <is>
-          <t>MCHP</t>
+          <t>PENN</t>
         </is>
       </c>
       <c r="B440" t="n">
@@ -4831,7 +4831,7 @@
     <row r="441">
       <c r="A441" s="1" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>SYK</t>
         </is>
       </c>
       <c r="B441" t="n">
@@ -4841,7 +4841,7 @@
     <row r="442">
       <c r="A442" s="1" t="inlineStr">
         <is>
-          <t>MAT</t>
+          <t>SYMC</t>
         </is>
       </c>
       <c r="B442" t="n">
@@ -4851,7 +4851,7 @@
     <row r="443">
       <c r="A443" s="1" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B443" t="n">
@@ -4861,7 +4861,7 @@
     <row r="444">
       <c r="A444" s="1" t="inlineStr">
         <is>
-          <t>MAC</t>
+          <t>PRU</t>
         </is>
       </c>
       <c r="B444" t="n">
@@ -4871,7 +4871,7 @@
     <row r="445">
       <c r="A445" s="1" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>PRGO</t>
         </is>
       </c>
       <c r="B445" t="n">
@@ -4881,7 +4881,7 @@
     <row r="446">
       <c r="A446" s="1" t="inlineStr">
         <is>
-          <t>MRO</t>
+          <t>PPL</t>
         </is>
       </c>
       <c r="B446" t="n">
@@ -4891,7 +4891,7 @@
     <row r="447">
       <c r="A447" s="1" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>PPG</t>
         </is>
       </c>
       <c r="B447" t="n">
@@ -4901,7 +4901,7 @@
     <row r="448">
       <c r="A448" s="1" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="B448" t="n">
@@ -4911,7 +4911,7 @@
     <row r="449">
       <c r="A449" s="1" t="inlineStr">
         <is>
-          <t>MPWR</t>
+          <t>PODD</t>
         </is>
       </c>
       <c r="B449" t="n">
@@ -4921,7 +4921,7 @@
     <row r="450">
       <c r="A450" s="1" t="inlineStr">
         <is>
-          <t>MPC</t>
+          <t>PNR</t>
         </is>
       </c>
       <c r="B450" t="n">
@@ -4931,7 +4931,7 @@
     <row r="451">
       <c r="A451" s="1" t="inlineStr">
         <is>
-          <t>MOS</t>
+          <t>TDC</t>
         </is>
       </c>
       <c r="B451" t="n">
@@ -4941,7 +4941,7 @@
     <row r="452">
       <c r="A452" s="1" t="inlineStr">
         <is>
-          <t>MON</t>
+          <t>PNC</t>
         </is>
       </c>
       <c r="B452" t="n">
@@ -4951,7 +4951,7 @@
     <row r="453">
       <c r="A453" s="1" t="inlineStr">
         <is>
-          <t>MOH</t>
+          <t>TDG</t>
         </is>
       </c>
       <c r="B453" t="n">
@@ -4961,7 +4961,7 @@
     <row r="454">
       <c r="A454" s="1" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B454" t="n">
@@ -4971,7 +4971,7 @@
     <row r="455">
       <c r="A455" s="1" t="inlineStr">
         <is>
-          <t>MNST</t>
+          <t>TDY</t>
         </is>
       </c>
       <c r="B455" t="n">
@@ -4981,7 +4981,7 @@
     <row r="456">
       <c r="A456" s="1" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>TFC</t>
         </is>
       </c>
       <c r="B456" t="n">
@@ -4991,7 +4991,7 @@
     <row r="457">
       <c r="A457" s="1" t="inlineStr">
         <is>
-          <t>MLM</t>
+          <t>PKG</t>
         </is>
       </c>
       <c r="B457" t="n">
@@ -5001,7 +5001,7 @@
     <row r="458">
       <c r="A458" s="1" t="inlineStr">
         <is>
-          <t>MKTX</t>
+          <t>PHM</t>
         </is>
       </c>
       <c r="B458" t="n">
@@ -5011,7 +5011,7 @@
     <row r="459">
       <c r="A459" s="1" t="inlineStr">
         <is>
-          <t>NCLH</t>
+          <t>TFX</t>
         </is>
       </c>
       <c r="B459" t="n">
@@ -5021,7 +5021,7 @@
     <row r="460">
       <c r="A460" s="1" t="inlineStr">
         <is>
-          <t>NBR</t>
+          <t>THC</t>
         </is>
       </c>
       <c r="B460" t="n">
@@ -5031,7 +5031,7 @@
     <row r="461">
       <c r="A461" s="1" t="inlineStr">
         <is>
-          <t>NBL</t>
+          <t>PGN</t>
         </is>
       </c>
       <c r="B461" t="n">
@@ -5041,7 +5041,7 @@
     <row r="462">
       <c r="A462" s="1" t="inlineStr">
         <is>
-          <t>NAVI</t>
+          <t>TLAB</t>
         </is>
       </c>
       <c r="B462" t="n">
@@ -5051,7 +5051,7 @@
     <row r="463">
       <c r="A463" s="1" t="inlineStr">
         <is>
-          <t>MYL</t>
+          <t>TMK</t>
         </is>
       </c>
       <c r="B463" t="n">
@@ -5061,7 +5061,7 @@
     <row r="464">
       <c r="A464" s="1" t="inlineStr">
         <is>
-          <t>MXIM</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B464" t="n">
@@ -5071,7 +5071,7 @@
     <row r="465">
       <c r="A465" s="1" t="inlineStr">
         <is>
-          <t>MWV</t>
+          <t>TPL</t>
         </is>
       </c>
       <c r="B465" t="n">
@@ -5081,7 +5081,7 @@
     <row r="466">
       <c r="A466" s="1" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="B466" t="n">
@@ -5091,7 +5091,7 @@
     <row r="467">
       <c r="A467" s="1" t="inlineStr">
         <is>
-          <t>MTD</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B467" t="n">
@@ -5101,7 +5101,7 @@
     <row r="468">
       <c r="A468" s="1" t="inlineStr">
         <is>
-          <t>MTCH</t>
+          <t>UHS</t>
         </is>
       </c>
       <c r="B468" t="n">
@@ -5111,7 +5111,7 @@
     <row r="469">
       <c r="A469" s="1" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>MHS</t>
         </is>
       </c>
       <c r="B469" t="n">
@@ -5121,7 +5121,7 @@
     <row r="470">
       <c r="A470" s="1" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>JCP</t>
         </is>
       </c>
       <c r="B470" t="n">
@@ -5131,7 +5131,7 @@
     <row r="471">
       <c r="A471" s="1" t="inlineStr">
         <is>
-          <t>CARR</t>
+          <t>MGM</t>
         </is>
       </c>
       <c r="B471" t="n">
@@ -5141,7 +5141,7 @@
     <row r="472">
       <c r="A472" s="1" t="inlineStr">
         <is>
-          <t>CAM</t>
+          <t>CFG</t>
         </is>
       </c>
       <c r="B472" t="n">
@@ -5151,7 +5151,7 @@
     <row r="473">
       <c r="A473" s="1" t="inlineStr">
         <is>
-          <t>CAH</t>
+          <t>CHD</t>
         </is>
       </c>
       <c r="B473" t="n">
@@ -5161,7 +5161,7 @@
     <row r="474">
       <c r="A474" s="1" t="inlineStr">
         <is>
-          <t>CAG</t>
+          <t>CHK</t>
         </is>
       </c>
       <c r="B474" t="n">
@@ -5171,7 +5171,7 @@
     <row r="475">
       <c r="A475" s="1" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>CHRW</t>
         </is>
       </c>
       <c r="B475" t="n">
@@ -5181,7 +5181,7 @@
     <row r="476">
       <c r="A476" s="1" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B476" t="n">
@@ -5191,7 +5191,7 @@
     <row r="477">
       <c r="A477" s="1" t="inlineStr">
         <is>
-          <t>BWA</t>
+          <t>CINF</t>
         </is>
       </c>
       <c r="B477" t="n">
@@ -5201,7 +5201,7 @@
     <row r="478">
       <c r="A478" s="1" t="inlineStr">
         <is>
-          <t>BRO</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B478" t="n">
@@ -5211,7 +5211,7 @@
     <row r="479">
       <c r="A479" s="1" t="inlineStr">
         <is>
-          <t>BRK-B</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="B479" t="n">
@@ -5221,7 +5221,7 @@
     <row r="480">
       <c r="A480" s="1" t="inlineStr">
         <is>
-          <t>BRCM</t>
+          <t>CLF</t>
         </is>
       </c>
       <c r="B480" t="n">
@@ -5231,7 +5231,7 @@
     <row r="481">
       <c r="A481" s="1" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="B481" t="n">
@@ -5241,7 +5241,7 @@
     <row r="482">
       <c r="A482" s="1" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>CNC</t>
         </is>
       </c>
       <c r="B482" t="n">
@@ -5251,7 +5251,7 @@
     <row r="483">
       <c r="A483" s="1" t="inlineStr">
         <is>
-          <t>NSC</t>
+          <t>CNP</t>
         </is>
       </c>
       <c r="B483" t="n">
@@ -5261,7 +5261,7 @@
     <row r="484">
       <c r="A484" s="1" t="inlineStr">
         <is>
-          <t>NRG</t>
+          <t>CNX</t>
         </is>
       </c>
       <c r="B484" t="n">
@@ -5271,7 +5271,7 @@
     <row r="485">
       <c r="A485" s="1" t="inlineStr">
         <is>
-          <t>NOW</t>
+          <t>COF</t>
         </is>
       </c>
       <c r="B485" t="n">
@@ -5281,7 +5281,7 @@
     <row r="486">
       <c r="A486" s="1" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>COG</t>
         </is>
       </c>
       <c r="B486" t="n">
@@ -5291,7 +5291,7 @@
     <row r="487">
       <c r="A487" s="1" t="inlineStr">
         <is>
-          <t>NLOK</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="B487" t="n">
@@ -5301,7 +5301,7 @@
     <row r="488">
       <c r="A488" s="1" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>CMCSK</t>
         </is>
       </c>
       <c r="B488" t="n">
@@ -5311,7 +5311,7 @@
     <row r="489">
       <c r="A489" s="1" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>COO</t>
         </is>
       </c>
       <c r="B489" t="n">
@@ -5321,7 +5321,7 @@
     <row r="490">
       <c r="A490" s="1" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>CERN</t>
         </is>
       </c>
       <c r="B490" t="n">
@@ -5331,7 +5331,7 @@
     <row r="491">
       <c r="A491" s="1" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="B491" t="n">
@@ -5341,7 +5341,7 @@
     <row r="492">
       <c r="A492" s="1" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>BTUUQ</t>
         </is>
       </c>
       <c r="B492" t="n">
@@ -5351,7 +5351,7 @@
     <row r="493">
       <c r="A493" s="1" t="inlineStr">
         <is>
-          <t>NDSN</t>
+          <t>BWA</t>
         </is>
       </c>
       <c r="B493" t="n">
@@ -5361,7 +5361,7 @@
     <row r="494">
       <c r="A494" s="1" t="inlineStr">
         <is>
-          <t>ON</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B494" t="n">
@@ -5371,7 +5371,7 @@
     <row r="495">
       <c r="A495" s="1" t="inlineStr">
         <is>
-          <t>OKE</t>
+          <t>BXLT</t>
         </is>
       </c>
       <c r="B495" t="n">
@@ -5381,7 +5381,7 @@
     <row r="496">
       <c r="A496" s="1" t="inlineStr">
         <is>
-          <t>OI</t>
+          <t>BXP</t>
         </is>
       </c>
       <c r="B496" t="n">
@@ -5391,7 +5391,7 @@
     <row r="497">
       <c r="A497" s="1" t="inlineStr">
         <is>
-          <t>OGN</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B497" t="n">
@@ -5401,7 +5401,7 @@
     <row r="498">
       <c r="A498" s="1" t="inlineStr">
         <is>
-          <t>ODFL</t>
+          <t>CAM</t>
         </is>
       </c>
       <c r="B498" t="n">
@@ -5411,7 +5411,7 @@
     <row r="499">
       <c r="A499" s="1" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>CEPH</t>
         </is>
       </c>
       <c r="B499" t="n">
@@ -5421,7 +5421,7 @@
     <row r="500">
       <c r="A500" s="1" t="inlineStr">
         <is>
-          <t>NXPI</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="B500" t="n">
@@ -5431,7 +5431,7 @@
     <row r="501">
       <c r="A501" s="1" t="inlineStr">
         <is>
-          <t>NWS</t>
+          <t>CBE</t>
         </is>
       </c>
       <c r="B501" t="n">
@@ -5441,7 +5441,7 @@
     <row r="502">
       <c r="A502" s="1" t="inlineStr">
         <is>
-          <t>NVR</t>
+          <t>CBRE</t>
         </is>
       </c>
       <c r="B502" t="n">
@@ -5451,7 +5451,7 @@
     <row r="503">
       <c r="A503" s="1" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>CCEP</t>
         </is>
       </c>
       <c r="B503" t="n">
@@ -5461,7 +5461,7 @@
     <row r="504">
       <c r="A504" s="1" t="inlineStr">
         <is>
-          <t>NUE</t>
+          <t>CCI</t>
         </is>
       </c>
       <c r="B504" t="n">
@@ -5471,7 +5471,7 @@
     <row r="505">
       <c r="A505" s="1" t="inlineStr">
         <is>
-          <t>NTRS</t>
+          <t>CCL</t>
         </is>
       </c>
       <c r="B505" t="n">
@@ -5481,7 +5481,7 @@
     <row r="506">
       <c r="A506" s="1" t="inlineStr">
         <is>
-          <t>NTAP</t>
+          <t>CDAY</t>
         </is>
       </c>
       <c r="B506" t="n">
@@ -5491,7 +5491,7 @@
     <row r="507">
       <c r="A507" s="1" t="inlineStr">
         <is>
-          <t>PCL</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="B507" t="n">
@@ -5501,7 +5501,7 @@
     <row r="508">
       <c r="A508" s="1" t="inlineStr">
         <is>
-          <t>PCG</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="B508" t="n">
@@ -5511,7 +5511,7 @@
     <row r="509">
       <c r="A509" s="1" t="inlineStr">
         <is>
-          <t>PCAR</t>
+          <t>BRO</t>
         </is>
       </c>
       <c r="B509" t="n">
@@ -5521,7 +5521,7 @@
     <row r="510">
       <c r="A510" s="1" t="inlineStr">
         <is>
-          <t>PBI</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="B510" t="n">
@@ -5531,7 +5531,7 @@
     <row r="511">
       <c r="A511" s="1" t="inlineStr">
         <is>
-          <t>PBCT</t>
+          <t>CPRT</t>
         </is>
       </c>
       <c r="B511" t="n">
@@ -5541,7 +5541,7 @@
     <row r="512">
       <c r="A512" s="1" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B512" t="n">
@@ -5551,7 +5551,7 @@
     <row r="513">
       <c r="A513" s="1" t="inlineStr">
         <is>
-          <t>PAYC</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="B513" t="n">
@@ -5561,7 +5561,7 @@
     <row r="514">
       <c r="A514" s="1" t="inlineStr">
         <is>
-          <t>PARA</t>
+          <t>DFS</t>
         </is>
       </c>
       <c r="B514" t="n">
@@ -5571,7 +5571,7 @@
     <row r="515">
       <c r="A515" s="1" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="B515" t="n">
@@ -5581,7 +5581,7 @@
     <row r="516">
       <c r="A516" s="1" t="inlineStr">
         <is>
-          <t>OTIS</t>
+          <t>DGX</t>
         </is>
       </c>
       <c r="B516" t="n">
@@ -5591,7 +5591,7 @@
     <row r="517">
       <c r="A517" s="1" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B517" t="n">
@@ -5601,7 +5601,7 @@
     <row r="518">
       <c r="A518" s="1" t="inlineStr">
         <is>
-          <t>BLL</t>
+          <t>DISH</t>
         </is>
       </c>
       <c r="B518" t="n">
@@ -5611,7 +5611,7 @@
     <row r="519">
       <c r="A519" s="1" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>DECK</t>
         </is>
       </c>
       <c r="B519" t="n">
@@ -5621,7 +5621,7 @@
     <row r="520">
       <c r="A520" s="1" t="inlineStr">
         <is>
-          <t>BLDR</t>
+          <t>DLR</t>
         </is>
       </c>
       <c r="B520" t="n">
@@ -5631,7 +5631,7 @@
     <row r="521">
       <c r="A521" s="1" t="inlineStr">
         <is>
-          <t>BKR</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="B521" t="n">
@@ -5641,7 +5641,7 @@
     <row r="522">
       <c r="A522" s="1" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>DOC</t>
         </is>
       </c>
       <c r="B522" t="n">
@@ -5651,7 +5651,7 @@
     <row r="523">
       <c r="A523" s="1" t="inlineStr">
         <is>
-          <t>BK</t>
+          <t>DOV</t>
         </is>
       </c>
       <c r="B523" t="n">
@@ -5661,7 +5661,7 @@
     <row r="524">
       <c r="A524" s="1" t="inlineStr">
         <is>
-          <t>BIO</t>
+          <t>DOW</t>
         </is>
       </c>
       <c r="B524" t="n">
@@ -5671,7 +5671,7 @@
     <row r="525">
       <c r="A525" s="1" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>DRE</t>
         </is>
       </c>
       <c r="B525" t="n">
@@ -5681,7 +5681,7 @@
     <row r="526">
       <c r="A526" s="1" t="inlineStr">
         <is>
-          <t>BHGE</t>
+          <t>DRI</t>
         </is>
       </c>
       <c r="B526" t="n">
@@ -5691,7 +5691,7 @@
     <row r="527">
       <c r="A527" s="1" t="inlineStr">
         <is>
-          <t>BHF</t>
+          <t>DTE</t>
         </is>
       </c>
       <c r="B527" t="n">
@@ -5701,7 +5701,7 @@
     <row r="528">
       <c r="A528" s="1" t="inlineStr">
         <is>
-          <t>BEN</t>
+          <t>DNR</t>
         </is>
       </c>
       <c r="B528" t="n">
@@ -5711,7 +5711,7 @@
     <row r="529">
       <c r="A529" s="1" t="inlineStr">
         <is>
-          <t>BCR</t>
+          <t>CPGX</t>
         </is>
       </c>
       <c r="B529" t="n">
@@ -5721,7 +5721,7 @@
     <row r="530">
       <c r="A530" s="1" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B530" t="n">
@@ -5731,7 +5731,7 @@
     <row r="531">
       <c r="A531" s="1" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="B531" t="n">
@@ -5741,7 +5741,7 @@
     <row r="532">
       <c r="A532" s="1" t="inlineStr">
         <is>
-          <t>PKI</t>
+          <t>CPT</t>
         </is>
       </c>
       <c r="B532" t="n">
@@ -5751,7 +5751,7 @@
     <row r="533">
       <c r="A533" s="1" t="inlineStr">
         <is>
-          <t>PKG</t>
+          <t>CRL</t>
         </is>
       </c>
       <c r="B533" t="n">
@@ -5761,7 +5761,7 @@
     <row r="534">
       <c r="A534" s="1" t="inlineStr">
         <is>
-          <t>PHM</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B534" t="n">
@@ -5771,7 +5771,7 @@
     <row r="535">
       <c r="A535" s="1" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B535" t="n">
@@ -5781,7 +5781,7 @@
     <row r="536">
       <c r="A536" s="1" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>CSGP</t>
         </is>
       </c>
       <c r="B536" t="n">
@@ -5791,7 +5791,7 @@
     <row r="537">
       <c r="A537" s="1" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>CSRA</t>
         </is>
       </c>
       <c r="B537" t="n">
@@ -5801,7 +5801,7 @@
     <row r="538">
       <c r="A538" s="1" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>CTAS</t>
         </is>
       </c>
       <c r="B538" t="n">
@@ -5811,7 +5811,7 @@
     <row r="539">
       <c r="A539" s="1" t="inlineStr">
         <is>
-          <t>PETM</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="B539" t="n">
@@ -5821,7 +5821,7 @@
     <row r="540">
       <c r="A540" s="1" t="inlineStr">
         <is>
-          <t>PENN</t>
+          <t>CTL</t>
         </is>
       </c>
       <c r="B540" t="n">
@@ -5831,7 +5831,7 @@
     <row r="541">
       <c r="A541" s="1" t="inlineStr">
         <is>
-          <t>PX</t>
+          <t>CTRA</t>
         </is>
       </c>
       <c r="B541" t="n">
@@ -5841,7 +5841,7 @@
     <row r="542">
       <c r="A542" s="1" t="inlineStr">
         <is>
-          <t>PWR</t>
+          <t>CTVA</t>
         </is>
       </c>
       <c r="B542" t="n">
@@ -5851,7 +5851,7 @@
     <row r="543">
       <c r="A543" s="1" t="inlineStr">
         <is>
-          <t>PVH</t>
+          <t>CVH</t>
         </is>
       </c>
       <c r="B543" t="n">
@@ -5861,7 +5861,7 @@
     <row r="544">
       <c r="A544" s="1" t="inlineStr">
         <is>
-          <t>PSA</t>
+          <t>CVS</t>
         </is>
       </c>
       <c r="B544" t="n">
@@ -5871,7 +5871,7 @@
     <row r="545">
       <c r="A545" s="1" t="inlineStr">
         <is>
-          <t>PRU</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B545" t="n">
@@ -5881,7 +5881,7 @@
     <row r="546">
       <c r="A546" s="1" t="inlineStr">
         <is>
-          <t>PRGO</t>
+          <t>CXO</t>
         </is>
       </c>
       <c r="B546" t="n">
@@ -5891,7 +5891,7 @@
     <row r="547">
       <c r="A547" s="1" t="inlineStr">
         <is>
-          <t>PPL</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B547" t="n">
@@ -5901,7 +5901,7 @@
     <row r="548">
       <c r="A548" s="1" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>CTLT</t>
         </is>
       </c>
       <c r="B548" t="n">
@@ -5911,7 +5911,7 @@
     <row r="549">
       <c r="A549" s="1" t="inlineStr">
         <is>
-          <t>POM</t>
+          <t>DTV</t>
         </is>
       </c>
       <c r="B549" t="n">
@@ -5921,7 +5921,7 @@
     <row r="550">
       <c r="A550" s="1" t="inlineStr">
         <is>
-          <t>PNW</t>
+          <t>BRK-B</t>
         </is>
       </c>
       <c r="B550" t="n">
@@ -5931,7 +5931,7 @@
     <row r="551">
       <c r="A551" s="1" t="inlineStr">
         <is>
-          <t>PNC</t>
+          <t>BNI</t>
         </is>
       </c>
       <c r="B551" t="n">
@@ -5941,7 +5941,7 @@
     <row r="552">
       <c r="A552" s="1" t="inlineStr">
         <is>
-          <t>BBT</t>
+          <t>AJG</t>
         </is>
       </c>
       <c r="B552" t="n">
@@ -5951,7 +5951,7 @@
     <row r="553">
       <c r="A553" s="1" t="inlineStr">
         <is>
-          <t>BBBY</t>
+          <t>AKAM</t>
         </is>
       </c>
       <c r="B553" t="n">
@@ -5961,7 +5961,7 @@
     <row r="554">
       <c r="A554" s="1" t="inlineStr">
         <is>
-          <t>BAX</t>
+          <t>AKS</t>
         </is>
       </c>
       <c r="B554" t="n">
@@ -5971,7 +5971,7 @@
     <row r="555">
       <c r="A555" s="1" t="inlineStr">
         <is>
-          <t>BALL</t>
+          <t>ALB</t>
         </is>
       </c>
       <c r="B555" t="n">
@@ -5981,7 +5981,7 @@
     <row r="556">
       <c r="A556" s="1" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B556" t="n">
@@ -5991,7 +5991,7 @@
     <row r="557">
       <c r="A557" s="1" t="inlineStr">
         <is>
-          <t>AZO</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="B557" t="n">
@@ -6001,7 +6001,7 @@
     <row r="558">
       <c r="A558" s="1" t="inlineStr">
         <is>
-          <t>AYI</t>
+          <t>ALLE</t>
         </is>
       </c>
       <c r="B558" t="n">
@@ -6011,7 +6011,7 @@
     <row r="559">
       <c r="A559" s="1" t="inlineStr">
         <is>
-          <t>AXP</t>
+          <t>AIZ</t>
         </is>
       </c>
       <c r="B559" t="n">
@@ -6021,7 +6021,7 @@
     <row r="560">
       <c r="A560" s="1" t="inlineStr">
         <is>
-          <t>AXON</t>
+          <t>ALXN</t>
         </is>
       </c>
       <c r="B560" t="n">
@@ -6031,7 +6031,7 @@
     <row r="561">
       <c r="A561" s="1" t="inlineStr">
         <is>
-          <t>AWK</t>
+          <t>AMT</t>
         </is>
       </c>
       <c r="B561" t="n">
@@ -6041,7 +6041,7 @@
     <row r="562">
       <c r="A562" s="1" t="inlineStr">
         <is>
-          <t>AVY</t>
+          <t>AMTM</t>
         </is>
       </c>
       <c r="B562" t="n">
@@ -6051,7 +6051,7 @@
     <row r="563">
       <c r="A563" s="1" t="inlineStr">
         <is>
-          <t>AVP</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B563" t="n">
@@ -6061,7 +6061,7 @@
     <row r="564">
       <c r="A564" s="1" t="inlineStr">
         <is>
-          <t>AVB</t>
+          <t>AN</t>
         </is>
       </c>
       <c r="B564" t="n">
@@ -6071,7 +6071,7 @@
     <row r="565">
       <c r="A565" s="1" t="inlineStr">
         <is>
-          <t>RJF</t>
+          <t>ANDV</t>
         </is>
       </c>
       <c r="B565" t="n">
@@ -6081,7 +6081,7 @@
     <row r="566">
       <c r="A566" s="1" t="inlineStr">
         <is>
-          <t>RIG</t>
+          <t>ANRZQ</t>
         </is>
       </c>
       <c r="B566" t="n">
@@ -6091,7 +6091,7 @@
     <row r="567">
       <c r="A567" s="1" t="inlineStr">
         <is>
-          <t>RHT</t>
+          <t>ANSS</t>
         </is>
       </c>
       <c r="B567" t="n">
@@ -6101,7 +6101,7 @@
     <row r="568">
       <c r="A568" s="1" t="inlineStr">
         <is>
-          <t>RHI</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="B568" t="n">
@@ -6111,7 +6111,7 @@
     <row r="569">
       <c r="A569" s="1" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>ANTM</t>
         </is>
       </c>
       <c r="B569" t="n">
@@ -6121,7 +6121,7 @@
     <row r="570">
       <c r="A570" s="1" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>AIV</t>
         </is>
       </c>
       <c r="B570" t="n">
@@ -6131,7 +6131,7 @@
     <row r="571">
       <c r="A571" s="1" t="inlineStr">
         <is>
-          <t>REG</t>
+          <t>AFL</t>
         </is>
       </c>
       <c r="B571" t="n">
@@ -6141,7 +6141,7 @@
     <row r="572">
       <c r="A572" s="1" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>AAP</t>
         </is>
       </c>
       <c r="B572" t="n">
@@ -6151,7 +6151,7 @@
     <row r="573">
       <c r="A573" s="1" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B573" t="n">
@@ -6161,7 +6161,7 @@
     <row r="574">
       <c r="A574" s="1" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="B574" t="n">
@@ -6171,7 +6171,7 @@
     <row r="575">
       <c r="A575" s="1" t="inlineStr">
         <is>
-          <t>PXD</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="B575" t="n">
@@ -6181,7 +6181,7 @@
     <row r="576">
       <c r="A576" s="1" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>ABMD</t>
         </is>
       </c>
       <c r="B576" t="n">
@@ -6191,7 +6191,7 @@
     <row r="577">
       <c r="A577" s="1" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B577" t="n">
@@ -6201,7 +6201,7 @@
     <row r="578">
       <c r="A578" s="1" t="inlineStr">
         <is>
-          <t>SCG</t>
+          <t>ACGL</t>
         </is>
       </c>
       <c r="B578" t="n">
@@ -6211,7 +6211,7 @@
     <row r="579">
       <c r="A579" s="1" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>AIR</t>
         </is>
       </c>
       <c r="B579" t="n">
@@ -6221,7 +6221,7 @@
     <row r="580">
       <c r="A580" s="1" t="inlineStr">
         <is>
-          <t>SBNY</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B580" t="n">
@@ -6231,7 +6231,7 @@
     <row r="581">
       <c r="A581" s="1" t="inlineStr">
         <is>
-          <t>SBAC</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B581" t="n">
@@ -6241,7 +6241,7 @@
     <row r="582">
       <c r="A582" s="1" t="inlineStr">
         <is>
-          <t>RVTY</t>
+          <t>ADI</t>
         </is>
       </c>
       <c r="B582" t="n">
@@ -6251,7 +6251,7 @@
     <row r="583">
       <c r="A583" s="1" t="inlineStr">
         <is>
-          <t>ROST</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="B583" t="n">
@@ -6261,7 +6261,7 @@
     <row r="584">
       <c r="A584" s="1" t="inlineStr">
         <is>
-          <t>ROP</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B584" t="n">
@@ -6271,7 +6271,7 @@
     <row r="585">
       <c r="A585" s="1" t="inlineStr">
         <is>
-          <t>ROL</t>
+          <t>ADS</t>
         </is>
       </c>
       <c r="B585" t="n">
@@ -6281,7 +6281,7 @@
     <row r="586">
       <c r="A586" s="1" t="inlineStr">
         <is>
-          <t>RL</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="B586" t="n">
@@ -6291,7 +6291,7 @@
     <row r="587">
       <c r="A587" s="1" t="inlineStr">
         <is>
-          <t>SOLV</t>
+          <t>AES</t>
         </is>
       </c>
       <c r="B587" t="n">
@@ -6301,7 +6301,7 @@
     <row r="588">
       <c r="A588" s="1" t="inlineStr">
         <is>
-          <t>SO</t>
+          <t>ACS</t>
         </is>
       </c>
       <c r="B588" t="n">
@@ -6311,7 +6311,7 @@
     <row r="589">
       <c r="A589" s="1" t="inlineStr">
         <is>
-          <t>SNPS</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="B589" t="n">
@@ -6321,7 +6321,7 @@
     <row r="590">
       <c r="A590" s="1" t="inlineStr">
         <is>
-          <t>SNI</t>
+          <t>AON</t>
         </is>
       </c>
       <c r="B590" t="n">
@@ -6331,7 +6331,7 @@
     <row r="591">
       <c r="A591" s="1" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>APD</t>
         </is>
       </c>
       <c r="B591" t="n">
@@ -6341,7 +6341,7 @@
     <row r="592">
       <c r="A592" s="1" t="inlineStr">
         <is>
-          <t>SNA</t>
+          <t>BEN</t>
         </is>
       </c>
       <c r="B592" t="n">
@@ -6351,7 +6351,7 @@
     <row r="593">
       <c r="A593" s="1" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>BF-B</t>
         </is>
       </c>
       <c r="B593" t="n">
@@ -6361,7 +6361,7 @@
     <row r="594">
       <c r="A594" s="1" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="B594" t="n">
@@ -6371,7 +6371,7 @@
     <row r="595">
       <c r="A595" s="1" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>BHF</t>
         </is>
       </c>
       <c r="B595" t="n">
@@ -6381,7 +6381,7 @@
     <row r="596">
       <c r="A596" s="1" t="inlineStr">
         <is>
-          <t>SJM</t>
+          <t>BHGE</t>
         </is>
       </c>
       <c r="B596" t="n">
@@ -6391,7 +6391,7 @@
     <row r="597">
       <c r="A597" s="1" t="inlineStr">
         <is>
-          <t>SIVB</t>
+          <t>BIIB</t>
         </is>
       </c>
       <c r="B597" t="n">
@@ -6401,7 +6401,7 @@
     <row r="598">
       <c r="A598" s="1" t="inlineStr">
         <is>
-          <t>SIG</t>
+          <t>BIO</t>
         </is>
       </c>
       <c r="B598" t="n">
@@ -6411,7 +6411,7 @@
     <row r="599">
       <c r="A599" s="1" t="inlineStr">
         <is>
-          <t>SIAL</t>
+          <t>BEAM</t>
         </is>
       </c>
       <c r="B599" t="n">
@@ -6421,7 +6421,7 @@
     <row r="600">
       <c r="A600" s="1" t="inlineStr">
         <is>
-          <t>SHW</t>
+          <t>BJS</t>
         </is>
       </c>
       <c r="B600" t="n">
@@ -6431,7 +6431,7 @@
     <row r="601">
       <c r="A601" s="1" t="inlineStr">
         <is>
-          <t>SEDG</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B601" t="n">
@@ -6441,7 +6441,7 @@
     <row r="602">
       <c r="A602" s="1" t="inlineStr">
         <is>
-          <t>ATVI</t>
+          <t>BKR</t>
         </is>
       </c>
       <c r="B602" t="n">
@@ -6451,7 +6451,7 @@
     <row r="603">
       <c r="A603" s="1" t="inlineStr">
         <is>
-          <t>ATI</t>
+          <t>BLDR</t>
         </is>
       </c>
       <c r="B603" t="n">
@@ -6461,7 +6461,7 @@
     <row r="604">
       <c r="A604" s="1" t="inlineStr">
         <is>
-          <t>ARNC</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="B604" t="n">
@@ -6471,7 +6471,7 @@
     <row r="605">
       <c r="A605" s="1" t="inlineStr">
         <is>
-          <t>ARE</t>
+          <t>BLL</t>
         </is>
       </c>
       <c r="B605" t="n">
@@ -6481,7 +6481,7 @@
     <row r="606">
       <c r="A606" s="1" t="inlineStr">
         <is>
-          <t>APTV</t>
+          <t>BMS</t>
         </is>
       </c>
       <c r="B606" t="n">
@@ -6491,7 +6491,7 @@
     <row r="607">
       <c r="A607" s="1" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="B607" t="n">
@@ -6501,7 +6501,7 @@
     <row r="608">
       <c r="A608" s="1" t="inlineStr">
         <is>
-          <t>APD</t>
+          <t>BK</t>
         </is>
       </c>
       <c r="B608" t="n">
@@ -6521,7 +6521,7 @@
     <row r="610">
       <c r="A610" s="1" t="inlineStr">
         <is>
-          <t>AOS</t>
+          <t>BDX</t>
         </is>
       </c>
       <c r="B610" t="n">
@@ -6531,7 +6531,7 @@
     <row r="611">
       <c r="A611" s="1" t="inlineStr">
         <is>
-          <t>AON</t>
+          <t>BBWI</t>
         </is>
       </c>
       <c r="B611" t="n">
@@ -6541,7 +6541,7 @@
     <row r="612">
       <c r="A612" s="1" t="inlineStr">
         <is>
-          <t>ANTM</t>
+          <t>APH</t>
         </is>
       </c>
       <c r="B612" t="n">
@@ -6551,7 +6551,7 @@
     <row r="613">
       <c r="A613" s="1" t="inlineStr">
         <is>
-          <t>ANSS</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="B613" t="n">
@@ -6561,7 +6561,7 @@
     <row r="614">
       <c r="A614" s="1" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>APOL</t>
         </is>
       </c>
       <c r="B614" t="n">
@@ -6571,7 +6571,7 @@
     <row r="615">
       <c r="A615" s="1" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>APTV</t>
         </is>
       </c>
       <c r="B615" t="n">
@@ -6581,7 +6581,7 @@
     <row r="616">
       <c r="A616" s="1" t="inlineStr">
         <is>
-          <t>STZ</t>
+          <t>ARE</t>
         </is>
       </c>
       <c r="B616" t="n">
@@ -6591,7 +6591,7 @@
     <row r="617">
       <c r="A617" s="1" t="inlineStr">
         <is>
-          <t>STJ</t>
+          <t>ARNC</t>
         </is>
       </c>
       <c r="B617" t="n">
@@ -6601,7 +6601,7 @@
     <row r="618">
       <c r="A618" s="1" t="inlineStr">
         <is>
-          <t>STI</t>
+          <t>ATGE</t>
         </is>
       </c>
       <c r="B618" t="n">
@@ -6611,7 +6611,7 @@
     <row r="619">
       <c r="A619" s="1" t="inlineStr">
         <is>
-          <t>STE</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="B619" t="n">
@@ -6621,7 +6621,7 @@
     <row r="620">
       <c r="A620" s="1" t="inlineStr">
         <is>
-          <t>SRE</t>
+          <t>ATI</t>
         </is>
       </c>
       <c r="B620" t="n">
@@ -6631,7 +6631,7 @@
     <row r="621">
       <c r="A621" s="1" t="inlineStr">
         <is>
-          <t>SPLS</t>
+          <t>AVP</t>
         </is>
       </c>
       <c r="B621" t="n">
@@ -6641,7 +6641,7 @@
     <row r="622">
       <c r="A622" s="1" t="inlineStr">
         <is>
-          <t>SPG</t>
+          <t>AYI</t>
         </is>
       </c>
       <c r="B622" t="n">
@@ -6651,7 +6651,7 @@
     <row r="623">
       <c r="A623" s="1" t="inlineStr">
         <is>
-          <t>TFC</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="B623" t="n">
@@ -6661,7 +6661,7 @@
     <row r="624">
       <c r="A624" s="1" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>BALL</t>
         </is>
       </c>
       <c r="B624" t="n">
@@ -6671,7 +6671,7 @@
     <row r="625">
       <c r="A625" s="1" t="inlineStr">
         <is>
-          <t>TEL</t>
+          <t>BAX</t>
         </is>
       </c>
       <c r="B625" t="n">
@@ -6681,7 +6681,7 @@
     <row r="626">
       <c r="A626" s="1" t="inlineStr">
         <is>
-          <t>TEG</t>
+          <t>BAYRY</t>
         </is>
       </c>
       <c r="B626" t="n">
@@ -6691,7 +6691,7 @@
     <row r="627">
       <c r="A627" s="1" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>BBBY</t>
         </is>
       </c>
       <c r="B627" t="n">
@@ -6701,7 +6701,7 @@
     <row r="628">
       <c r="A628" s="1" t="inlineStr">
         <is>
-          <t>TDY</t>
+          <t>ATO</t>
         </is>
       </c>
       <c r="B628" t="n">
@@ -6711,7 +6711,7 @@
     <row r="629">
       <c r="A629" s="1" t="inlineStr">
         <is>
-          <t>TDG</t>
+          <t>DUK</t>
         </is>
       </c>
       <c r="B629" t="n">
@@ -6721,7 +6721,7 @@
     <row r="630">
       <c r="A630" s="1" t="inlineStr">
         <is>
-          <t>TDC</t>
+          <t>DVA</t>
         </is>
       </c>
       <c r="B630" t="n">
@@ -6731,7 +6731,7 @@
     <row r="631">
       <c r="A631" s="1" t="inlineStr">
         <is>
-          <t>TAP</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="B631" t="n">
@@ -6741,7 +6741,7 @@
     <row r="632">
       <c r="A632" s="1" t="inlineStr">
         <is>
-          <t>SYMC</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B632" t="n">
@@ -6751,7 +6751,7 @@
     <row r="633">
       <c r="A633" s="1" t="inlineStr">
         <is>
-          <t>SYK</t>
+          <t>INVH</t>
         </is>
       </c>
       <c r="B633" t="n">
@@ -6761,7 +6761,7 @@
     <row r="634">
       <c r="A634" s="1" t="inlineStr">
         <is>
-          <t>SWY</t>
+          <t>IP</t>
         </is>
       </c>
       <c r="B634" t="n">
@@ -6771,7 +6771,7 @@
     <row r="635">
       <c r="A635" s="1" t="inlineStr">
         <is>
-          <t>ANDV</t>
+          <t>IQV</t>
         </is>
       </c>
       <c r="B635" t="n">
@@ -6781,7 +6781,7 @@
     <row r="636">
       <c r="A636" s="1" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>ITW</t>
         </is>
       </c>
       <c r="B636" t="n">
@@ -6791,7 +6791,7 @@
     <row r="637">
       <c r="A637" s="1" t="inlineStr">
         <is>
-          <t>AMTM</t>
+          <t>IVZ</t>
         </is>
       </c>
       <c r="B637" t="n">
@@ -6801,7 +6801,7 @@
     <row r="638">
       <c r="A638" s="1" t="inlineStr">
         <is>
-          <t>AMT</t>
+          <t>J</t>
         </is>
       </c>
       <c r="B638" t="n">
@@ -6811,7 +6811,7 @@
     <row r="639">
       <c r="A639" s="1" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>INFO</t>
         </is>
       </c>
       <c r="B639" t="n">
@@ -6821,7 +6821,7 @@
     <row r="640">
       <c r="A640" s="1" t="inlineStr">
         <is>
-          <t>AMG</t>
+          <t>JAVA</t>
         </is>
       </c>
       <c r="B640" t="n">
@@ -6831,7 +6831,7 @@
     <row r="641">
       <c r="A641" s="1" t="inlineStr">
         <is>
-          <t>AME</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="B641" t="n">
@@ -6841,7 +6841,7 @@
     <row r="642">
       <c r="A642" s="1" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>JCI</t>
         </is>
       </c>
       <c r="B642" t="n">
@@ -6851,7 +6851,7 @@
     <row r="643">
       <c r="A643" s="1" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>ZION</t>
         </is>
       </c>
       <c r="B643" t="n">
@@ -6861,7 +6861,7 @@
     <row r="644">
       <c r="A644" s="1" t="inlineStr">
         <is>
-          <t>ALXN</t>
+          <t>JEC</t>
         </is>
       </c>
       <c r="B644" t="n">
@@ -6871,7 +6871,7 @@
     <row r="645">
       <c r="A645" s="1" t="inlineStr">
         <is>
-          <t>ALTR</t>
+          <t>JEF</t>
         </is>
       </c>
       <c r="B645" t="n">
@@ -6881,7 +6881,7 @@
     <row r="646">
       <c r="A646" s="1" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="B646" t="n">
@@ -6891,7 +6891,7 @@
     <row r="647">
       <c r="A647" s="1" t="inlineStr">
         <is>
-          <t>TRV</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B647" t="n">
@@ -6901,7 +6901,7 @@
     <row r="648">
       <c r="A648" s="1" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="B648" t="n">
@@ -6911,7 +6911,7 @@
     <row r="649">
       <c r="A649" s="1" t="inlineStr">
         <is>
-          <t>TRMB</t>
+          <t>JNPR</t>
         </is>
       </c>
       <c r="B649" t="n">
@@ -6921,7 +6921,7 @@
     <row r="650">
       <c r="A650" s="1" t="inlineStr">
         <is>
-          <t>TRIP</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="B650" t="n">
@@ -6931,7 +6931,7 @@
     <row r="651">
       <c r="A651" s="1" t="inlineStr">
         <is>
-          <t>TPR</t>
+          <t>IGT</t>
         </is>
       </c>
       <c r="B651" t="n">
@@ -6941,7 +6941,7 @@
     <row r="652">
       <c r="A652" s="1" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>HES</t>
         </is>
       </c>
       <c r="B652" t="n">
@@ -6951,7 +6951,7 @@
     <row r="653">
       <c r="A653" s="1" t="inlineStr">
         <is>
-          <t>TMK</t>
+          <t>HFC</t>
         </is>
       </c>
       <c r="B653" t="n">
@@ -6961,7 +6961,7 @@
     <row r="654">
       <c r="A654" s="1" t="inlineStr">
         <is>
-          <t>TIF</t>
+          <t>HOT</t>
         </is>
       </c>
       <c r="B654" t="n">
@@ -6971,7 +6971,7 @@
     <row r="655">
       <c r="A655" s="1" t="inlineStr">
         <is>
-          <t>TFX</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="B655" t="n">
@@ -6981,7 +6981,7 @@
     <row r="656">
       <c r="A656" s="1" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>HPQ</t>
         </is>
       </c>
       <c r="B656" t="n">
@@ -6991,7 +6991,7 @@
     <row r="657">
       <c r="A657" s="1" t="inlineStr">
         <is>
-          <t>UAL</t>
+          <t>HRB</t>
         </is>
       </c>
       <c r="B657" t="n">
@@ -7001,7 +7001,7 @@
     <row r="658">
       <c r="A658" s="1" t="inlineStr">
         <is>
-          <t>UAA</t>
+          <t>HRL</t>
         </is>
       </c>
       <c r="B658" t="n">
@@ -7011,7 +7011,7 @@
     <row r="659">
       <c r="A659" s="1" t="inlineStr">
         <is>
-          <t>TYL</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="B659" t="n">
@@ -7021,7 +7021,7 @@
     <row r="660">
       <c r="A660" s="1" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>HRS</t>
         </is>
       </c>
       <c r="B660" t="n">
@@ -7031,7 +7031,7 @@
     <row r="661">
       <c r="A661" s="1" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>HSIC</t>
         </is>
       </c>
       <c r="B661" t="n">
@@ -7041,7 +7041,7 @@
     <row r="662">
       <c r="A662" s="1" t="inlineStr">
         <is>
-          <t>TWX</t>
+          <t>HST</t>
         </is>
       </c>
       <c r="B662" t="n">
@@ -7051,7 +7051,7 @@
     <row r="663">
       <c r="A663" s="1" t="inlineStr">
         <is>
-          <t>TWTR</t>
+          <t>HSY</t>
         </is>
       </c>
       <c r="B663" t="n">
@@ -7061,7 +7061,7 @@
     <row r="664">
       <c r="A664" s="1" t="inlineStr">
         <is>
-          <t>TWC</t>
+          <t>HUBB</t>
         </is>
       </c>
       <c r="B664" t="n">
@@ -7071,7 +7071,7 @@
     <row r="665">
       <c r="A665" s="1" t="inlineStr">
         <is>
-          <t>TTWO</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B665" t="n">
@@ -7081,7 +7081,7 @@
     <row r="666">
       <c r="A666" s="1" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="B666" t="n">
@@ -7091,7 +7091,7 @@
     <row r="667">
       <c r="A667" s="1" t="inlineStr">
         <is>
-          <t>TSS</t>
+          <t>IFF</t>
         </is>
       </c>
       <c r="B667" t="n">
@@ -7101,7 +7101,7 @@
     <row r="668">
       <c r="A668" s="1" t="inlineStr">
         <is>
-          <t>TSN</t>
+          <t>HSH</t>
         </is>
       </c>
       <c r="B668" t="n">
@@ -7111,7 +7111,7 @@
     <row r="669">
       <c r="A669" s="1" t="inlineStr">
         <is>
-          <t>VICI</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B669" t="n">
@@ -7121,7 +7121,7 @@
     <row r="670">
       <c r="A670" s="1" t="inlineStr">
         <is>
-          <t>VIAC</t>
+          <t>JNS</t>
         </is>
       </c>
       <c r="B670" t="n">
@@ -7131,7 +7131,7 @@
     <row r="671">
       <c r="A671" s="1" t="inlineStr">
         <is>
-          <t>VIAB</t>
+          <t>K</t>
         </is>
       </c>
       <c r="B671" t="n">
@@ -7141,7 +7141,7 @@
     <row r="672">
       <c r="A672" s="1" t="inlineStr">
         <is>
-          <t>VFC</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B672" t="n">
@@ -7151,7 +7151,7 @@
     <row r="673">
       <c r="A673" s="1" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B673" t="n">
@@ -7161,7 +7161,7 @@
     <row r="674">
       <c r="A674" s="1" t="inlineStr">
         <is>
-          <t>UTX</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="B674" t="n">
@@ -7171,7 +7171,7 @@
     <row r="675">
       <c r="A675" s="1" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>LUMN</t>
         </is>
       </c>
       <c r="B675" t="n">
@@ -7181,7 +7181,7 @@
     <row r="676">
       <c r="A676" s="1" t="inlineStr">
         <is>
-          <t>URI</t>
+          <t>LUV</t>
         </is>
       </c>
       <c r="B676" t="n">
@@ -7191,7 +7191,7 @@
     <row r="677">
       <c r="A677" s="1" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>LVS</t>
         </is>
       </c>
       <c r="B677" t="n">
@@ -7201,7 +7201,7 @@
     <row r="678">
       <c r="A678" s="1" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>LW</t>
         </is>
       </c>
       <c r="B678" t="n">
@@ -7211,7 +7211,7 @@
     <row r="679">
       <c r="A679" s="1" t="inlineStr">
         <is>
-          <t>UNM</t>
+          <t>LNT</t>
         </is>
       </c>
       <c r="B679" t="n">
@@ -7221,7 +7221,7 @@
     <row r="680">
       <c r="A680" s="1" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>LYB</t>
         </is>
       </c>
       <c r="B680" t="n">
@@ -7231,7 +7231,7 @@
     <row r="681">
       <c r="A681" s="1" t="inlineStr">
         <is>
-          <t>ULTA</t>
+          <t>MCHP</t>
         </is>
       </c>
       <c r="B681" t="n">
@@ -7241,7 +7241,7 @@
     <row r="682">
       <c r="A682" s="1" t="inlineStr">
         <is>
-          <t>WBD</t>
+          <t>MDLZ</t>
         </is>
       </c>
       <c r="B682" t="n">
@@ -7251,7 +7251,7 @@
     <row r="683">
       <c r="A683" s="1" t="inlineStr">
         <is>
-          <t>WAB</t>
+          <t>MDP</t>
         </is>
       </c>
       <c r="B683" t="n">
@@ -7261,7 +7261,7 @@
     <row r="684">
       <c r="A684" s="1" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B684" t="n">
@@ -7271,7 +7271,7 @@
     <row r="685">
       <c r="A685" s="1" t="inlineStr">
         <is>
-          <t>VTRS</t>
+          <t>MEE</t>
         </is>
       </c>
       <c r="B685" t="n">
@@ -7281,7 +7281,7 @@
     <row r="686">
       <c r="A686" s="1" t="inlineStr">
         <is>
-          <t>VTR</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B686" t="n">
@@ -7291,7 +7291,7 @@
     <row r="687">
       <c r="A687" s="1" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>MFE</t>
         </is>
       </c>
       <c r="B687" t="n">
@@ -7301,7 +7301,7 @@
     <row r="688">
       <c r="A688" s="1" t="inlineStr">
         <is>
-          <t>VRTX</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B688" t="n">
@@ -7311,7 +7311,7 @@
     <row r="689">
       <c r="A689" s="1" t="inlineStr">
         <is>
-          <t>VRSN</t>
+          <t>JWN</t>
         </is>
       </c>
       <c r="B689" t="n">
@@ -7321,7 +7321,7 @@
     <row r="690">
       <c r="A690" s="1" t="inlineStr">
         <is>
-          <t>VNT</t>
+          <t>LNC</t>
         </is>
       </c>
       <c r="B690" t="n">
@@ -7331,7 +7331,7 @@
     <row r="691">
       <c r="A691" s="1" t="inlineStr">
         <is>
-          <t>VNO</t>
+          <t>LII</t>
         </is>
       </c>
       <c r="B691" t="n">
@@ -7341,7 +7341,7 @@
     <row r="692">
       <c r="A692" s="1" t="inlineStr">
         <is>
-          <t>VMC</t>
+          <t>KDP</t>
         </is>
       </c>
       <c r="B692" t="n">
@@ -7351,7 +7351,7 @@
     <row r="693">
       <c r="A693" s="1" t="inlineStr">
         <is>
-          <t>VLTO</t>
+          <t>KEY</t>
         </is>
       </c>
       <c r="B693" t="n">
@@ -7361,7 +7361,7 @@
     <row r="694">
       <c r="A694" s="1" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>KEYS</t>
         </is>
       </c>
       <c r="B694" t="n">
@@ -7371,7 +7371,7 @@
     <row r="695">
       <c r="A695" s="1" t="inlineStr">
         <is>
-          <t>WU</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="B695" t="n">
@@ -7381,7 +7381,7 @@
     <row r="696">
       <c r="A696" s="1" t="inlineStr">
         <is>
-          <t>WST</t>
+          <t>KHC</t>
         </is>
       </c>
       <c r="B696" t="n">
@@ -7391,7 +7391,7 @@
     <row r="697">
       <c r="A697" s="1" t="inlineStr">
         <is>
-          <t>WRB</t>
+          <t>KKR</t>
         </is>
       </c>
       <c r="B697" t="n">
@@ -7401,7 +7401,7 @@
     <row r="698">
       <c r="A698" s="1" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B698" t="n">
@@ -7411,7 +7411,7 @@
     <row r="699">
       <c r="A699" s="1" t="inlineStr">
         <is>
-          <t>WMB</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B699" t="n">
@@ -7421,7 +7421,7 @@
     <row r="700">
       <c r="A700" s="1" t="inlineStr">
         <is>
-          <t>WM</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="B700" t="n">
@@ -7431,7 +7431,7 @@
     <row r="701">
       <c r="A701" s="1" t="inlineStr">
         <is>
-          <t>WLTW</t>
+          <t>KMX</t>
         </is>
       </c>
       <c r="B701" t="n">
@@ -7441,7 +7441,7 @@
     <row r="702">
       <c r="A702" s="1" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B702" t="n">
@@ -7451,7 +7451,7 @@
     <row r="703">
       <c r="A703" s="1" t="inlineStr">
         <is>
-          <t>WHR</t>
+          <t>KVUE</t>
         </is>
       </c>
       <c r="B703" t="n">
@@ -7461,7 +7461,7 @@
     <row r="704">
       <c r="A704" s="1" t="inlineStr">
         <is>
-          <t>WELL</t>
+          <t>L</t>
         </is>
       </c>
       <c r="B704" t="n">
@@ -7471,7 +7471,7 @@
     <row r="705">
       <c r="A705" s="1" t="inlineStr">
         <is>
-          <t>WEC</t>
+          <t>LEG</t>
         </is>
       </c>
       <c r="B705" t="n">
@@ -7481,7 +7481,7 @@
     <row r="706">
       <c r="A706" s="1" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>LEN</t>
         </is>
       </c>
       <c r="B706" t="n">
@@ -7491,7 +7491,7 @@
     <row r="707">
       <c r="A707" s="1" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>LIFE</t>
         </is>
       </c>
       <c r="B707" t="n">
@@ -7501,7 +7501,7 @@
     <row r="708">
       <c r="A708" s="1" t="inlineStr">
         <is>
-          <t>ALGN</t>
+          <t>KMI</t>
         </is>
       </c>
       <c r="B708" t="n">
@@ -7511,7 +7511,7 @@
     <row r="709">
       <c r="A709" s="1" t="inlineStr">
         <is>
-          <t>ALB</t>
+          <t>HCP</t>
         </is>
       </c>
       <c r="B709" t="n">
@@ -7521,7 +7521,7 @@
     <row r="710">
       <c r="A710" s="1" t="inlineStr">
         <is>
-          <t>AKAM</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B710" t="n">
@@ -7531,7 +7531,7 @@
     <row r="711">
       <c r="A711" s="1" t="inlineStr">
         <is>
-          <t>AJG</t>
+          <t>HBI</t>
         </is>
       </c>
       <c r="B711" t="n">
@@ -7541,7 +7541,7 @@
     <row r="712">
       <c r="A712" s="1" t="inlineStr">
         <is>
-          <t>AIZ</t>
+          <t>ETSY</t>
         </is>
       </c>
       <c r="B712" t="n">
@@ -7551,7 +7551,7 @@
     <row r="713">
       <c r="A713" s="1" t="inlineStr">
         <is>
-          <t>AIV</t>
+          <t>EVHC</t>
         </is>
       </c>
       <c r="B713" t="n">
@@ -7561,7 +7561,7 @@
     <row r="714">
       <c r="A714" s="1" t="inlineStr">
         <is>
-          <t>AIG</t>
+          <t>EVRG</t>
         </is>
       </c>
       <c r="B714" t="n">
@@ -7571,7 +7571,7 @@
     <row r="715">
       <c r="A715" s="1" t="inlineStr">
         <is>
-          <t>AGN</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="B715" t="n">
@@ -7581,7 +7581,7 @@
     <row r="716">
       <c r="A716" s="1" t="inlineStr">
         <is>
-          <t>AFL</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="B716" t="n">
@@ -7591,7 +7591,7 @@
     <row r="717">
       <c r="A717" s="1" t="inlineStr">
         <is>
-          <t>AET</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="B717" t="n">
@@ -7601,7 +7601,7 @@
     <row r="718">
       <c r="A718" s="1" t="inlineStr">
         <is>
-          <t>AES</t>
+          <t>EXPE</t>
         </is>
       </c>
       <c r="B718" t="n">
@@ -7611,7 +7611,7 @@
     <row r="719">
       <c r="A719" s="1" t="inlineStr">
         <is>
-          <t>AEP</t>
+          <t>ETR</t>
         </is>
       </c>
       <c r="B719" t="n">
@@ -7621,7 +7621,7 @@
     <row r="720">
       <c r="A720" s="1" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>EXR</t>
         </is>
       </c>
       <c r="B720" t="n">
@@ -7631,7 +7631,7 @@
     <row r="721">
       <c r="A721" s="1" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>FANG</t>
         </is>
       </c>
       <c r="B721" t="n">
@@ -7641,10 +7641,690 @@
     <row r="722">
       <c r="A722" s="1" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>FAST</t>
         </is>
       </c>
       <c r="B722" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" s="1" t="inlineStr">
+        <is>
+          <t>FBHS</t>
+        </is>
+      </c>
+      <c r="B723" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" s="1" t="inlineStr">
+        <is>
+          <t>FCPT</t>
+        </is>
+      </c>
+      <c r="B724" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" s="1" t="inlineStr">
+        <is>
+          <t>FCX</t>
+        </is>
+      </c>
+      <c r="B725" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" s="1" t="inlineStr">
+        <is>
+          <t>FDO</t>
+        </is>
+      </c>
+      <c r="B726" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" s="1" t="inlineStr">
+        <is>
+          <t>FDS</t>
+        </is>
+      </c>
+      <c r="B727" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B728" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" s="1" t="inlineStr">
+        <is>
+          <t>FDX</t>
+        </is>
+      </c>
+      <c r="B729" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" s="1" t="inlineStr">
+        <is>
+          <t>ESS</t>
+        </is>
+      </c>
+      <c r="B730" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" s="1" t="inlineStr">
+        <is>
+          <t>EQT</t>
+        </is>
+      </c>
+      <c r="B731" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" s="1" t="inlineStr">
+        <is>
+          <t>DXCM</t>
+        </is>
+      </c>
+      <c r="B732" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" s="1" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="B733" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" s="1" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="B734" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" s="1" t="inlineStr">
+        <is>
+          <t>ECL</t>
+        </is>
+      </c>
+      <c r="B735" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" s="1" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="B736" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" s="1" t="inlineStr">
+        <is>
+          <t>EIX</t>
+        </is>
+      </c>
+      <c r="B737" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" s="1" t="inlineStr">
+        <is>
+          <t>EKDKQ</t>
+        </is>
+      </c>
+      <c r="B738" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" s="1" t="inlineStr">
+        <is>
+          <t>ERIE</t>
+        </is>
+      </c>
+      <c r="B739" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" s="1" t="inlineStr">
+        <is>
+          <t>ELV</t>
+        </is>
+      </c>
+      <c r="B740" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" s="1" t="inlineStr">
+        <is>
+          <t>ENDP</t>
+        </is>
+      </c>
+      <c r="B741" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" s="1" t="inlineStr">
+        <is>
+          <t>ENPH</t>
+        </is>
+      </c>
+      <c r="B742" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" s="1" t="inlineStr">
+        <is>
+          <t>EOG</t>
+        </is>
+      </c>
+      <c r="B743" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" s="1" t="inlineStr">
+        <is>
+          <t>EP</t>
+        </is>
+      </c>
+      <c r="B744" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" s="1" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="B745" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" s="1" t="inlineStr">
+        <is>
+          <t>EQIX</t>
+        </is>
+      </c>
+      <c r="B746" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" s="1" t="inlineStr">
+        <is>
+          <t>EQR</t>
+        </is>
+      </c>
+      <c r="B747" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" s="1" t="inlineStr">
+        <is>
+          <t>EMC</t>
+        </is>
+      </c>
+      <c r="B748" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" s="1" t="inlineStr">
+        <is>
+          <t>FE</t>
+        </is>
+      </c>
+      <c r="B749" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" s="1" t="inlineStr">
+        <is>
+          <t>FFIV</t>
+        </is>
+      </c>
+      <c r="B750" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" s="1" t="inlineStr">
+        <is>
+          <t>FHN</t>
+        </is>
+      </c>
+      <c r="B751" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" s="1" t="inlineStr">
+        <is>
+          <t>GHC</t>
+        </is>
+      </c>
+      <c r="B752" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" s="1" t="inlineStr">
+        <is>
+          <t>GILD</t>
+        </is>
+      </c>
+      <c r="B753" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" s="1" t="inlineStr">
+        <is>
+          <t>GME</t>
+        </is>
+      </c>
+      <c r="B754" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" s="1" t="inlineStr">
+        <is>
+          <t>GNRC</t>
+        </is>
+      </c>
+      <c r="B755" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" s="1" t="inlineStr">
+        <is>
+          <t>GNW</t>
+        </is>
+      </c>
+      <c r="B756" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" s="1" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="B757" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" s="1" t="inlineStr">
+        <is>
+          <t>GPC</t>
+        </is>
+      </c>
+      <c r="B758" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" s="1" t="inlineStr">
+        <is>
+          <t>GGP</t>
+        </is>
+      </c>
+      <c r="B759" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" s="1" t="inlineStr">
+        <is>
+          <t>GPN</t>
+        </is>
+      </c>
+      <c r="B760" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" s="1" t="inlineStr">
+        <is>
+          <t>GR</t>
+        </is>
+      </c>
+      <c r="B761" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" s="1" t="inlineStr">
+        <is>
+          <t>GRMN</t>
+        </is>
+      </c>
+      <c r="B762" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" s="1" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="B763" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" s="1" t="inlineStr">
+        <is>
+          <t>GWW</t>
+        </is>
+      </c>
+      <c r="B764" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" s="1" t="inlineStr">
+        <is>
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="B765" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" s="1" t="inlineStr">
+        <is>
+          <t>HAS</t>
+        </is>
+      </c>
+      <c r="B766" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" s="1" t="inlineStr">
+        <is>
+          <t>HBAN</t>
+        </is>
+      </c>
+      <c r="B767" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" s="1" t="inlineStr">
+        <is>
+          <t>GPS</t>
+        </is>
+      </c>
+      <c r="B768" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" s="1" t="inlineStr">
+        <is>
+          <t>GEV</t>
+        </is>
+      </c>
+      <c r="B769" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" s="1" t="inlineStr">
+        <is>
+          <t>GEHC</t>
+        </is>
+      </c>
+      <c r="B770" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" s="1" t="inlineStr">
+        <is>
+          <t>GE</t>
+        </is>
+      </c>
+      <c r="B771" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" s="1" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="B772" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" s="1" t="inlineStr">
+        <is>
+          <t>FICO</t>
+        </is>
+      </c>
+      <c r="B773" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" s="1" t="inlineStr">
+        <is>
+          <t>FII</t>
+        </is>
+      </c>
+      <c r="B774" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" s="1" t="inlineStr">
+        <is>
+          <t>FIS</t>
+        </is>
+      </c>
+      <c r="B775" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" s="1" t="inlineStr">
+        <is>
+          <t>FITB</t>
+        </is>
+      </c>
+      <c r="B776" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" s="1" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="B777" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" s="1" t="inlineStr">
+        <is>
+          <t>FLT</t>
+        </is>
+      </c>
+      <c r="B778" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" s="1" t="inlineStr">
+        <is>
+          <t>FMC</t>
+        </is>
+      </c>
+      <c r="B779" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" s="1" t="inlineStr">
+        <is>
+          <t>FOSL</t>
+        </is>
+      </c>
+      <c r="B780" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" s="1" t="inlineStr">
+        <is>
+          <t>FOX</t>
+        </is>
+      </c>
+      <c r="B781" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" s="1" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="B782" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" s="1" t="inlineStr">
+        <is>
+          <t>FRC</t>
+        </is>
+      </c>
+      <c r="B783" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" s="1" t="inlineStr">
+        <is>
+          <t>FRT</t>
+        </is>
+      </c>
+      <c r="B784" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" s="1" t="inlineStr">
+        <is>
+          <t>FRX</t>
+        </is>
+      </c>
+      <c r="B785" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" s="1" t="inlineStr">
+        <is>
+          <t>FSLR</t>
+        </is>
+      </c>
+      <c r="B786" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" s="1" t="inlineStr">
+        <is>
+          <t>FTNT</t>
+        </is>
+      </c>
+      <c r="B787" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" s="1" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="B788" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" s="1" t="inlineStr">
+        <is>
+          <t>MHK</t>
+        </is>
+      </c>
+      <c r="B789" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" s="1" t="inlineStr">
+        <is>
+          <t>ZTS</t>
+        </is>
+      </c>
+      <c r="B790" t="n">
         <v>1</v>
       </c>
     </row>

--- a/data/ticker_availability.xlsx
+++ b/data/ticker_availability.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B790"/>
+  <dimension ref="A1:B812"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>HFC</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -451,7 +451,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>BTI</t>
+          <t>BTUUQ</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -461,7 +461,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>PCP</t>
+          <t>WFM</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -471,7 +471,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>DISCK</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -481,7 +481,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>LSI</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -491,7 +491,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>SWN</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -501,7 +501,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>GIS</t>
+          <t>WRK</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -511,7 +511,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -521,7 +521,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>CARR</t>
+          <t>BEAM</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -531,7 +531,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>JCP</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -541,7 +541,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>NLSN</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -551,7 +551,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>CBOE</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -561,7 +561,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>VAR</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -571,7 +571,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>CCE</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -581,7 +581,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>GDDY</t>
+          <t>RDC</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -591,7 +591,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>TIF</t>
+          <t>PTV</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -601,7 +601,7 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>GAS</t>
+          <t>JEC</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -611,7 +611,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>FTV</t>
+          <t>ADS</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -621,7 +621,7 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>BSX</t>
+          <t>TSS</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -631,7 +631,7 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>TGT</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -641,7 +641,7 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>MYL</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -651,7 +651,7 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>PCL</t>
+          <t>SIAL</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -661,7 +661,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>BDK</t>
+          <t>DRE</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -671,7 +671,7 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>NXPI</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -681,7 +681,7 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>NYX</t>
+          <t>WYND</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -691,7 +691,7 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>FRC</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -701,7 +701,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>HOG</t>
+          <t>CBS</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -711,7 +711,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>ULTA</t>
+          <t>LXK</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -721,7 +721,7 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>BIG</t>
+          <t>CELG</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -731,7 +731,7 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>HLT</t>
+          <t>MDP</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -741,7 +741,7 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>HII</t>
+          <t>MHS</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -751,7 +751,7 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>OTIS</t>
+          <t>CDAY</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -761,7 +761,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>JNS</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -771,7 +771,7 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>PBCT</t>
+          <t>FLT</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -781,7 +781,7 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>PBG</t>
+          <t>PETM</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -791,7 +791,7 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>BMC</t>
+          <t>BBT</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -801,7 +801,7 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>PBI</t>
+          <t>EKDKQ</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -811,7 +811,7 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>PCAR</t>
+          <t>POM</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -821,7 +821,7 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>PCG</t>
+          <t>HSP</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -831,7 +831,7 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>LLL</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -841,7 +841,7 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>FTR</t>
+          <t>NOVL</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -851,7 +851,7 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>FTI</t>
+          <t>TIF</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -861,7 +861,7 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>PKI</t>
+          <t>LLTC</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -871,7 +871,7 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -881,7 +881,7 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>RHT</t>
+          <t>BRCM</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -891,7 +891,7 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>CPWR</t>
+          <t>MWV</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -901,7 +901,7 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>RIG</t>
+          <t>FRX</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -911,7 +911,7 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>STLD</t>
+          <t>KSU</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -921,7 +921,7 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>CMCSK</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -931,7 +931,7 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>SBAC</t>
+          <t>HCP</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -941,7 +941,7 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>DPZ</t>
+          <t>VIAB</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -951,7 +951,7 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>SHLD</t>
+          <t>TEG</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -961,7 +961,7 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>CTXS</t>
+          <t>LVLT</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -971,7 +971,7 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>CVC</t>
+          <t>PCP</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -981,7 +981,7 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>DNB</t>
+          <t>FLIR</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -991,7 +991,7 @@
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>DLTR</t>
+          <t>COG</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -1001,7 +1001,7 @@
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>CZR</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -1011,7 +1011,7 @@
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>DISCA</t>
+          <t>SPLS</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -1021,7 +1021,7 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>BXLT</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -1031,7 +1031,7 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>DAY</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -1041,7 +1041,7 @@
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>ESRX</t>
+          <t>GENZ</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -1051,7 +1051,7 @@
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>GPS</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -1061,7 +1061,7 @@
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>COTY</t>
+          <t>CFN</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -1071,7 +1071,7 @@
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>ESV</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -1081,7 +1081,7 @@
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>CFN</t>
+          <t>STR</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -1091,7 +1091,7 @@
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>TEG</t>
+          <t>WPX</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -1101,7 +1101,7 @@
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>TECH</t>
+          <t>DTV</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -1111,7 +1111,7 @@
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>DNR</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -1121,7 +1121,7 @@
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>FLIR</t>
+          <t>ATVI</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -1131,7 +1131,7 @@
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>POM</t>
+          <t>CXO</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -1141,7 +1141,7 @@
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>CLX</t>
+          <t>NLOK</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -1151,7 +1151,7 @@
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>CMA</t>
+          <t>UTX</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -1161,7 +1161,7 @@
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>NWS</t>
+          <t>PDCO</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -1171,7 +1171,7 @@
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>PSA</t>
+          <t>JAVA</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -1181,7 +1181,7 @@
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>SYY</t>
+          <t>ABMD</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -1191,7 +1191,7 @@
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>CMI</t>
+          <t>CAM</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -1201,7 +1201,7 @@
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>CMS</t>
+          <t>CVC</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -1211,7 +1211,7 @@
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>TMK</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -1221,7 +1221,7 @@
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>PTV</t>
+          <t>DFS</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -1231,7 +1231,7 @@
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>SWKS</t>
+          <t>BHGE</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -1241,7 +1241,7 @@
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>ETFC</t>
+          <t>DISCA</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -1251,7 +1251,7 @@
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>PBCT</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -1261,7 +1261,7 @@
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>AVP</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -1271,7 +1271,7 @@
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>HUM</t>
+          <t>MMI</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -1281,7 +1281,7 @@
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>HAR</t>
+          <t>RRD</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -1291,7 +1291,7 @@
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>SJM</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -1301,7 +1301,7 @@
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>MAS</t>
+          <t>KORS</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -1311,7 +1311,7 @@
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>XLNX</t>
+          <t>LO</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -1321,7 +1321,7 @@
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>AGN</t>
+          <t>LIFE</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -1331,7 +1331,7 @@
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>ANF</t>
+          <t>NBL</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -1341,7 +1341,7 @@
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>FTR</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -1351,7 +1351,7 @@
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>RTN</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -1361,7 +1361,7 @@
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>VIAC</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -1371,7 +1371,7 @@
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>KRFT</t>
+          <t>BCR</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -1381,7 +1381,7 @@
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>KSS</t>
+          <t>XEC</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -1391,7 +1391,7 @@
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>WHR</t>
+          <t>AKS</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -1401,7 +1401,7 @@
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>KSU</t>
+          <t>NSM</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -1411,7 +1411,7 @@
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>MAC</t>
+          <t>FDO</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -1421,7 +1421,7 @@
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>DISH</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -1431,7 +1431,7 @@
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>HWM</t>
+          <t>MNK</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -1441,7 +1441,7 @@
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>AMCR</t>
+          <t>TWC</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -1451,7 +1451,7 @@
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>PGN</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -1461,7 +1461,7 @@
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>PLL</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -1471,7 +1471,7 @@
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>LYV</t>
+          <t>GGP</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -1481,7 +1481,7 @@
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>RX</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -1491,7 +1491,7 @@
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>AIG</t>
+          <t>STI</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -1501,7 +1501,7 @@
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>LSI</t>
+          <t>JWN</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -1511,7 +1511,7 @@
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>MPWR</t>
+          <t>BBBY</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -1521,7 +1521,7 @@
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>INFO</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -1531,7 +1531,7 @@
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>MTD</t>
+          <t>LM</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -1541,7 +1541,7 @@
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>TWTR</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -1551,7 +1551,7 @@
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>LH</t>
+          <t>PEAK</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -1561,7 +1561,7 @@
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>CHK</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -1571,7 +1571,7 @@
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>ALGN</t>
+          <t>CPGX</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -1581,7 +1581,7 @@
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>MTB</t>
+          <t>MJN</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -1591,7 +1591,7 @@
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>MWW</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -1601,7 +1601,7 @@
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>WLTW</t>
+          <t>MON</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -1611,7 +1611,7 @@
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>LHX</t>
+          <t>HRS</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -1621,7 +1621,7 @@
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>AOS</t>
+          <t>GMCR</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -1631,7 +1631,7 @@
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>KORS</t>
+          <t>DNB</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -1641,7 +1641,7 @@
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>MCO</t>
+          <t>PKI</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -1651,7 +1651,7 @@
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>SIVB</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -1661,7 +1661,7 @@
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>KRFT</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -1671,7 +1671,7 @@
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>AVY</t>
+          <t>WLTW</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -1681,7 +1681,7 @@
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>MLM</t>
+          <t>NVLS</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -1691,7 +1691,7 @@
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>AWK</t>
+          <t>XLNX</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -1701,7 +1701,7 @@
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>AXON</t>
+          <t>ETFC</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -1711,7 +1711,7 @@
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>IRM</t>
+          <t>PX</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -1721,7 +1721,7 @@
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>ANTM</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -1731,7 +1731,7 @@
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>AYE</t>
+          <t>PXD</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -1741,7 +1741,7 @@
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>IPGP</t>
+          <t>ARNC</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -1751,7 +1751,7 @@
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>YUM</t>
+          <t>DWDP</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -1761,7 +1761,7 @@
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>ZBH</t>
+          <t>RAI</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -1771,7 +1771,7 @@
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>ARG</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -1781,7 +1781,7 @@
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>MJN</t>
+          <t>ALTR</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -1791,7 +1791,7 @@
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>IDXX</t>
+          <t>QLGC</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -1801,7 +1801,7 @@
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -1811,7 +1811,7 @@
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>HCBK</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -1821,7 +1821,7 @@
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>PCL</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -1831,7 +1831,7 @@
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>MOH</t>
+          <t>SRCL</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -1841,7 +1841,7 @@
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>VTR</t>
+          <t>NYX</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -1851,7 +1851,7 @@
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>APOL</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -1861,7 +1861,7 @@
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>ATVI</t>
+          <t>MXIM</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -1871,7 +1871,7 @@
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>RSHCQ</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -1881,7 +1881,7 @@
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>MAT</t>
+          <t>XTO</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -1891,7 +1891,7 @@
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>ANRZQ</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -1901,7 +1901,7 @@
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>ITT</t>
+          <t>SBNY</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -1911,7 +1911,7 @@
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>BJS</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -1921,7 +1921,7 @@
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>NOV</t>
+          <t>MRO</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -1931,7 +1931,7 @@
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>AVB</t>
+          <t>BLL</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -1941,987 +1941,987 @@
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>DISCK</t>
+          <t>SYMC</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.0005170630816959669</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>CPB</t>
+          <t>CCE</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.002119766825649179</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>GMCR</t>
+          <t>CEPH</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.004073319755600814</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.0151033386327504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>SUNEQ</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.01828298887122417</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>0.03418124006359301</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>STX</t>
+          <t>SHLD</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0.06168521462639109</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>EFX</t>
+          <t>JOY</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0.06942236354001059</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>PLL</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>0.07508771929824562</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>WCG</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0.08664546899841018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>TIE</t>
+          <t>AGN</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>0.08666666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>SWY</t>
+          <t>FII</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>0.09725490196078432</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>GENZ</t>
+          <t>CTLT</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>0.1139240506329114</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>CPRI</t>
+          <t>EMC</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>0.1257976298997265</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>VRSK</t>
+          <t>QEP</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>0.134739560912613</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>NDAQ</t>
+          <t>CTL</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>0.1359300476947536</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>BIG</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>0.144287193648602</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>BCR</t>
+          <t>SWY</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>0.1549925484351714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>CAG</t>
+          <t>CERN</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>0.1584525702172761</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t>TEL</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0.1613000300932892</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>CTXS</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>0.1777954425013248</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
         <is>
-          <t>IR</t>
+          <t>RHT</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>0.2088376020264565</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
         <is>
-          <t>RMD</t>
+          <t>ESV</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>0.2089791555318012</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>SNI</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>0.2310545839957605</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>ENDP</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>0.262586115527292</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="inlineStr">
         <is>
-          <t>HNZ</t>
+          <t>FBHS</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>0.2827346465816918</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="inlineStr">
         <is>
-          <t>AEE</t>
+          <t>BNI</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>0.2835188129305776</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>0.2845786963434022</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="inlineStr">
         <is>
-          <t>VIAC</t>
+          <t>CVH</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>0.2913669064748202</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>MFE</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>0.3002119766825649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="inlineStr">
         <is>
-          <t>HIG</t>
+          <t>STJ</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>0.3192898781134075</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>AABA</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>0.3244170096021948</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>APC</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>0.3269740328563858</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>0.3307839388145316</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>HSH</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>0.3317435082140964</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="inlineStr">
         <is>
-          <t>BBT</t>
+          <t>ALXN</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>0.3334666133546582</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="inlineStr">
         <is>
-          <t>HPE</t>
+          <t>SUN</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>0.3365134431916739</v>
+        <v>0.01721664275466284</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="inlineStr">
         <is>
-          <t>DHI</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>0.3441971383147854</v>
+        <v>0.06776379477250725</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="inlineStr">
         <is>
-          <t>PETM</t>
+          <t>HOT</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>0.3721311475409836</v>
+        <v>0.2249114521841795</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="inlineStr">
         <is>
-          <t>WAT</t>
+          <t>BMC</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>0.3738738738738739</v>
+        <v>0.333692142088267</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="inlineStr">
         <is>
-          <t>WM</t>
+          <t>SCG</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>0.3765235824059354</v>
+        <v>0.3849889624724062</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
         <is>
-          <t>AME</t>
+          <t>FOXA</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>0.3805496828752643</v>
+        <v>0.3876523582405935</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>DOW</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>0.3860625331213566</v>
+        <v>0.4285291506362829</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>IR</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>0.3892421833598304</v>
+        <v>0.5409513087531663</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
         <is>
-          <t>AAL</t>
+          <t>CEG</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>0.3974091099038863</v>
+        <v>0.5696498054474708</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>HAR</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>0.3977212506624271</v>
+        <v>0.5773480662983426</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>GAS</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>0.3990447242726878</v>
+        <v>0.621638141809291</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
         <is>
-          <t>SHW</t>
+          <t>FOX</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>0.4043455219925808</v>
+        <v>0.6258561643835616</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>COV</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>0.4666136724960254</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
         <is>
-          <t>AET</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>0.4701426024955437</v>
+        <v>0.6953612845673506</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>SII</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>0.4795972443031267</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>ACS</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>0.4976152623211447</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>BDK</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>0.505299417064123</v>
+        <v>0.8775510204081632</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>MEE</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>0.5092739798622151</v>
+        <v>0.8851540616246498</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="inlineStr">
         <is>
-          <t>ETN</t>
+          <t>AYE</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>0.5442501324854266</v>
+        <v>0.9278350515463918</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>0.5521766965428937</v>
+        <v>0.9614197530864198</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="inlineStr">
         <is>
-          <t>TAP</t>
+          <t>TIE</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>0.5635930047694754</v>
+        <v>0.9746666666666667</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="inlineStr">
         <is>
-          <t>HON</t>
+          <t>CBE</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>0.566507684154743</v>
+        <v>0.980544747081712</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="1" t="inlineStr">
         <is>
-          <t>CEG</t>
+          <t>VLTO</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>0.5696498054474708</v>
+        <v>0.9936507936507937</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="inlineStr">
         <is>
-          <t>AEP</t>
+          <t>EVHC</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>0.5731319554848967</v>
+        <v>0.9957264957264957</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="inlineStr">
         <is>
-          <t>ROP</t>
+          <t>CSRA</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>0.5832008479067302</v>
+        <v>0.9983050847457627</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="inlineStr">
         <is>
-          <t>VNO</t>
+          <t>NFX</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>0.5956017104459377</v>
+        <v>0.9985387238188017</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>TWX</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>0.5983041865394807</v>
+        <v>0.9995300751879699</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="inlineStr">
         <is>
-          <t>EMN</t>
+          <t>ANDV</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>0.6054583995760466</v>
+        <v>0.9995458673932789</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="inlineStr">
         <is>
-          <t>CSX</t>
+          <t>ESRX</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>0.6065182829888712</v>
+        <v>0.9995573262505534</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="inlineStr">
         <is>
-          <t>PNW</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>0.6094329623741388</v>
+        <v>1</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="inlineStr">
         <is>
-          <t>TJX</t>
+          <t>GHC</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>0.6197668256491786</v>
+        <v>1</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>0.631376323387873</v>
+        <v>1</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>0.6332803391626921</v>
+        <v>1</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="inlineStr">
         <is>
-          <t>CDNS</t>
+          <t>VFC</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>0.6390403489640131</v>
+        <v>1</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>0.6515633280339163</v>
+        <v>1</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="inlineStr">
         <is>
-          <t>AMG</t>
+          <t>CPRT</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>0.6545981173062998</v>
+        <v>1</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="inlineStr">
         <is>
-          <t>HOLX</t>
+          <t>CMA</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>0.6634920634920635</v>
+        <v>1</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="inlineStr">
         <is>
-          <t>CAH</t>
+          <t>HST</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="inlineStr">
         <is>
-          <t>LKQ</t>
+          <t>ORLY</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>0.6746654360867559</v>
+        <v>1</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="inlineStr">
         <is>
-          <t>AXP</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>0.6801801801801802</v>
+        <v>1</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="inlineStr">
         <is>
-          <t>IPG</t>
+          <t>CBOE</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>0.6854795972443031</v>
+        <v>1</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="inlineStr">
         <is>
-          <t>SCG</t>
+          <t>HSY</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>0.7108167770419426</v>
+        <v>1</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="inlineStr">
         <is>
-          <t>WEC</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>0.7368839427662957</v>
+        <v>1</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="inlineStr">
         <is>
-          <t>FLR</t>
+          <t>CVS</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>0.7387083157450401</v>
+        <v>1</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>ULTA</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>0.7413884472708002</v>
+        <v>1</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="inlineStr">
         <is>
-          <t>MSI</t>
+          <t>ESS</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>0.7678855325914149</v>
+        <v>1</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="inlineStr">
         <is>
-          <t>MET</t>
+          <t>CMCSA</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>0.7694753577106518</v>
+        <v>1</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="inlineStr">
         <is>
-          <t>SPG</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>0.7694753577106518</v>
+        <v>1</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="inlineStr">
         <is>
-          <t>LXK</t>
+          <t>WBD</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>0.784992784992785</v>
+        <v>1</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>0.7946475887652358</v>
+        <v>1</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="inlineStr">
         <is>
-          <t>KIM</t>
+          <t>LUMN</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>0.8420773714891362</v>
+        <v>1</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="inlineStr">
         <is>
-          <t>SNA</t>
+          <t>ETSY</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>0.8481717011128775</v>
+        <v>1</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="inlineStr">
         <is>
-          <t>SNI</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B240" t="n">
-        <v>0.8551992225461613</v>
+        <v>1</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="inlineStr">
         <is>
-          <t>TGNA</t>
+          <t>AMT</t>
         </is>
       </c>
       <c r="B241" t="n">
-        <v>0.8580610605249063</v>
+        <v>1</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="inlineStr">
         <is>
-          <t>AZO</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>0.859830418653948</v>
+        <v>1</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="inlineStr">
         <is>
-          <t>LM</t>
+          <t>KDP</t>
         </is>
       </c>
       <c r="B243" t="n">
-        <v>0.8657487091222031</v>
+        <v>1</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>NWS</t>
         </is>
       </c>
       <c r="B244" t="n">
-        <v>0.870291702067403</v>
+        <v>1</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="inlineStr">
         <is>
-          <t>CMCSA</t>
+          <t>TJX</t>
         </is>
       </c>
       <c r="B245" t="n">
-        <v>0.9364069952305246</v>
+        <v>1</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="1" t="inlineStr">
         <is>
-          <t>NTAP</t>
+          <t>BF-B</t>
         </is>
       </c>
       <c r="B246" t="n">
-        <v>0.9703232644409115</v>
+        <v>1</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="1" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>BAX</t>
         </is>
       </c>
       <c r="B247" t="n">
-        <v>0.9894011658717541</v>
+        <v>1</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="1" t="inlineStr">
         <is>
-          <t>FLS</t>
+          <t>NTRS</t>
         </is>
       </c>
       <c r="B248" t="n">
-        <v>0.9904357066950054</v>
+        <v>1</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="1" t="inlineStr">
         <is>
-          <t>LDOS</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B249" t="n">
-        <v>0.9995642701525055</v>
+        <v>1</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="1" t="inlineStr">
         <is>
-          <t>VLTO</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="B250" t="n">
@@ -2931,7 +2931,7 @@
     <row r="251">
       <c r="A251" s="1" t="inlineStr">
         <is>
-          <t>NFX</t>
+          <t>KIM</t>
         </is>
       </c>
       <c r="B251" t="n">
@@ -2941,7 +2941,7 @@
     <row r="252">
       <c r="A252" s="1" t="inlineStr">
         <is>
-          <t>NOVL</t>
+          <t>NDAQ</t>
         </is>
       </c>
       <c r="B252" t="n">
@@ -2951,7 +2951,7 @@
     <row r="253">
       <c r="A253" s="1" t="inlineStr">
         <is>
-          <t>VRTX</t>
+          <t>DPZ</t>
         </is>
       </c>
       <c r="B253" t="n">
@@ -2961,7 +2961,7 @@
     <row r="254">
       <c r="A254" s="1" t="inlineStr">
         <is>
-          <t>NKTR</t>
+          <t>URBN</t>
         </is>
       </c>
       <c r="B254" t="n">
@@ -2971,7 +2971,7 @@
     <row r="255">
       <c r="A255" s="1" t="inlineStr">
         <is>
-          <t>NLOK</t>
+          <t>HPQ</t>
         </is>
       </c>
       <c r="B255" t="n">
@@ -2981,7 +2981,7 @@
     <row r="256">
       <c r="A256" s="1" t="inlineStr">
         <is>
-          <t>NLSN</t>
+          <t>LH</t>
         </is>
       </c>
       <c r="B256" t="n">
@@ -2991,7 +2991,7 @@
     <row r="257">
       <c r="A257" s="1" t="inlineStr">
         <is>
-          <t>VRSN</t>
+          <t>MPC</t>
         </is>
       </c>
       <c r="B257" t="n">
@@ -3001,7 +3001,7 @@
     <row r="258">
       <c r="A258" s="1" t="inlineStr">
         <is>
-          <t>VNT</t>
+          <t>AYI</t>
         </is>
       </c>
       <c r="B258" t="n">
@@ -3011,7 +3011,7 @@
     <row r="259">
       <c r="A259" s="1" t="inlineStr">
         <is>
-          <t>VMC</t>
+          <t>GPN</t>
         </is>
       </c>
       <c r="B259" t="n">
@@ -3021,7 +3021,7 @@
     <row r="260">
       <c r="A260" s="1" t="inlineStr">
         <is>
-          <t>NI</t>
+          <t>RHI</t>
         </is>
       </c>
       <c r="B260" t="n">
@@ -3031,7 +3031,7 @@
     <row r="261">
       <c r="A261" s="1" t="inlineStr">
         <is>
-          <t>ODP</t>
+          <t>AEP</t>
         </is>
       </c>
       <c r="B261" t="n">
@@ -3041,7 +3041,7 @@
     <row r="262">
       <c r="A262" s="1" t="inlineStr">
         <is>
-          <t>NRG</t>
+          <t>STE</t>
         </is>
       </c>
       <c r="B262" t="n">
@@ -3051,7 +3051,7 @@
     <row r="263">
       <c r="A263" s="1" t="inlineStr">
         <is>
-          <t>NOW</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B263" t="n">
@@ -3061,7 +3061,7 @@
     <row r="264">
       <c r="A264" s="1" t="inlineStr">
         <is>
-          <t>ODFL</t>
+          <t>IVZ</t>
         </is>
       </c>
       <c r="B264" t="n">
@@ -3071,7 +3071,7 @@
     <row r="265">
       <c r="A265" s="1" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>BMS</t>
         </is>
       </c>
       <c r="B265" t="n">
@@ -3081,7 +3081,7 @@
     <row r="266">
       <c r="A266" s="1" t="inlineStr">
         <is>
-          <t>URBN</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B266" t="n">
@@ -3091,7 +3091,7 @@
     <row r="267">
       <c r="A267" s="1" t="inlineStr">
         <is>
-          <t>NYT</t>
+          <t>LNC</t>
         </is>
       </c>
       <c r="B267" t="n">
@@ -3101,7 +3101,7 @@
     <row r="268">
       <c r="A268" s="1" t="inlineStr">
         <is>
-          <t>URI</t>
+          <t>AON</t>
         </is>
       </c>
       <c r="B268" t="n">
@@ -3111,7 +3111,7 @@
     <row r="269">
       <c r="A269" s="1" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="B269" t="n">
@@ -3121,7 +3121,7 @@
     <row r="270">
       <c r="A270" s="1" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>BDX</t>
         </is>
       </c>
       <c r="B270" t="n">
@@ -3131,7 +3131,7 @@
     <row r="271">
       <c r="A271" s="1" t="inlineStr">
         <is>
-          <t>UTX</t>
+          <t>HWM</t>
         </is>
       </c>
       <c r="B271" t="n">
@@ -3141,7 +3141,7 @@
     <row r="272">
       <c r="A272" s="1" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>MUR</t>
         </is>
       </c>
       <c r="B272" t="n">
@@ -3151,7 +3151,7 @@
     <row r="273">
       <c r="A273" s="1" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B273" t="n">
@@ -3161,7 +3161,7 @@
     <row r="274">
       <c r="A274" s="1" t="inlineStr">
         <is>
-          <t>VAR</t>
+          <t>JNPR</t>
         </is>
       </c>
       <c r="B274" t="n">
@@ -3171,7 +3171,7 @@
     <row r="275">
       <c r="A275" s="1" t="inlineStr">
         <is>
-          <t>VICI</t>
+          <t>HII</t>
         </is>
       </c>
       <c r="B275" t="n">
@@ -3181,7 +3181,7 @@
     <row r="276">
       <c r="A276" s="1" t="inlineStr">
         <is>
-          <t>NWL</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B276" t="n">
@@ -3191,7 +3191,7 @@
     <row r="277">
       <c r="A277" s="1" t="inlineStr">
         <is>
-          <t>NVR</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="B277" t="n">
@@ -3201,7 +3201,7 @@
     <row r="278">
       <c r="A278" s="1" t="inlineStr">
         <is>
-          <t>NVLS</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="B278" t="n">
@@ -3211,7 +3211,7 @@
     <row r="279">
       <c r="A279" s="1" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>BIO</t>
         </is>
       </c>
       <c r="B279" t="n">
@@ -3221,7 +3221,7 @@
     <row r="280">
       <c r="A280" s="1" t="inlineStr">
         <is>
-          <t>NUE</t>
+          <t>NTAP</t>
         </is>
       </c>
       <c r="B280" t="n">
@@ -3231,7 +3231,7 @@
     <row r="281">
       <c r="A281" s="1" t="inlineStr">
         <is>
-          <t>NTRS</t>
+          <t>SO</t>
         </is>
       </c>
       <c r="B281" t="n">
@@ -3241,7 +3241,7 @@
     <row r="282">
       <c r="A282" s="1" t="inlineStr">
         <is>
-          <t>OI</t>
+          <t>KMI</t>
         </is>
       </c>
       <c r="B282" t="n">
@@ -3251,7 +3251,7 @@
     <row r="283">
       <c r="A283" s="1" t="inlineStr">
         <is>
-          <t>VIAV</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="B283" t="n">
@@ -3261,7 +3261,7 @@
     <row r="284">
       <c r="A284" s="1" t="inlineStr">
         <is>
-          <t>NSM</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="B284" t="n">
@@ -3271,7 +3271,7 @@
     <row r="285">
       <c r="A285" s="1" t="inlineStr">
         <is>
-          <t>OKE</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B285" t="n">
@@ -3281,7 +3281,7 @@
     <row r="286">
       <c r="A286" s="1" t="inlineStr">
         <is>
-          <t>NSC</t>
+          <t>TDY</t>
         </is>
       </c>
       <c r="B286" t="n">
@@ -3291,7 +3291,7 @@
     <row r="287">
       <c r="A287" s="1" t="inlineStr">
         <is>
-          <t>OGN</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B287" t="n">
@@ -3301,7 +3301,7 @@
     <row r="288">
       <c r="A288" s="1" t="inlineStr">
         <is>
-          <t>VFC</t>
+          <t>AIG</t>
         </is>
       </c>
       <c r="B288" t="n">
@@ -3311,7 +3311,7 @@
     <row r="289">
       <c r="A289" s="1" t="inlineStr">
         <is>
-          <t>SLM</t>
+          <t>KVUE</t>
         </is>
       </c>
       <c r="B289" t="n">
@@ -3321,7 +3321,7 @@
     <row r="290">
       <c r="A290" s="1" t="inlineStr">
         <is>
-          <t>NAVI</t>
+          <t>IFF</t>
         </is>
       </c>
       <c r="B290" t="n">
@@ -3331,7 +3331,7 @@
     <row r="291">
       <c r="A291" s="1" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>CPRI</t>
         </is>
       </c>
       <c r="B291" t="n">
@@ -3341,7 +3341,7 @@
     <row r="292">
       <c r="A292" s="1" t="inlineStr">
         <is>
-          <t>MPC</t>
+          <t>URI</t>
         </is>
       </c>
       <c r="B292" t="n">
@@ -3351,7 +3351,7 @@
     <row r="293">
       <c r="A293" s="1" t="inlineStr">
         <is>
-          <t>MOS</t>
+          <t>AWK</t>
         </is>
       </c>
       <c r="B293" t="n">
@@ -3361,7 +3361,7 @@
     <row r="294">
       <c r="A294" s="1" t="inlineStr">
         <is>
-          <t>WU</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B294" t="n">
@@ -3371,7 +3371,7 @@
     <row r="295">
       <c r="A295" s="1" t="inlineStr">
         <is>
-          <t>MOLX</t>
+          <t>RVTY</t>
         </is>
       </c>
       <c r="B295" t="n">
@@ -3381,7 +3381,7 @@
     <row r="296">
       <c r="A296" s="1" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>CZR</t>
         </is>
       </c>
       <c r="B296" t="n">
@@ -3391,7 +3391,7 @@
     <row r="297">
       <c r="A297" s="1" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>SWKS</t>
         </is>
       </c>
       <c r="B297" t="n">
@@ -3401,7 +3401,7 @@
     <row r="298">
       <c r="A298" s="1" t="inlineStr">
         <is>
-          <t>MNST</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B298" t="n">
@@ -3411,7 +3411,7 @@
     <row r="299">
       <c r="A299" s="1" t="inlineStr">
         <is>
-          <t>MNK</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B299" t="n">
@@ -3421,7 +3421,7 @@
     <row r="300">
       <c r="A300" s="1" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="B300" t="n">
@@ -3431,7 +3431,7 @@
     <row r="301">
       <c r="A301" s="1" t="inlineStr">
         <is>
-          <t>WYND</t>
+          <t>ENPH</t>
         </is>
       </c>
       <c r="B301" t="n">
@@ -3441,7 +3441,7 @@
     <row r="302">
       <c r="A302" s="1" t="inlineStr">
         <is>
-          <t>WYNN</t>
+          <t>EXR</t>
         </is>
       </c>
       <c r="B302" t="n">
@@ -3451,7 +3451,7 @@
     <row r="303">
       <c r="A303" s="1" t="inlineStr">
         <is>
-          <t>XEC</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B303" t="n">
@@ -3461,7 +3461,7 @@
     <row r="304">
       <c r="A304" s="1" t="inlineStr">
         <is>
-          <t>XEL</t>
+          <t>FDS</t>
         </is>
       </c>
       <c r="B304" t="n">
@@ -3471,7 +3471,7 @@
     <row r="305">
       <c r="A305" s="1" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>SEDG</t>
         </is>
       </c>
       <c r="B305" t="n">
@@ -3481,7 +3481,7 @@
     <row r="306">
       <c r="A306" s="1" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>HUM</t>
         </is>
       </c>
       <c r="B306" t="n">
@@ -3491,7 +3491,7 @@
     <row r="307">
       <c r="A307" s="1" t="inlineStr">
         <is>
-          <t>XRAY</t>
+          <t>MAC</t>
         </is>
       </c>
       <c r="B307" t="n">
@@ -3501,7 +3501,7 @@
     <row r="308">
       <c r="A308" s="1" t="inlineStr">
         <is>
-          <t>MMI</t>
+          <t>STZ</t>
         </is>
       </c>
       <c r="B308" t="n">
@@ -3511,7 +3511,7 @@
     <row r="309">
       <c r="A309" s="1" t="inlineStr">
         <is>
-          <t>MMC</t>
+          <t>GEHC</t>
         </is>
       </c>
       <c r="B309" t="n">
@@ -3521,7 +3521,7 @@
     <row r="310">
       <c r="A310" s="1" t="inlineStr">
         <is>
-          <t>XRX</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B310" t="n">
@@ -3531,7 +3531,7 @@
     <row r="311">
       <c r="A311" s="1" t="inlineStr">
         <is>
-          <t>XTO</t>
+          <t>PSX</t>
         </is>
       </c>
       <c r="B311" t="n">
@@ -3541,7 +3541,7 @@
     <row r="312">
       <c r="A312" s="1" t="inlineStr">
         <is>
-          <t>XYL</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="B312" t="n">
@@ -3551,7 +3551,7 @@
     <row r="313">
       <c r="A313" s="1" t="inlineStr">
         <is>
-          <t>MKTX</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B313" t="n">
@@ -3561,7 +3561,7 @@
     <row r="314">
       <c r="A314" s="1" t="inlineStr">
         <is>
-          <t>YHOO</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="B314" t="n">
@@ -3571,7 +3571,7 @@
     <row r="315">
       <c r="A315" s="1" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>DHI</t>
         </is>
       </c>
       <c r="B315" t="n">
@@ -3581,7 +3581,7 @@
     <row r="316">
       <c r="A316" s="1" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B316" t="n">
@@ -3591,7 +3591,7 @@
     <row r="317">
       <c r="A317" s="1" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>PCG</t>
         </is>
       </c>
       <c r="B317" t="n">
@@ -3601,7 +3601,7 @@
     <row r="318">
       <c r="A318" s="1" t="inlineStr">
         <is>
-          <t>WST</t>
+          <t>STX</t>
         </is>
       </c>
       <c r="B318" t="n">
@@ -3611,7 +3611,7 @@
     <row r="319">
       <c r="A319" s="1" t="inlineStr">
         <is>
-          <t>WRK</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B319" t="n">
@@ -3621,7 +3621,7 @@
     <row r="320">
       <c r="A320" s="1" t="inlineStr">
         <is>
-          <t>MRO</t>
+          <t>ROP</t>
         </is>
       </c>
       <c r="B320" t="n">
@@ -3631,7 +3631,7 @@
     <row r="321">
       <c r="A321" s="1" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="B321" t="n">
@@ -3641,7 +3641,7 @@
     <row r="322">
       <c r="A322" s="1" t="inlineStr">
         <is>
-          <t>NDSN</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="B322" t="n">
@@ -3651,7 +3651,7 @@
     <row r="323">
       <c r="A323" s="1" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>NOV</t>
         </is>
       </c>
       <c r="B323" t="n">
@@ -3661,7 +3661,7 @@
     <row r="324">
       <c r="A324" s="1" t="inlineStr">
         <is>
-          <t>VTRS</t>
+          <t>UNM</t>
         </is>
       </c>
       <c r="B324" t="n">
@@ -3671,7 +3671,7 @@
     <row r="325">
       <c r="A325" s="1" t="inlineStr">
         <is>
-          <t>NCLH</t>
+          <t>ECL</t>
         </is>
       </c>
       <c r="B325" t="n">
@@ -3681,7 +3681,7 @@
     <row r="326">
       <c r="A326" s="1" t="inlineStr">
         <is>
-          <t>NBR</t>
+          <t>TSCO</t>
         </is>
       </c>
       <c r="B326" t="n">
@@ -3691,7 +3691,7 @@
     <row r="327">
       <c r="A327" s="1" t="inlineStr">
         <is>
-          <t>NBL</t>
+          <t>AES</t>
         </is>
       </c>
       <c r="B327" t="n">
@@ -3701,7 +3701,7 @@
     <row r="328">
       <c r="A328" s="1" t="inlineStr">
         <is>
-          <t>UNM</t>
+          <t>FOSL</t>
         </is>
       </c>
       <c r="B328" t="n">
@@ -3711,7 +3711,7 @@
     <row r="329">
       <c r="A329" s="1" t="inlineStr">
         <is>
-          <t>MYL</t>
+          <t>VRSK</t>
         </is>
       </c>
       <c r="B329" t="n">
@@ -3721,7 +3721,7 @@
     <row r="330">
       <c r="A330" s="1" t="inlineStr">
         <is>
-          <t>MXIM</t>
+          <t>SIG</t>
         </is>
       </c>
       <c r="B330" t="n">
@@ -3731,7 +3731,7 @@
     <row r="331">
       <c r="A331" s="1" t="inlineStr">
         <is>
-          <t>MWW</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B331" t="n">
@@ -3741,7 +3741,7 @@
     <row r="332">
       <c r="A332" s="1" t="inlineStr">
         <is>
-          <t>MWV</t>
+          <t>PENN</t>
         </is>
       </c>
       <c r="B332" t="n">
@@ -3751,7 +3751,7 @@
     <row r="333">
       <c r="A333" s="1" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>HSIC</t>
         </is>
       </c>
       <c r="B333" t="n">
@@ -3761,7 +3761,7 @@
     <row r="334">
       <c r="A334" s="1" t="inlineStr">
         <is>
-          <t>MUR</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="B334" t="n">
@@ -3771,7 +3771,7 @@
     <row r="335">
       <c r="A335" s="1" t="inlineStr">
         <is>
-          <t>WAB</t>
+          <t>BRK-B</t>
         </is>
       </c>
       <c r="B335" t="n">
@@ -3781,7 +3781,7 @@
     <row r="336">
       <c r="A336" s="1" t="inlineStr">
         <is>
-          <t>MTCH</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="B336" t="n">
@@ -3791,7 +3791,7 @@
     <row r="337">
       <c r="A337" s="1" t="inlineStr">
         <is>
-          <t>WBA</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="B337" t="n">
@@ -3801,7 +3801,7 @@
     <row r="338">
       <c r="A338" s="1" t="inlineStr">
         <is>
-          <t>WBD</t>
+          <t>CPB</t>
         </is>
       </c>
       <c r="B338" t="n">
@@ -3811,7 +3811,7 @@
     <row r="339">
       <c r="A339" s="1" t="inlineStr">
         <is>
-          <t>WELL</t>
+          <t>ANSS</t>
         </is>
       </c>
       <c r="B339" t="n">
@@ -3821,7 +3821,7 @@
     <row r="340">
       <c r="A340" s="1" t="inlineStr">
         <is>
-          <t>WMB</t>
+          <t>YUM</t>
         </is>
       </c>
       <c r="B340" t="n">
@@ -3831,7 +3831,7 @@
     <row r="341">
       <c r="A341" s="1" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>MPWR</t>
         </is>
       </c>
       <c r="B341" t="n">
@@ -3841,7 +3841,7 @@
     <row r="342">
       <c r="A342" s="1" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B342" t="n">
@@ -3851,7 +3851,7 @@
     <row r="343">
       <c r="A343" s="1" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>J</t>
         </is>
       </c>
       <c r="B343" t="n">
@@ -3861,7 +3861,7 @@
     <row r="344">
       <c r="A344" s="1" t="inlineStr">
         <is>
-          <t>WPX</t>
+          <t>NDSN</t>
         </is>
       </c>
       <c r="B344" t="n">
@@ -3871,7 +3871,7 @@
     <row r="345">
       <c r="A345" s="1" t="inlineStr">
         <is>
-          <t>WRB</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B345" t="n">
@@ -3881,7 +3881,7 @@
     <row r="346">
       <c r="A346" s="1" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>UHS</t>
         </is>
       </c>
       <c r="B346" t="n">
@@ -3891,7 +3891,7 @@
     <row r="347">
       <c r="A347" s="1" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>CLF</t>
         </is>
       </c>
       <c r="B347" t="n">
@@ -3901,7 +3901,7 @@
     <row r="348">
       <c r="A348" s="1" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>LW</t>
         </is>
       </c>
       <c r="B348" t="n">
@@ -3911,7 +3911,7 @@
     <row r="349">
       <c r="A349" s="1" t="inlineStr">
         <is>
-          <t>UAA</t>
+          <t>LEN</t>
         </is>
       </c>
       <c r="B349" t="n">
@@ -3921,7 +3921,7 @@
     <row r="350">
       <c r="A350" s="1" t="inlineStr">
         <is>
-          <t>UDR</t>
+          <t>CINF</t>
         </is>
       </c>
       <c r="B350" t="n">
@@ -3931,7 +3931,7 @@
     <row r="351">
       <c r="A351" s="1" t="inlineStr">
         <is>
-          <t>ROST</t>
+          <t>PRU</t>
         </is>
       </c>
       <c r="B351" t="n">
@@ -3941,7 +3941,7 @@
     <row r="352">
       <c r="A352" s="1" t="inlineStr">
         <is>
-          <t>ROL</t>
+          <t>EXPE</t>
         </is>
       </c>
       <c r="B352" t="n">
@@ -3951,7 +3951,7 @@
     <row r="353">
       <c r="A353" s="1" t="inlineStr">
         <is>
-          <t>ROK</t>
+          <t>MOS</t>
         </is>
       </c>
       <c r="B353" t="n">
@@ -3961,7 +3961,7 @@
     <row r="354">
       <c r="A354" s="1" t="inlineStr">
         <is>
-          <t>STT</t>
+          <t>WU</t>
         </is>
       </c>
       <c r="B354" t="n">
@@ -3971,7 +3971,7 @@
     <row r="355">
       <c r="A355" s="1" t="inlineStr">
         <is>
-          <t>RL</t>
+          <t>OTIS</t>
         </is>
       </c>
       <c r="B355" t="n">
@@ -3981,7 +3981,7 @@
     <row r="356">
       <c r="A356" s="1" t="inlineStr">
         <is>
-          <t>RJF</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B356" t="n">
@@ -3991,7 +3991,7 @@
     <row r="357">
       <c r="A357" s="1" t="inlineStr">
         <is>
-          <t>STZ</t>
+          <t>KEY</t>
         </is>
       </c>
       <c r="B357" t="n">
@@ -4001,7 +4001,7 @@
     <row r="358">
       <c r="A358" s="1" t="inlineStr">
         <is>
-          <t>SUN</t>
+          <t>EVRG</t>
         </is>
       </c>
       <c r="B358" t="n">
@@ -4011,7 +4011,7 @@
     <row r="359">
       <c r="A359" s="1" t="inlineStr">
         <is>
-          <t>RHI</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="B359" t="n">
@@ -4021,7 +4021,7 @@
     <row r="360">
       <c r="A360" s="1" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>AFL</t>
         </is>
       </c>
       <c r="B360" t="n">
@@ -4031,7 +4031,7 @@
     <row r="361">
       <c r="A361" s="1" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>EIX</t>
         </is>
       </c>
       <c r="B361" t="n">
@@ -4041,7 +4041,7 @@
     <row r="362">
       <c r="A362" s="1" t="inlineStr">
         <is>
-          <t>SUNEQ</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B362" t="n">
@@ -4051,7 +4051,7 @@
     <row r="363">
       <c r="A363" s="1" t="inlineStr">
         <is>
-          <t>RRC</t>
+          <t>KEYS</t>
         </is>
       </c>
       <c r="B363" t="n">
@@ -4061,7 +4061,7 @@
     <row r="364">
       <c r="A364" s="1" t="inlineStr">
         <is>
-          <t>SVU</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="B364" t="n">
@@ -4071,7 +4071,7 @@
     <row r="365">
       <c r="A365" s="1" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>PEG</t>
         </is>
       </c>
       <c r="B365" t="n">
@@ -4081,7 +4081,7 @@
     <row r="366">
       <c r="A366" s="1" t="inlineStr">
         <is>
-          <t>SWN</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B366" t="n">
@@ -4091,7 +4091,7 @@
     <row r="367">
       <c r="A367" s="1" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>TAP</t>
         </is>
       </c>
       <c r="B367" t="n">
@@ -4101,7 +4101,7 @@
     <row r="368">
       <c r="A368" s="1" t="inlineStr">
         <is>
-          <t>RDC</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B368" t="n">
@@ -4111,7 +4111,7 @@
     <row r="369">
       <c r="A369" s="1" t="inlineStr">
         <is>
-          <t>RCL</t>
+          <t>AZO</t>
         </is>
       </c>
       <c r="B369" t="n">
@@ -4121,7 +4121,7 @@
     <row r="370">
       <c r="A370" s="1" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>FMC</t>
         </is>
       </c>
       <c r="B370" t="n">
@@ -4131,7 +4131,7 @@
     <row r="371">
       <c r="A371" s="1" t="inlineStr">
         <is>
-          <t>QRVO</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B371" t="n">
@@ -4141,7 +4141,7 @@
     <row r="372">
       <c r="A372" s="1" t="inlineStr">
         <is>
-          <t>QLGC</t>
+          <t>KHC</t>
         </is>
       </c>
       <c r="B372" t="n">
@@ -4151,7 +4151,7 @@
     <row r="373">
       <c r="A373" s="1" t="inlineStr">
         <is>
-          <t>QEP</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="B373" t="n">
@@ -4161,7 +4161,7 @@
     <row r="374">
       <c r="A374" s="1" t="inlineStr">
         <is>
-          <t>SYF</t>
+          <t>CNX</t>
         </is>
       </c>
       <c r="B374" t="n">
@@ -4171,7 +4171,7 @@
     <row r="375">
       <c r="A375" s="1" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>CPWR</t>
         </is>
       </c>
       <c r="B375" t="n">
@@ -4181,7 +4181,7 @@
     <row r="376">
       <c r="A376" s="1" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B376" t="n">
@@ -4191,7 +4191,7 @@
     <row r="377">
       <c r="A377" s="1" t="inlineStr">
         <is>
-          <t>REG</t>
+          <t>FHN</t>
         </is>
       </c>
       <c r="B377" t="n">
@@ -4201,7 +4201,7 @@
     <row r="378">
       <c r="A378" s="1" t="inlineStr">
         <is>
-          <t>PXD</t>
+          <t>APH</t>
         </is>
       </c>
       <c r="B378" t="n">
@@ -4211,7 +4211,7 @@
     <row r="379">
       <c r="A379" s="1" t="inlineStr">
         <is>
-          <t>RRD</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B379" t="n">
@@ -4221,7 +4221,7 @@
     <row r="380">
       <c r="A380" s="1" t="inlineStr">
         <is>
-          <t>STJ</t>
+          <t>HOLX</t>
         </is>
       </c>
       <c r="B380" t="n">
@@ -4231,7 +4231,7 @@
     <row r="381">
       <c r="A381" s="1" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>DOV</t>
         </is>
       </c>
       <c r="B381" t="n">
@@ -4241,7 +4241,7 @@
     <row r="382">
       <c r="A382" s="1" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="B382" t="n">
@@ -4251,7 +4251,7 @@
     <row r="383">
       <c r="A383" s="1" t="inlineStr">
         <is>
-          <t>SIVB</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="B383" t="n">
@@ -4261,7 +4261,7 @@
     <row r="384">
       <c r="A384" s="1" t="inlineStr">
         <is>
-          <t>SNPS</t>
+          <t>WM</t>
         </is>
       </c>
       <c r="B384" t="n">
@@ -4271,7 +4271,7 @@
     <row r="385">
       <c r="A385" s="1" t="inlineStr">
         <is>
-          <t>SII</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="B385" t="n">
@@ -4281,7 +4281,7 @@
     <row r="386">
       <c r="A386" s="1" t="inlineStr">
         <is>
-          <t>SO</t>
+          <t>JCI</t>
         </is>
       </c>
       <c r="B386" t="n">
@@ -4291,7 +4291,7 @@
     <row r="387">
       <c r="A387" s="1" t="inlineStr">
         <is>
-          <t>SOLV</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B387" t="n">
@@ -4301,7 +4301,7 @@
     <row r="388">
       <c r="A388" s="1" t="inlineStr">
         <is>
-          <t>SIG</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B388" t="n">
@@ -4311,7 +4311,7 @@
     <row r="389">
       <c r="A389" s="1" t="inlineStr">
         <is>
-          <t>SIAL</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="B389" t="n">
@@ -4321,7 +4321,7 @@
     <row r="390">
       <c r="A390" s="1" t="inlineStr">
         <is>
-          <t>SPLS</t>
+          <t>CTRA</t>
         </is>
       </c>
       <c r="B390" t="n">
@@ -4331,7 +4331,7 @@
     <row r="391">
       <c r="A391" s="1" t="inlineStr">
         <is>
-          <t>SRCL</t>
+          <t>EBAY</t>
         </is>
       </c>
       <c r="B391" t="n">
@@ -4341,7 +4341,7 @@
     <row r="392">
       <c r="A392" s="1" t="inlineStr">
         <is>
-          <t>SRE</t>
+          <t>TFX</t>
         </is>
       </c>
       <c r="B392" t="n">
@@ -4351,7 +4351,7 @@
     <row r="393">
       <c r="A393" s="1" t="inlineStr">
         <is>
-          <t>STR</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B393" t="n">
@@ -4361,7 +4361,7 @@
     <row r="394">
       <c r="A394" s="1" t="inlineStr">
         <is>
-          <t>SEE</t>
+          <t>ERIE</t>
         </is>
       </c>
       <c r="B394" t="n">
@@ -4371,7 +4371,7 @@
     <row r="395">
       <c r="A395" s="1" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>FAST</t>
         </is>
       </c>
       <c r="B395" t="n">
@@ -4381,7 +4381,7 @@
     <row r="396">
       <c r="A396" s="1" t="inlineStr">
         <is>
-          <t>STE</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="B396" t="n">
@@ -4391,7 +4391,7 @@
     <row r="397">
       <c r="A397" s="1" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>TRIP</t>
         </is>
       </c>
       <c r="B397" t="n">
@@ -4401,7 +4401,7 @@
     <row r="398">
       <c r="A398" s="1" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>IQV</t>
         </is>
       </c>
       <c r="B398" t="n">
@@ -4411,7 +4411,7 @@
     <row r="399">
       <c r="A399" s="1" t="inlineStr">
         <is>
-          <t>SBNY</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B399" t="n">
@@ -4421,7 +4421,7 @@
     <row r="400">
       <c r="A400" s="1" t="inlineStr">
         <is>
-          <t>STI</t>
+          <t>CHTR</t>
         </is>
       </c>
       <c r="B400" t="n">
@@ -4431,7 +4431,7 @@
     <row r="401">
       <c r="A401" s="1" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="B401" t="n">
@@ -4441,7 +4441,7 @@
     <row r="402">
       <c r="A402" s="1" t="inlineStr">
         <is>
-          <t>RX</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B402" t="n">
@@ -4451,7 +4451,7 @@
     <row r="403">
       <c r="A403" s="1" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>INVH</t>
         </is>
       </c>
       <c r="B403" t="n">
@@ -4461,7 +4461,7 @@
     <row r="404">
       <c r="A404" s="1" t="inlineStr">
         <is>
-          <t>RVTY</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="B404" t="n">
@@ -4471,7 +4471,7 @@
     <row r="405">
       <c r="A405" s="1" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="B405" t="n">
@@ -4481,7 +4481,7 @@
     <row r="406">
       <c r="A406" s="1" t="inlineStr">
         <is>
-          <t>RSHCQ</t>
+          <t>CAH</t>
         </is>
       </c>
       <c r="B406" t="n">
@@ -4491,7 +4491,7 @@
     <row r="407">
       <c r="A407" s="1" t="inlineStr">
         <is>
-          <t>SEDG</t>
+          <t>CTAS</t>
         </is>
       </c>
       <c r="B407" t="n">
@@ -4501,7 +4501,7 @@
     <row r="408">
       <c r="A408" s="1" t="inlineStr">
         <is>
-          <t>PX</t>
+          <t>JEF</t>
         </is>
       </c>
       <c r="B408" t="n">
@@ -4511,7 +4511,7 @@
     <row r="409">
       <c r="A409" s="1" t="inlineStr">
         <is>
-          <t>PWR</t>
+          <t>PARA</t>
         </is>
       </c>
       <c r="B409" t="n">
@@ -4521,7 +4521,7 @@
     <row r="410">
       <c r="A410" s="1" t="inlineStr">
         <is>
-          <t>PVH</t>
+          <t>FE</t>
         </is>
       </c>
       <c r="B410" t="n">
@@ -4531,7 +4531,7 @@
     <row r="411">
       <c r="A411" s="1" t="inlineStr">
         <is>
-          <t>TRMB</t>
+          <t>PRGO</t>
         </is>
       </c>
       <c r="B411" t="n">
@@ -4541,7 +4541,7 @@
     <row r="412">
       <c r="A412" s="1" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>MCO</t>
         </is>
       </c>
       <c r="B412" t="n">
@@ -4551,7 +4551,7 @@
     <row r="413">
       <c r="A413" s="1" t="inlineStr">
         <is>
-          <t>PEG</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B413" t="n">
@@ -4561,7 +4561,7 @@
     <row r="414">
       <c r="A414" s="1" t="inlineStr">
         <is>
-          <t>PEAK</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="B414" t="n">
@@ -4571,7 +4571,7 @@
     <row r="415">
       <c r="A415" s="1" t="inlineStr">
         <is>
-          <t>PDCO</t>
+          <t>NAVI</t>
         </is>
       </c>
       <c r="B415" t="n">
@@ -4581,7 +4581,7 @@
     <row r="416">
       <c r="A416" s="1" t="inlineStr">
         <is>
-          <t>TRV</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="B416" t="n">
@@ -4591,7 +4591,7 @@
     <row r="417">
       <c r="A417" s="1" t="inlineStr">
         <is>
-          <t>TSCO</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B417" t="n">
@@ -4601,7 +4601,7 @@
     <row r="418">
       <c r="A418" s="1" t="inlineStr">
         <is>
-          <t>TSN</t>
+          <t>THC</t>
         </is>
       </c>
       <c r="B418" t="n">
@@ -4611,7 +4611,7 @@
     <row r="419">
       <c r="A419" s="1" t="inlineStr">
         <is>
-          <t>TSS</t>
+          <t>ZBH</t>
         </is>
       </c>
       <c r="B419" t="n">
@@ -4621,7 +4621,7 @@
     <row r="420">
       <c r="A420" s="1" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B420" t="n">
@@ -4631,7 +4631,7 @@
     <row r="421">
       <c r="A421" s="1" t="inlineStr">
         <is>
-          <t>TTWO</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B421" t="n">
@@ -4641,7 +4641,7 @@
     <row r="422">
       <c r="A422" s="1" t="inlineStr">
         <is>
-          <t>TWX</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="B422" t="n">
@@ -4651,7 +4651,7 @@
     <row r="423">
       <c r="A423" s="1" t="inlineStr">
         <is>
-          <t>TRIP</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B423" t="n">
@@ -4661,7 +4661,7 @@
     <row r="424">
       <c r="A424" s="1" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="B424" t="n">
@@ -4671,7 +4671,7 @@
     <row r="425">
       <c r="A425" s="1" t="inlineStr">
         <is>
-          <t>TYL</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="B425" t="n">
@@ -4681,7 +4681,7 @@
     <row r="426">
       <c r="A426" s="1" t="inlineStr">
         <is>
-          <t>PAYC</t>
+          <t>DOC</t>
         </is>
       </c>
       <c r="B426" t="n">
@@ -4691,7 +4691,7 @@
     <row r="427">
       <c r="A427" s="1" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>ROK</t>
         </is>
       </c>
       <c r="B427" t="n">
@@ -4701,7 +4701,7 @@
     <row r="428">
       <c r="A428" s="1" t="inlineStr">
         <is>
-          <t>PARA</t>
+          <t>UAA</t>
         </is>
       </c>
       <c r="B428" t="n">
@@ -4711,7 +4711,7 @@
     <row r="429">
       <c r="A429" s="1" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>TT</t>
         </is>
       </c>
       <c r="B429" t="n">
@@ -4721,7 +4721,7 @@
     <row r="430">
       <c r="A430" s="1" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>RCL</t>
         </is>
       </c>
       <c r="B430" t="n">
@@ -4731,7 +4731,7 @@
     <row r="431">
       <c r="A431" s="1" t="inlineStr">
         <is>
-          <t>UAL</t>
+          <t>ZION</t>
         </is>
       </c>
       <c r="B431" t="n">
@@ -4741,7 +4741,7 @@
     <row r="432">
       <c r="A432" s="1" t="inlineStr">
         <is>
-          <t>ORLY</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="B432" t="n">
@@ -4751,7 +4751,7 @@
     <row r="433">
       <c r="A433" s="1" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>CNC</t>
         </is>
       </c>
       <c r="B433" t="n">
@@ -4761,7 +4761,7 @@
     <row r="434">
       <c r="A434" s="1" t="inlineStr">
         <is>
-          <t>ON</t>
+          <t>USB</t>
         </is>
       </c>
       <c r="B434" t="n">
@@ -4771,7 +4771,7 @@
     <row r="435">
       <c r="A435" s="1" t="inlineStr">
         <is>
-          <t>OMC</t>
+          <t>SNPS</t>
         </is>
       </c>
       <c r="B435" t="n">
@@ -4781,7 +4781,7 @@
     <row r="436">
       <c r="A436" s="1" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B436" t="n">
@@ -4791,7 +4791,7 @@
     <row r="437">
       <c r="A437" s="1" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>DXCM</t>
         </is>
       </c>
       <c r="B437" t="n">
@@ -4801,7 +4801,7 @@
     <row r="438">
       <c r="A438" s="1" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="B438" t="n">
@@ -4811,7 +4811,7 @@
     <row r="439">
       <c r="A439" s="1" t="inlineStr">
         <is>
-          <t>TPR</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="B439" t="n">
@@ -4821,7 +4821,7 @@
     <row r="440">
       <c r="A440" s="1" t="inlineStr">
         <is>
-          <t>PENN</t>
+          <t>KKR</t>
         </is>
       </c>
       <c r="B440" t="n">
@@ -4831,7 +4831,7 @@
     <row r="441">
       <c r="A441" s="1" t="inlineStr">
         <is>
-          <t>SYK</t>
+          <t>ON</t>
         </is>
       </c>
       <c r="B441" t="n">
@@ -4841,7 +4841,7 @@
     <row r="442">
       <c r="A442" s="1" t="inlineStr">
         <is>
-          <t>SYMC</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="B442" t="n">
@@ -4851,7 +4851,7 @@
     <row r="443">
       <c r="A443" s="1" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="B443" t="n">
@@ -4861,7 +4861,7 @@
     <row r="444">
       <c r="A444" s="1" t="inlineStr">
         <is>
-          <t>PRU</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="B444" t="n">
@@ -4871,7 +4871,7 @@
     <row r="445">
       <c r="A445" s="1" t="inlineStr">
         <is>
-          <t>PRGO</t>
+          <t>TER</t>
         </is>
       </c>
       <c r="B445" t="n">
@@ -4881,7 +4881,7 @@
     <row r="446">
       <c r="A446" s="1" t="inlineStr">
         <is>
-          <t>PPL</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="B446" t="n">
@@ -4891,7 +4891,7 @@
     <row r="447">
       <c r="A447" s="1" t="inlineStr">
         <is>
-          <t>PPG</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="B447" t="n">
@@ -4901,7 +4901,7 @@
     <row r="448">
       <c r="A448" s="1" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>UAL</t>
         </is>
       </c>
       <c r="B448" t="n">
@@ -4921,7 +4921,7 @@
     <row r="450">
       <c r="A450" s="1" t="inlineStr">
         <is>
-          <t>PNR</t>
+          <t>MAT</t>
         </is>
       </c>
       <c r="B450" t="n">
@@ -4931,7 +4931,7 @@
     <row r="451">
       <c r="A451" s="1" t="inlineStr">
         <is>
-          <t>TDC</t>
+          <t>SNA</t>
         </is>
       </c>
       <c r="B451" t="n">
@@ -4941,7 +4941,7 @@
     <row r="452">
       <c r="A452" s="1" t="inlineStr">
         <is>
-          <t>PNC</t>
+          <t>BIIB</t>
         </is>
       </c>
       <c r="B452" t="n">
@@ -4951,7 +4951,7 @@
     <row r="453">
       <c r="A453" s="1" t="inlineStr">
         <is>
-          <t>TDG</t>
+          <t>EFX</t>
         </is>
       </c>
       <c r="B453" t="n">
@@ -4961,7 +4961,7 @@
     <row r="454">
       <c r="A454" s="1" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>TFC</t>
         </is>
       </c>
       <c r="B454" t="n">
@@ -4971,7 +4971,7 @@
     <row r="455">
       <c r="A455" s="1" t="inlineStr">
         <is>
-          <t>TDY</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B455" t="n">
@@ -4981,7 +4981,7 @@
     <row r="456">
       <c r="A456" s="1" t="inlineStr">
         <is>
-          <t>TFC</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B456" t="n">
@@ -4991,7 +4991,7 @@
     <row r="457">
       <c r="A457" s="1" t="inlineStr">
         <is>
-          <t>PKG</t>
+          <t>PBI</t>
         </is>
       </c>
       <c r="B457" t="n">
@@ -5001,7 +5001,7 @@
     <row r="458">
       <c r="A458" s="1" t="inlineStr">
         <is>
-          <t>PHM</t>
+          <t>TYL</t>
         </is>
       </c>
       <c r="B458" t="n">
@@ -5011,7 +5011,7 @@
     <row r="459">
       <c r="A459" s="1" t="inlineStr">
         <is>
-          <t>TFX</t>
+          <t>RIG</t>
         </is>
       </c>
       <c r="B459" t="n">
@@ -5021,7 +5021,7 @@
     <row r="460">
       <c r="A460" s="1" t="inlineStr">
         <is>
-          <t>THC</t>
+          <t>VRTX</t>
         </is>
       </c>
       <c r="B460" t="n">
@@ -5031,7 +5031,7 @@
     <row r="461">
       <c r="A461" s="1" t="inlineStr">
         <is>
-          <t>PGN</t>
+          <t>GNW</t>
         </is>
       </c>
       <c r="B461" t="n">
@@ -5041,7 +5041,7 @@
     <row r="462">
       <c r="A462" s="1" t="inlineStr">
         <is>
-          <t>TLAB</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="B462" t="n">
@@ -5051,7 +5051,7 @@
     <row r="463">
       <c r="A463" s="1" t="inlineStr">
         <is>
-          <t>TMK</t>
+          <t>APD</t>
         </is>
       </c>
       <c r="B463" t="n">
@@ -5061,7 +5061,7 @@
     <row r="464">
       <c r="A464" s="1" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B464" t="n">
@@ -5071,7 +5071,7 @@
     <row r="465">
       <c r="A465" s="1" t="inlineStr">
         <is>
-          <t>TPL</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="B465" t="n">
@@ -5081,7 +5081,7 @@
     <row r="466">
       <c r="A466" s="1" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>CCEP</t>
         </is>
       </c>
       <c r="B466" t="n">
@@ -5091,7 +5091,7 @@
     <row r="467">
       <c r="A467" s="1" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>GPC</t>
         </is>
       </c>
       <c r="B467" t="n">
@@ -5101,7 +5101,7 @@
     <row r="468">
       <c r="A468" s="1" t="inlineStr">
         <is>
-          <t>UHS</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B468" t="n">
@@ -5111,7 +5111,7 @@
     <row r="469">
       <c r="A469" s="1" t="inlineStr">
         <is>
-          <t>MHS</t>
+          <t>BLDR</t>
         </is>
       </c>
       <c r="B469" t="n">
@@ -5121,7 +5121,7 @@
     <row r="470">
       <c r="A470" s="1" t="inlineStr">
         <is>
-          <t>JCP</t>
+          <t>HUBB</t>
         </is>
       </c>
       <c r="B470" t="n">
@@ -5131,7 +5131,7 @@
     <row r="471">
       <c r="A471" s="1" t="inlineStr">
         <is>
-          <t>MGM</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="B471" t="n">
@@ -5141,7 +5141,7 @@
     <row r="472">
       <c r="A472" s="1" t="inlineStr">
         <is>
-          <t>CFG</t>
+          <t>LEG</t>
         </is>
       </c>
       <c r="B472" t="n">
@@ -5151,7 +5151,7 @@
     <row r="473">
       <c r="A473" s="1" t="inlineStr">
         <is>
-          <t>CHD</t>
+          <t>BEN</t>
         </is>
       </c>
       <c r="B473" t="n">
@@ -5161,7 +5161,7 @@
     <row r="474">
       <c r="A474" s="1" t="inlineStr">
         <is>
-          <t>CHK</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B474" t="n">
@@ -5171,7 +5171,7 @@
     <row r="475">
       <c r="A475" s="1" t="inlineStr">
         <is>
-          <t>CHRW</t>
+          <t>HRL</t>
         </is>
       </c>
       <c r="B475" t="n">
@@ -5181,7 +5181,7 @@
     <row r="476">
       <c r="A476" s="1" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>MOH</t>
         </is>
       </c>
       <c r="B476" t="n">
@@ -5191,7 +5191,7 @@
     <row r="477">
       <c r="A477" s="1" t="inlineStr">
         <is>
-          <t>CINF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B477" t="n">
@@ -5201,7 +5201,7 @@
     <row r="478">
       <c r="A478" s="1" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>IGT</t>
         </is>
       </c>
       <c r="B478" t="n">
@@ -5211,7 +5211,7 @@
     <row r="479">
       <c r="A479" s="1" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>LYV</t>
         </is>
       </c>
       <c r="B479" t="n">
@@ -5221,7 +5221,7 @@
     <row r="480">
       <c r="A480" s="1" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>WELL</t>
         </is>
       </c>
       <c r="B480" t="n">
@@ -5231,7 +5231,7 @@
     <row r="481">
       <c r="A481" s="1" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>BWA</t>
         </is>
       </c>
       <c r="B481" t="n">
@@ -5241,7 +5241,7 @@
     <row r="482">
       <c r="A482" s="1" t="inlineStr">
         <is>
-          <t>CNC</t>
+          <t>HAS</t>
         </is>
       </c>
       <c r="B482" t="n">
@@ -5251,7 +5251,7 @@
     <row r="483">
       <c r="A483" s="1" t="inlineStr">
         <is>
-          <t>CNP</t>
+          <t>WMB</t>
         </is>
       </c>
       <c r="B483" t="n">
@@ -5261,7 +5261,7 @@
     <row r="484">
       <c r="A484" s="1" t="inlineStr">
         <is>
-          <t>CNX</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="B484" t="n">
@@ -5271,7 +5271,7 @@
     <row r="485">
       <c r="A485" s="1" t="inlineStr">
         <is>
-          <t>COF</t>
+          <t>SRE</t>
         </is>
       </c>
       <c r="B485" t="n">
@@ -5281,7 +5281,7 @@
     <row r="486">
       <c r="A486" s="1" t="inlineStr">
         <is>
-          <t>COG</t>
+          <t>ETR</t>
         </is>
       </c>
       <c r="B486" t="n">
@@ -5291,7 +5291,7 @@
     <row r="487">
       <c r="A487" s="1" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>VRSN</t>
         </is>
       </c>
       <c r="B487" t="n">
@@ -5301,7 +5301,7 @@
     <row r="488">
       <c r="A488" s="1" t="inlineStr">
         <is>
-          <t>CMCSK</t>
+          <t>SLM</t>
         </is>
       </c>
       <c r="B488" t="n">
@@ -5311,7 +5311,7 @@
     <row r="489">
       <c r="A489" s="1" t="inlineStr">
         <is>
-          <t>COO</t>
+          <t>ATI</t>
         </is>
       </c>
       <c r="B489" t="n">
@@ -5321,7 +5321,7 @@
     <row r="490">
       <c r="A490" s="1" t="inlineStr">
         <is>
-          <t>CERN</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B490" t="n">
@@ -5331,7 +5331,7 @@
     <row r="491">
       <c r="A491" s="1" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>APTV</t>
         </is>
       </c>
       <c r="B491" t="n">
@@ -5341,7 +5341,7 @@
     <row r="492">
       <c r="A492" s="1" t="inlineStr">
         <is>
-          <t>BTUUQ</t>
+          <t>BK</t>
         </is>
       </c>
       <c r="B492" t="n">
@@ -5351,7 +5351,7 @@
     <row r="493">
       <c r="A493" s="1" t="inlineStr">
         <is>
-          <t>BWA</t>
+          <t>GDDY</t>
         </is>
       </c>
       <c r="B493" t="n">
@@ -5361,7 +5361,7 @@
     <row r="494">
       <c r="A494" s="1" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>DAY</t>
         </is>
       </c>
       <c r="B494" t="n">
@@ -5371,7 +5371,7 @@
     <row r="495">
       <c r="A495" s="1" t="inlineStr">
         <is>
-          <t>BXLT</t>
+          <t>XYL</t>
         </is>
       </c>
       <c r="B495" t="n">
@@ -5381,7 +5381,7 @@
     <row r="496">
       <c r="A496" s="1" t="inlineStr">
         <is>
-          <t>BXP</t>
+          <t>CMI</t>
         </is>
       </c>
       <c r="B496" t="n">
@@ -5391,7 +5391,7 @@
     <row r="497">
       <c r="A497" s="1" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>HBAN</t>
         </is>
       </c>
       <c r="B497" t="n">
@@ -5401,7 +5401,7 @@
     <row r="498">
       <c r="A498" s="1" t="inlineStr">
         <is>
-          <t>CAM</t>
+          <t>DVA</t>
         </is>
       </c>
       <c r="B498" t="n">
@@ -5411,7 +5411,7 @@
     <row r="499">
       <c r="A499" s="1" t="inlineStr">
         <is>
-          <t>CEPH</t>
+          <t>XEL</t>
         </is>
       </c>
       <c r="B499" t="n">
@@ -5421,7 +5421,7 @@
     <row r="500">
       <c r="A500" s="1" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>STLD</t>
         </is>
       </c>
       <c r="B500" t="n">
@@ -5431,7 +5431,7 @@
     <row r="501">
       <c r="A501" s="1" t="inlineStr">
         <is>
-          <t>CBE</t>
+          <t>WAT</t>
         </is>
       </c>
       <c r="B501" t="n">
@@ -5441,7 +5441,7 @@
     <row r="502">
       <c r="A502" s="1" t="inlineStr">
         <is>
-          <t>CBRE</t>
+          <t>MET</t>
         </is>
       </c>
       <c r="B502" t="n">
@@ -5451,7 +5451,7 @@
     <row r="503">
       <c r="A503" s="1" t="inlineStr">
         <is>
-          <t>CCEP</t>
+          <t>MTD</t>
         </is>
       </c>
       <c r="B503" t="n">
@@ -5461,7 +5461,7 @@
     <row r="504">
       <c r="A504" s="1" t="inlineStr">
         <is>
-          <t>CCI</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B504" t="n">
@@ -5471,7 +5471,7 @@
     <row r="505">
       <c r="A505" s="1" t="inlineStr">
         <is>
-          <t>CCL</t>
+          <t>L</t>
         </is>
       </c>
       <c r="B505" t="n">
@@ -5481,7 +5481,7 @@
     <row r="506">
       <c r="A506" s="1" t="inlineStr">
         <is>
-          <t>CDAY</t>
+          <t>NXPI</t>
         </is>
       </c>
       <c r="B506" t="n">
@@ -5491,7 +5491,7 @@
     <row r="507">
       <c r="A507" s="1" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>ROST</t>
         </is>
       </c>
       <c r="B507" t="n">
@@ -5501,7 +5501,7 @@
     <row r="508">
       <c r="A508" s="1" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>LDOS</t>
         </is>
       </c>
       <c r="B508" t="n">
@@ -5511,7 +5511,7 @@
     <row r="509">
       <c r="A509" s="1" t="inlineStr">
         <is>
-          <t>BRO</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="B509" t="n">
@@ -5521,7 +5521,7 @@
     <row r="510">
       <c r="A510" s="1" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="B510" t="n">
@@ -5531,7 +5531,7 @@
     <row r="511">
       <c r="A511" s="1" t="inlineStr">
         <is>
-          <t>CPRT</t>
+          <t>MNST</t>
         </is>
       </c>
       <c r="B511" t="n">
@@ -5541,7 +5541,7 @@
     <row r="512">
       <c r="A512" s="1" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="B512" t="n">
@@ -5551,7 +5551,7 @@
     <row r="513">
       <c r="A513" s="1" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>AN</t>
         </is>
       </c>
       <c r="B513" t="n">
@@ -5561,7 +5561,7 @@
     <row r="514">
       <c r="A514" s="1" t="inlineStr">
         <is>
-          <t>DFS</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="B514" t="n">
@@ -5571,7 +5571,7 @@
     <row r="515">
       <c r="A515" s="1" t="inlineStr">
         <is>
-          <t>DG</t>
+          <t>KSS</t>
         </is>
       </c>
       <c r="B515" t="n">
@@ -5581,7 +5581,7 @@
     <row r="516">
       <c r="A516" s="1" t="inlineStr">
         <is>
-          <t>DGX</t>
+          <t>CTVA</t>
         </is>
       </c>
       <c r="B516" t="n">
@@ -5591,7 +5591,7 @@
     <row r="517">
       <c r="A517" s="1" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="B517" t="n">
@@ -5601,7 +5601,7 @@
     <row r="518">
       <c r="A518" s="1" t="inlineStr">
         <is>
-          <t>DISH</t>
+          <t>CNP</t>
         </is>
       </c>
       <c r="B518" t="n">
@@ -5611,7 +5611,7 @@
     <row r="519">
       <c r="A519" s="1" t="inlineStr">
         <is>
-          <t>DECK</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B519" t="n">
@@ -5621,7 +5621,7 @@
     <row r="520">
       <c r="A520" s="1" t="inlineStr">
         <is>
-          <t>DLR</t>
+          <t>AXON</t>
         </is>
       </c>
       <c r="B520" t="n">
@@ -5631,7 +5631,7 @@
     <row r="521">
       <c r="A521" s="1" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>CFG</t>
         </is>
       </c>
       <c r="B521" t="n">
@@ -5641,7 +5641,7 @@
     <row r="522">
       <c r="A522" s="1" t="inlineStr">
         <is>
-          <t>DOC</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B522" t="n">
@@ -5651,7 +5651,7 @@
     <row r="523">
       <c r="A523" s="1" t="inlineStr">
         <is>
-          <t>DOV</t>
+          <t>NVR</t>
         </is>
       </c>
       <c r="B523" t="n">
@@ -5661,7 +5661,7 @@
     <row r="524">
       <c r="A524" s="1" t="inlineStr">
         <is>
-          <t>DOW</t>
+          <t>HRB</t>
         </is>
       </c>
       <c r="B524" t="n">
@@ -5671,7 +5671,7 @@
     <row r="525">
       <c r="A525" s="1" t="inlineStr">
         <is>
-          <t>DRE</t>
+          <t>TGNA</t>
         </is>
       </c>
       <c r="B525" t="n">
@@ -5681,7 +5681,7 @@
     <row r="526">
       <c r="A526" s="1" t="inlineStr">
         <is>
-          <t>DRI</t>
+          <t>FLS</t>
         </is>
       </c>
       <c r="B526" t="n">
@@ -5691,7 +5691,7 @@
     <row r="527">
       <c r="A527" s="1" t="inlineStr">
         <is>
-          <t>DTE</t>
+          <t>AEE</t>
         </is>
       </c>
       <c r="B527" t="n">
@@ -5701,7 +5701,7 @@
     <row r="528">
       <c r="A528" s="1" t="inlineStr">
         <is>
-          <t>DNR</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="B528" t="n">
@@ -5711,7 +5711,7 @@
     <row r="529">
       <c r="A529" s="1" t="inlineStr">
         <is>
-          <t>CPGX</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="B529" t="n">
@@ -5721,7 +5721,7 @@
     <row r="530">
       <c r="A530" s="1" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B530" t="n">
@@ -5731,7 +5731,7 @@
     <row r="531">
       <c r="A531" s="1" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>FRT</t>
         </is>
       </c>
       <c r="B531" t="n">
@@ -5741,7 +5741,7 @@
     <row r="532">
       <c r="A532" s="1" t="inlineStr">
         <is>
-          <t>CPT</t>
+          <t>GIS</t>
         </is>
       </c>
       <c r="B532" t="n">
@@ -5751,7 +5751,7 @@
     <row r="533">
       <c r="A533" s="1" t="inlineStr">
         <is>
-          <t>CRL</t>
+          <t>MMC</t>
         </is>
       </c>
       <c r="B533" t="n">
@@ -5761,7 +5761,7 @@
     <row r="534">
       <c r="A534" s="1" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>VTR</t>
         </is>
       </c>
       <c r="B534" t="n">
@@ -5771,7 +5771,7 @@
     <row r="535">
       <c r="A535" s="1" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="B535" t="n">
@@ -5781,7 +5781,7 @@
     <row r="536">
       <c r="A536" s="1" t="inlineStr">
         <is>
-          <t>CSGP</t>
+          <t>RJF</t>
         </is>
       </c>
       <c r="B536" t="n">
@@ -5791,7 +5791,7 @@
     <row r="537">
       <c r="A537" s="1" t="inlineStr">
         <is>
-          <t>CSRA</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="B537" t="n">
@@ -5801,7 +5801,7 @@
     <row r="538">
       <c r="A538" s="1" t="inlineStr">
         <is>
-          <t>CTAS</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B538" t="n">
@@ -5811,7 +5811,7 @@
     <row r="539">
       <c r="A539" s="1" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B539" t="n">
@@ -5821,7 +5821,7 @@
     <row r="540">
       <c r="A540" s="1" t="inlineStr">
         <is>
-          <t>CTL</t>
+          <t>AIV</t>
         </is>
       </c>
       <c r="B540" t="n">
@@ -5831,7 +5831,7 @@
     <row r="541">
       <c r="A541" s="1" t="inlineStr">
         <is>
-          <t>CTRA</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B541" t="n">
@@ -5841,7 +5841,7 @@
     <row r="542">
       <c r="A542" s="1" t="inlineStr">
         <is>
-          <t>CTVA</t>
+          <t>DUK</t>
         </is>
       </c>
       <c r="B542" t="n">
@@ -5851,7 +5851,7 @@
     <row r="543">
       <c r="A543" s="1" t="inlineStr">
         <is>
-          <t>CVH</t>
+          <t>PPL</t>
         </is>
       </c>
       <c r="B543" t="n">
@@ -5861,7 +5861,7 @@
     <row r="544">
       <c r="A544" s="1" t="inlineStr">
         <is>
-          <t>CVS</t>
+          <t>REG</t>
         </is>
       </c>
       <c r="B544" t="n">
@@ -5871,7 +5871,7 @@
     <row r="545">
       <c r="A545" s="1" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B545" t="n">
@@ -5881,7 +5881,7 @@
     <row r="546">
       <c r="A546" s="1" t="inlineStr">
         <is>
-          <t>CXO</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="B546" t="n">
@@ -5891,7 +5891,7 @@
     <row r="547">
       <c r="A547" s="1" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CRL</t>
         </is>
       </c>
       <c r="B547" t="n">
@@ -5901,7 +5901,7 @@
     <row r="548">
       <c r="A548" s="1" t="inlineStr">
         <is>
-          <t>CTLT</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="B548" t="n">
@@ -5911,7 +5911,7 @@
     <row r="549">
       <c r="A549" s="1" t="inlineStr">
         <is>
-          <t>DTV</t>
+          <t>NRG</t>
         </is>
       </c>
       <c r="B549" t="n">
@@ -5921,7 +5921,7 @@
     <row r="550">
       <c r="A550" s="1" t="inlineStr">
         <is>
-          <t>BRK-B</t>
+          <t>BHF</t>
         </is>
       </c>
       <c r="B550" t="n">
@@ -5931,7 +5931,7 @@
     <row r="551">
       <c r="A551" s="1" t="inlineStr">
         <is>
-          <t>BNI</t>
+          <t>VMC</t>
         </is>
       </c>
       <c r="B551" t="n">
@@ -5941,7 +5941,7 @@
     <row r="552">
       <c r="A552" s="1" t="inlineStr">
         <is>
-          <t>AJG</t>
+          <t>TEL</t>
         </is>
       </c>
       <c r="B552" t="n">
@@ -5951,7 +5951,7 @@
     <row r="553">
       <c r="A553" s="1" t="inlineStr">
         <is>
-          <t>AKAM</t>
+          <t>MTB</t>
         </is>
       </c>
       <c r="B553" t="n">
@@ -5961,7 +5961,7 @@
     <row r="554">
       <c r="A554" s="1" t="inlineStr">
         <is>
-          <t>AKS</t>
+          <t>ROL</t>
         </is>
       </c>
       <c r="B554" t="n">
@@ -5971,7 +5971,7 @@
     <row r="555">
       <c r="A555" s="1" t="inlineStr">
         <is>
-          <t>ALB</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="B555" t="n">
@@ -5981,7 +5981,7 @@
     <row r="556">
       <c r="A556" s="1" t="inlineStr">
         <is>
-          <t>ALK</t>
+          <t>FITB</t>
         </is>
       </c>
       <c r="B556" t="n">
@@ -5991,7 +5991,7 @@
     <row r="557">
       <c r="A557" s="1" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>FLR</t>
         </is>
       </c>
       <c r="B557" t="n">
@@ -6001,7 +6001,7 @@
     <row r="558">
       <c r="A558" s="1" t="inlineStr">
         <is>
-          <t>ALLE</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="B558" t="n">
@@ -6011,7 +6011,7 @@
     <row r="559">
       <c r="A559" s="1" t="inlineStr">
         <is>
-          <t>AIZ</t>
+          <t>RL</t>
         </is>
       </c>
       <c r="B559" t="n">
@@ -6021,7 +6021,7 @@
     <row r="560">
       <c r="A560" s="1" t="inlineStr">
         <is>
-          <t>ALXN</t>
+          <t>EQR</t>
         </is>
       </c>
       <c r="B560" t="n">
@@ -6031,7 +6031,7 @@
     <row r="561">
       <c r="A561" s="1" t="inlineStr">
         <is>
-          <t>AMT</t>
+          <t>NWSA</t>
         </is>
       </c>
       <c r="B561" t="n">
@@ -6041,7 +6041,7 @@
     <row r="562">
       <c r="A562" s="1" t="inlineStr">
         <is>
-          <t>AMTM</t>
+          <t>ALGN</t>
         </is>
       </c>
       <c r="B562" t="n">
@@ -6051,7 +6051,7 @@
     <row r="563">
       <c r="A563" s="1" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B563" t="n">
@@ -6061,7 +6061,7 @@
     <row r="564">
       <c r="A564" s="1" t="inlineStr">
         <is>
-          <t>AN</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B564" t="n">
@@ -6071,7 +6071,7 @@
     <row r="565">
       <c r="A565" s="1" t="inlineStr">
         <is>
-          <t>ANDV</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B565" t="n">
@@ -6081,7 +6081,7 @@
     <row r="566">
       <c r="A566" s="1" t="inlineStr">
         <is>
-          <t>ANRZQ</t>
+          <t>ODFL</t>
         </is>
       </c>
       <c r="B566" t="n">
@@ -6091,7 +6091,7 @@
     <row r="567">
       <c r="A567" s="1" t="inlineStr">
         <is>
-          <t>ANSS</t>
+          <t>DGX</t>
         </is>
       </c>
       <c r="B567" t="n">
@@ -6101,7 +6101,7 @@
     <row r="568">
       <c r="A568" s="1" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B568" t="n">
@@ -6111,7 +6111,7 @@
     <row r="569">
       <c r="A569" s="1" t="inlineStr">
         <is>
-          <t>ANTM</t>
+          <t>K</t>
         </is>
       </c>
       <c r="B569" t="n">
@@ -6121,7 +6121,7 @@
     <row r="570">
       <c r="A570" s="1" t="inlineStr">
         <is>
-          <t>AIV</t>
+          <t>GWW</t>
         </is>
       </c>
       <c r="B570" t="n">
@@ -6131,7 +6131,7 @@
     <row r="571">
       <c r="A571" s="1" t="inlineStr">
         <is>
-          <t>AFL</t>
+          <t>CHD</t>
         </is>
       </c>
       <c r="B571" t="n">
@@ -6141,7 +6141,7 @@
     <row r="572">
       <c r="A572" s="1" t="inlineStr">
         <is>
-          <t>AAP</t>
+          <t>FCX</t>
         </is>
       </c>
       <c r="B572" t="n">
@@ -6151,7 +6151,7 @@
     <row r="573">
       <c r="A573" s="1" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>CAG</t>
         </is>
       </c>
       <c r="B573" t="n">
@@ -6161,7 +6161,7 @@
     <row r="574">
       <c r="A574" s="1" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>HON</t>
         </is>
       </c>
       <c r="B574" t="n">
@@ -6171,7 +6171,7 @@
     <row r="575">
       <c r="A575" s="1" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>CSX</t>
         </is>
       </c>
       <c r="B575" t="n">
@@ -6181,7 +6181,7 @@
     <row r="576">
       <c r="A576" s="1" t="inlineStr">
         <is>
-          <t>ABMD</t>
+          <t>HOG</t>
         </is>
       </c>
       <c r="B576" t="n">
@@ -6191,7 +6191,7 @@
     <row r="577">
       <c r="A577" s="1" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>MOLX</t>
         </is>
       </c>
       <c r="B577" t="n">
@@ -6201,7 +6201,7 @@
     <row r="578">
       <c r="A578" s="1" t="inlineStr">
         <is>
-          <t>ACGL</t>
+          <t>GNRC</t>
         </is>
       </c>
       <c r="B578" t="n">
@@ -6211,7 +6211,7 @@
     <row r="579">
       <c r="A579" s="1" t="inlineStr">
         <is>
-          <t>AIR</t>
+          <t>NCLH</t>
         </is>
       </c>
       <c r="B579" t="n">
@@ -6221,7 +6221,7 @@
     <row r="580">
       <c r="A580" s="1" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>HLT</t>
         </is>
       </c>
       <c r="B580" t="n">
@@ -6231,7 +6231,7 @@
     <row r="581">
       <c r="A581" s="1" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>PAYC</t>
         </is>
       </c>
       <c r="B581" t="n">
@@ -6241,7 +6241,7 @@
     <row r="582">
       <c r="A582" s="1" t="inlineStr">
         <is>
-          <t>ADI</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B582" t="n">
@@ -6251,7 +6251,7 @@
     <row r="583">
       <c r="A583" s="1" t="inlineStr">
         <is>
-          <t>ADM</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="B583" t="n">
@@ -6261,7 +6261,7 @@
     <row r="584">
       <c r="A584" s="1" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>EMR</t>
         </is>
       </c>
       <c r="B584" t="n">
@@ -6271,7 +6271,7 @@
     <row r="585">
       <c r="A585" s="1" t="inlineStr">
         <is>
-          <t>ADS</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B585" t="n">
@@ -6281,7 +6281,7 @@
     <row r="586">
       <c r="A586" s="1" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>ANF</t>
         </is>
       </c>
       <c r="B586" t="n">
@@ -6291,7 +6291,7 @@
     <row r="587">
       <c r="A587" s="1" t="inlineStr">
         <is>
-          <t>AES</t>
+          <t>AVY</t>
         </is>
       </c>
       <c r="B587" t="n">
@@ -6301,7 +6301,7 @@
     <row r="588">
       <c r="A588" s="1" t="inlineStr">
         <is>
-          <t>ACS</t>
+          <t>AIZ</t>
         </is>
       </c>
       <c r="B588" t="n">
@@ -6311,7 +6311,7 @@
     <row r="589">
       <c r="A589" s="1" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="B589" t="n">
@@ -6321,7 +6321,7 @@
     <row r="590">
       <c r="A590" s="1" t="inlineStr">
         <is>
-          <t>AON</t>
+          <t>SJM</t>
         </is>
       </c>
       <c r="B590" t="n">
@@ -6331,7 +6331,7 @@
     <row r="591">
       <c r="A591" s="1" t="inlineStr">
         <is>
-          <t>APD</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B591" t="n">
@@ -6341,7 +6341,7 @@
     <row r="592">
       <c r="A592" s="1" t="inlineStr">
         <is>
-          <t>BEN</t>
+          <t>PWR</t>
         </is>
       </c>
       <c r="B592" t="n">
@@ -6351,7 +6351,7 @@
     <row r="593">
       <c r="A593" s="1" t="inlineStr">
         <is>
-          <t>BF-B</t>
+          <t>KMX</t>
         </is>
       </c>
       <c r="B593" t="n">
@@ -6361,7 +6361,7 @@
     <row r="594">
       <c r="A594" s="1" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B594" t="n">
@@ -6371,7 +6371,7 @@
     <row r="595">
       <c r="A595" s="1" t="inlineStr">
         <is>
-          <t>BHF</t>
+          <t>PSA</t>
         </is>
       </c>
       <c r="B595" t="n">
@@ -6381,7 +6381,7 @@
     <row r="596">
       <c r="A596" s="1" t="inlineStr">
         <is>
-          <t>BHGE</t>
+          <t>WY</t>
         </is>
       </c>
       <c r="B596" t="n">
@@ -6391,7 +6391,7 @@
     <row r="597">
       <c r="A597" s="1" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>EQT</t>
         </is>
       </c>
       <c r="B597" t="n">
@@ -6401,7 +6401,7 @@
     <row r="598">
       <c r="A598" s="1" t="inlineStr">
         <is>
-          <t>BIO</t>
+          <t>IP</t>
         </is>
       </c>
       <c r="B598" t="n">
@@ -6411,7 +6411,7 @@
     <row r="599">
       <c r="A599" s="1" t="inlineStr">
         <is>
-          <t>BEAM</t>
+          <t>ITW</t>
         </is>
       </c>
       <c r="B599" t="n">
@@ -6421,7 +6421,7 @@
     <row r="600">
       <c r="A600" s="1" t="inlineStr">
         <is>
-          <t>BJS</t>
+          <t>MKC</t>
         </is>
       </c>
       <c r="B600" t="n">
@@ -6431,7 +6431,7 @@
     <row r="601">
       <c r="A601" s="1" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>IPG</t>
         </is>
       </c>
       <c r="B601" t="n">
@@ -6441,7 +6441,7 @@
     <row r="602">
       <c r="A602" s="1" t="inlineStr">
         <is>
-          <t>BKR</t>
+          <t>MHK</t>
         </is>
       </c>
       <c r="B602" t="n">
@@ -6451,7 +6451,7 @@
     <row r="603">
       <c r="A603" s="1" t="inlineStr">
         <is>
-          <t>BLDR</t>
+          <t>EMN</t>
         </is>
       </c>
       <c r="B603" t="n">
@@ -6461,7 +6461,7 @@
     <row r="604">
       <c r="A604" s="1" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>VNT</t>
         </is>
       </c>
       <c r="B604" t="n">
@@ -6471,7 +6471,7 @@
     <row r="605">
       <c r="A605" s="1" t="inlineStr">
         <is>
-          <t>BLL</t>
+          <t>TLAB</t>
         </is>
       </c>
       <c r="B605" t="n">
@@ -6481,7 +6481,7 @@
     <row r="606">
       <c r="A606" s="1" t="inlineStr">
         <is>
-          <t>BMS</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B606" t="n">
@@ -6491,7 +6491,7 @@
     <row r="607">
       <c r="A607" s="1" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>LII</t>
         </is>
       </c>
       <c r="B607" t="n">
@@ -6501,7 +6501,7 @@
     <row r="608">
       <c r="A608" s="1" t="inlineStr">
         <is>
-          <t>BK</t>
+          <t>ALLE</t>
         </is>
       </c>
       <c r="B608" t="n">
@@ -6511,7 +6511,7 @@
     <row r="609">
       <c r="A609" s="1" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>LYB</t>
         </is>
       </c>
       <c r="B609" t="n">
@@ -6521,7 +6521,7 @@
     <row r="610">
       <c r="A610" s="1" t="inlineStr">
         <is>
-          <t>BDX</t>
+          <t>FCPT</t>
         </is>
       </c>
       <c r="B610" t="n">
@@ -6531,7 +6531,7 @@
     <row r="611">
       <c r="A611" s="1" t="inlineStr">
         <is>
-          <t>BBWI</t>
+          <t>FANG</t>
         </is>
       </c>
       <c r="B611" t="n">
@@ -6541,7 +6541,7 @@
     <row r="612">
       <c r="A612" s="1" t="inlineStr">
         <is>
-          <t>APH</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="B612" t="n">
@@ -6551,7 +6551,7 @@
     <row r="613">
       <c r="A613" s="1" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>EOG</t>
         </is>
       </c>
       <c r="B613" t="n">
@@ -6561,7 +6561,7 @@
     <row r="614">
       <c r="A614" s="1" t="inlineStr">
         <is>
-          <t>APOL</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B614" t="n">
@@ -6571,7 +6571,7 @@
     <row r="615">
       <c r="A615" s="1" t="inlineStr">
         <is>
-          <t>APTV</t>
+          <t>ELV</t>
         </is>
       </c>
       <c r="B615" t="n">
@@ -6581,7 +6581,7 @@
     <row r="616">
       <c r="A616" s="1" t="inlineStr">
         <is>
-          <t>ARE</t>
+          <t>MSI</t>
         </is>
       </c>
       <c r="B616" t="n">
@@ -6591,7 +6591,7 @@
     <row r="617">
       <c r="A617" s="1" t="inlineStr">
         <is>
-          <t>ARNC</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="B617" t="n">
@@ -6601,7 +6601,7 @@
     <row r="618">
       <c r="A618" s="1" t="inlineStr">
         <is>
-          <t>ATGE</t>
+          <t>OMC</t>
         </is>
       </c>
       <c r="B618" t="n">
@@ -6611,7 +6611,7 @@
     <row r="619">
       <c r="A619" s="1" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>ITT</t>
         </is>
       </c>
       <c r="B619" t="n">
@@ -6621,7 +6621,7 @@
     <row r="620">
       <c r="A620" s="1" t="inlineStr">
         <is>
-          <t>ATI</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B620" t="n">
@@ -6631,7 +6631,7 @@
     <row r="621">
       <c r="A621" s="1" t="inlineStr">
         <is>
-          <t>AVP</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B621" t="n">
@@ -6641,7 +6641,7 @@
     <row r="622">
       <c r="A622" s="1" t="inlineStr">
         <is>
-          <t>AYI</t>
+          <t>DTE</t>
         </is>
       </c>
       <c r="B622" t="n">
@@ -6651,7 +6651,7 @@
     <row r="623">
       <c r="A623" s="1" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>AAL</t>
         </is>
       </c>
       <c r="B623" t="n">
@@ -6661,7 +6661,7 @@
     <row r="624">
       <c r="A624" s="1" t="inlineStr">
         <is>
-          <t>BALL</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B624" t="n">
@@ -6671,7 +6671,7 @@
     <row r="625">
       <c r="A625" s="1" t="inlineStr">
         <is>
-          <t>BAX</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B625" t="n">
@@ -6681,7 +6681,7 @@
     <row r="626">
       <c r="A626" s="1" t="inlineStr">
         <is>
-          <t>BAYRY</t>
+          <t>PNR</t>
         </is>
       </c>
       <c r="B626" t="n">
@@ -6691,7 +6691,7 @@
     <row r="627">
       <c r="A627" s="1" t="inlineStr">
         <is>
-          <t>BBBY</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B627" t="n">
@@ -6701,7 +6701,7 @@
     <row r="628">
       <c r="A628" s="1" t="inlineStr">
         <is>
-          <t>ATO</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B628" t="n">
@@ -6711,7 +6711,7 @@
     <row r="629">
       <c r="A629" s="1" t="inlineStr">
         <is>
-          <t>DUK</t>
+          <t>NKTR</t>
         </is>
       </c>
       <c r="B629" t="n">
@@ -6721,7 +6721,7 @@
     <row r="630">
       <c r="A630" s="1" t="inlineStr">
         <is>
-          <t>DVA</t>
+          <t>SW</t>
         </is>
       </c>
       <c r="B630" t="n">
@@ -6731,7 +6731,7 @@
     <row r="631">
       <c r="A631" s="1" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>COO</t>
         </is>
       </c>
       <c r="B631" t="n">
@@ -6741,7 +6741,7 @@
     <row r="632">
       <c r="A632" s="1" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>COF</t>
         </is>
       </c>
       <c r="B632" t="n">
@@ -6751,7 +6751,7 @@
     <row r="633">
       <c r="A633" s="1" t="inlineStr">
         <is>
-          <t>INVH</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B633" t="n">
@@ -6761,7 +6761,7 @@
     <row r="634">
       <c r="A634" s="1" t="inlineStr">
         <is>
-          <t>IP</t>
+          <t>SYF</t>
         </is>
       </c>
       <c r="B634" t="n">
@@ -6771,7 +6771,7 @@
     <row r="635">
       <c r="A635" s="1" t="inlineStr">
         <is>
-          <t>IQV</t>
+          <t>BALL</t>
         </is>
       </c>
       <c r="B635" t="n">
@@ -6781,7 +6781,7 @@
     <row r="636">
       <c r="A636" s="1" t="inlineStr">
         <is>
-          <t>ITW</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="B636" t="n">
@@ -6791,7 +6791,7 @@
     <row r="637">
       <c r="A637" s="1" t="inlineStr">
         <is>
-          <t>IVZ</t>
+          <t>ODP</t>
         </is>
       </c>
       <c r="B637" t="n">
@@ -6801,7 +6801,7 @@
     <row r="638">
       <c r="A638" s="1" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B638" t="n">
@@ -6811,7 +6811,7 @@
     <row r="639">
       <c r="A639" s="1" t="inlineStr">
         <is>
-          <t>INFO</t>
+          <t>XRX</t>
         </is>
       </c>
       <c r="B639" t="n">
@@ -6821,7 +6821,7 @@
     <row r="640">
       <c r="A640" s="1" t="inlineStr">
         <is>
-          <t>JAVA</t>
+          <t>IDXX</t>
         </is>
       </c>
       <c r="B640" t="n">
@@ -6831,7 +6831,7 @@
     <row r="641">
       <c r="A641" s="1" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="B641" t="n">
@@ -6841,7 +6841,7 @@
     <row r="642">
       <c r="A642" s="1" t="inlineStr">
         <is>
-          <t>JCI</t>
+          <t>NUE</t>
         </is>
       </c>
       <c r="B642" t="n">
@@ -6851,7 +6851,7 @@
     <row r="643">
       <c r="A643" s="1" t="inlineStr">
         <is>
-          <t>ZION</t>
+          <t>ALK</t>
         </is>
       </c>
       <c r="B643" t="n">
@@ -6861,7 +6861,7 @@
     <row r="644">
       <c r="A644" s="1" t="inlineStr">
         <is>
-          <t>JEC</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B644" t="n">
@@ -6871,7 +6871,7 @@
     <row r="645">
       <c r="A645" s="1" t="inlineStr">
         <is>
-          <t>JEF</t>
+          <t>AJG</t>
         </is>
       </c>
       <c r="B645" t="n">
@@ -6881,7 +6881,7 @@
     <row r="646">
       <c r="A646" s="1" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>MAS</t>
         </is>
       </c>
       <c r="B646" t="n">
@@ -6891,7 +6891,7 @@
     <row r="647">
       <c r="A647" s="1" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B647" t="n">
@@ -6901,7 +6901,7 @@
     <row r="648">
       <c r="A648" s="1" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>WYNN</t>
         </is>
       </c>
       <c r="B648" t="n">
@@ -6911,7 +6911,7 @@
     <row r="649">
       <c r="A649" s="1" t="inlineStr">
         <is>
-          <t>JNPR</t>
+          <t>X</t>
         </is>
       </c>
       <c r="B649" t="n">
@@ -6921,7 +6921,7 @@
     <row r="650">
       <c r="A650" s="1" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>QRVO</t>
         </is>
       </c>
       <c r="B650" t="n">
@@ -6931,7 +6931,7 @@
     <row r="651">
       <c r="A651" s="1" t="inlineStr">
         <is>
-          <t>IGT</t>
+          <t>BBWI</t>
         </is>
       </c>
       <c r="B651" t="n">
@@ -6941,7 +6941,7 @@
     <row r="652">
       <c r="A652" s="1" t="inlineStr">
         <is>
-          <t>HES</t>
+          <t>HPE</t>
         </is>
       </c>
       <c r="B652" t="n">
@@ -6951,7 +6951,7 @@
     <row r="653">
       <c r="A653" s="1" t="inlineStr">
         <is>
-          <t>HFC</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="B653" t="n">
@@ -6961,7 +6961,7 @@
     <row r="654">
       <c r="A654" s="1" t="inlineStr">
         <is>
-          <t>HOT</t>
+          <t>SYY</t>
         </is>
       </c>
       <c r="B654" t="n">
@@ -6971,7 +6971,7 @@
     <row r="655">
       <c r="A655" s="1" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>MKTX</t>
         </is>
       </c>
       <c r="B655" t="n">
@@ -6981,7 +6981,7 @@
     <row r="656">
       <c r="A656" s="1" t="inlineStr">
         <is>
-          <t>HPQ</t>
+          <t>EPAM</t>
         </is>
       </c>
       <c r="B656" t="n">
@@ -6991,7 +6991,7 @@
     <row r="657">
       <c r="A657" s="1" t="inlineStr">
         <is>
-          <t>HRB</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="B657" t="n">
@@ -7001,7 +7001,7 @@
     <row r="658">
       <c r="A658" s="1" t="inlineStr">
         <is>
-          <t>HRL</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="B658" t="n">
@@ -7011,7 +7011,7 @@
     <row r="659">
       <c r="A659" s="1" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B659" t="n">
@@ -7021,7 +7021,7 @@
     <row r="660">
       <c r="A660" s="1" t="inlineStr">
         <is>
-          <t>HRS</t>
+          <t>NYT</t>
         </is>
       </c>
       <c r="B660" t="n">
@@ -7031,7 +7031,7 @@
     <row r="661">
       <c r="A661" s="1" t="inlineStr">
         <is>
-          <t>HSIC</t>
+          <t>PKG</t>
         </is>
       </c>
       <c r="B661" t="n">
@@ -7041,7 +7041,7 @@
     <row r="662">
       <c r="A662" s="1" t="inlineStr">
         <is>
-          <t>HST</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B662" t="n">
@@ -7051,7 +7051,7 @@
     <row r="663">
       <c r="A663" s="1" t="inlineStr">
         <is>
-          <t>HSY</t>
+          <t>CDNS</t>
         </is>
       </c>
       <c r="B663" t="n">
@@ -7061,7 +7061,7 @@
     <row r="664">
       <c r="A664" s="1" t="inlineStr">
         <is>
-          <t>HUBB</t>
+          <t>GME</t>
         </is>
       </c>
       <c r="B664" t="n">
@@ -7071,7 +7071,7 @@
     <row r="665">
       <c r="A665" s="1" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="B665" t="n">
@@ -7081,7 +7081,7 @@
     <row r="666">
       <c r="A666" s="1" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>TPR</t>
         </is>
       </c>
       <c r="B666" t="n">
@@ -7091,7 +7091,7 @@
     <row r="667">
       <c r="A667" s="1" t="inlineStr">
         <is>
-          <t>IFF</t>
+          <t>RRC</t>
         </is>
       </c>
       <c r="B667" t="n">
@@ -7101,7 +7101,7 @@
     <row r="668">
       <c r="A668" s="1" t="inlineStr">
         <is>
-          <t>HSH</t>
+          <t>DECK</t>
         </is>
       </c>
       <c r="B668" t="n">
@@ -7111,7 +7111,7 @@
     <row r="669">
       <c r="A669" s="1" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>AMTM</t>
         </is>
       </c>
       <c r="B669" t="n">
@@ -7121,7 +7121,7 @@
     <row r="670">
       <c r="A670" s="1" t="inlineStr">
         <is>
-          <t>JNS</t>
+          <t>AMCR</t>
         </is>
       </c>
       <c r="B670" t="n">
@@ -7131,7 +7131,7 @@
     <row r="671">
       <c r="A671" s="1" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="B671" t="n">
@@ -7141,7 +7141,7 @@
     <row r="672">
       <c r="A672" s="1" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>UDR</t>
         </is>
       </c>
       <c r="B672" t="n">
@@ -7151,7 +7151,7 @@
     <row r="673">
       <c r="A673" s="1" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="B673" t="n">
@@ -7161,7 +7161,7 @@
     <row r="674">
       <c r="A674" s="1" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>CMS</t>
         </is>
       </c>
       <c r="B674" t="n">
@@ -7171,7 +7171,7 @@
     <row r="675">
       <c r="A675" s="1" t="inlineStr">
         <is>
-          <t>LUMN</t>
+          <t>TPL</t>
         </is>
       </c>
       <c r="B675" t="n">
@@ -7181,7 +7181,7 @@
     <row r="676">
       <c r="A676" s="1" t="inlineStr">
         <is>
-          <t>LUV</t>
+          <t>VICI</t>
         </is>
       </c>
       <c r="B676" t="n">
@@ -7191,7 +7191,7 @@
     <row r="677">
       <c r="A677" s="1" t="inlineStr">
         <is>
-          <t>LVS</t>
+          <t>TDG</t>
         </is>
       </c>
       <c r="B677" t="n">
@@ -7201,7 +7201,7 @@
     <row r="678">
       <c r="A678" s="1" t="inlineStr">
         <is>
-          <t>LW</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B678" t="n">
@@ -7211,7 +7211,7 @@
     <row r="679">
       <c r="A679" s="1" t="inlineStr">
         <is>
-          <t>LNT</t>
+          <t>WEC</t>
         </is>
       </c>
       <c r="B679" t="n">
@@ -7221,7 +7221,7 @@
     <row r="680">
       <c r="A680" s="1" t="inlineStr">
         <is>
-          <t>LYB</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B680" t="n">
@@ -7231,7 +7231,7 @@
     <row r="681">
       <c r="A681" s="1" t="inlineStr">
         <is>
-          <t>MCHP</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="B681" t="n">
@@ -7241,7 +7241,7 @@
     <row r="682">
       <c r="A682" s="1" t="inlineStr">
         <is>
-          <t>MDLZ</t>
+          <t>SVU</t>
         </is>
       </c>
       <c r="B682" t="n">
@@ -7251,7 +7251,7 @@
     <row r="683">
       <c r="A683" s="1" t="inlineStr">
         <is>
-          <t>MDP</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B683" t="n">
@@ -7261,7 +7261,7 @@
     <row r="684">
       <c r="A684" s="1" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="B684" t="n">
@@ -7271,7 +7271,7 @@
     <row r="685">
       <c r="A685" s="1" t="inlineStr">
         <is>
-          <t>MEE</t>
+          <t>CCL</t>
         </is>
       </c>
       <c r="B685" t="n">
@@ -7281,7 +7281,7 @@
     <row r="686">
       <c r="A686" s="1" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B686" t="n">
@@ -7291,7 +7291,7 @@
     <row r="687">
       <c r="A687" s="1" t="inlineStr">
         <is>
-          <t>MFE</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="B687" t="n">
@@ -7301,7 +7301,7 @@
     <row r="688">
       <c r="A688" s="1" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B688" t="n">
@@ -7311,7 +7311,7 @@
     <row r="689">
       <c r="A689" s="1" t="inlineStr">
         <is>
-          <t>JWN</t>
+          <t>MDLZ</t>
         </is>
       </c>
       <c r="B689" t="n">
@@ -7321,7 +7321,7 @@
     <row r="690">
       <c r="A690" s="1" t="inlineStr">
         <is>
-          <t>LNC</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="B690" t="n">
@@ -7331,7 +7331,7 @@
     <row r="691">
       <c r="A691" s="1" t="inlineStr">
         <is>
-          <t>LII</t>
+          <t>BKR</t>
         </is>
       </c>
       <c r="B691" t="n">
@@ -7341,7 +7341,7 @@
     <row r="692">
       <c r="A692" s="1" t="inlineStr">
         <is>
-          <t>KDP</t>
+          <t>SPG</t>
         </is>
       </c>
       <c r="B692" t="n">
@@ -7351,7 +7351,7 @@
     <row r="693">
       <c r="A693" s="1" t="inlineStr">
         <is>
-          <t>KEY</t>
+          <t>PVH</t>
         </is>
       </c>
       <c r="B693" t="n">
@@ -7361,7 +7361,7 @@
     <row r="694">
       <c r="A694" s="1" t="inlineStr">
         <is>
-          <t>KEYS</t>
+          <t>HIG</t>
         </is>
       </c>
       <c r="B694" t="n">
@@ -7371,7 +7371,7 @@
     <row r="695">
       <c r="A695" s="1" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>FTV</t>
         </is>
       </c>
       <c r="B695" t="n">
@@ -7381,7 +7381,7 @@
     <row r="696">
       <c r="A696" s="1" t="inlineStr">
         <is>
-          <t>KHC</t>
+          <t>PNC</t>
         </is>
       </c>
       <c r="B696" t="n">
@@ -7391,7 +7391,7 @@
     <row r="697">
       <c r="A697" s="1" t="inlineStr">
         <is>
-          <t>KKR</t>
+          <t>TSN</t>
         </is>
       </c>
       <c r="B697" t="n">
@@ -7401,7 +7401,7 @@
     <row r="698">
       <c r="A698" s="1" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>MTCH</t>
         </is>
       </c>
       <c r="B698" t="n">
@@ -7411,7 +7411,7 @@
     <row r="699">
       <c r="A699" s="1" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>ATGE</t>
         </is>
       </c>
       <c r="B699" t="n">
@@ -7421,7 +7421,7 @@
     <row r="700">
       <c r="A700" s="1" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>SYK</t>
         </is>
       </c>
       <c r="B700" t="n">
@@ -7431,7 +7431,7 @@
     <row r="701">
       <c r="A701" s="1" t="inlineStr">
         <is>
-          <t>KMX</t>
+          <t>CBRE</t>
         </is>
       </c>
       <c r="B701" t="n">
@@ -7441,7 +7441,7 @@
     <row r="702">
       <c r="A702" s="1" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="B702" t="n">
@@ -7451,7 +7451,7 @@
     <row r="703">
       <c r="A703" s="1" t="inlineStr">
         <is>
-          <t>KVUE</t>
+          <t>EP</t>
         </is>
       </c>
       <c r="B703" t="n">
@@ -7461,7 +7461,7 @@
     <row r="704">
       <c r="A704" s="1" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>AVB</t>
         </is>
       </c>
       <c r="B704" t="n">
@@ -7471,7 +7471,7 @@
     <row r="705">
       <c r="A705" s="1" t="inlineStr">
         <is>
-          <t>LEG</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="B705" t="n">
@@ -7481,7 +7481,7 @@
     <row r="706">
       <c r="A706" s="1" t="inlineStr">
         <is>
-          <t>LEN</t>
+          <t>SHW</t>
         </is>
       </c>
       <c r="B706" t="n">
@@ -7491,7 +7491,7 @@
     <row r="707">
       <c r="A707" s="1" t="inlineStr">
         <is>
-          <t>LIFE</t>
+          <t>CCI</t>
         </is>
       </c>
       <c r="B707" t="n">
@@ -7501,7 +7501,7 @@
     <row r="708">
       <c r="A708" s="1" t="inlineStr">
         <is>
-          <t>KMI</t>
+          <t>SEE</t>
         </is>
       </c>
       <c r="B708" t="n">
@@ -7511,7 +7511,7 @@
     <row r="709">
       <c r="A709" s="1" t="inlineStr">
         <is>
-          <t>HCP</t>
+          <t>UA</t>
         </is>
       </c>
       <c r="B709" t="n">
@@ -7521,7 +7521,7 @@
     <row r="710">
       <c r="A710" s="1" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>TRMB</t>
         </is>
       </c>
       <c r="B710" t="n">
@@ -7531,7 +7531,7 @@
     <row r="711">
       <c r="A711" s="1" t="inlineStr">
         <is>
-          <t>HBI</t>
+          <t>AET</t>
         </is>
       </c>
       <c r="B711" t="n">
@@ -7541,7 +7541,7 @@
     <row r="712">
       <c r="A712" s="1" t="inlineStr">
         <is>
-          <t>ETSY</t>
+          <t>MLM</t>
         </is>
       </c>
       <c r="B712" t="n">
@@ -7551,7 +7551,7 @@
     <row r="713">
       <c r="A713" s="1" t="inlineStr">
         <is>
-          <t>EVHC</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="B713" t="n">
@@ -7561,7 +7561,7 @@
     <row r="714">
       <c r="A714" s="1" t="inlineStr">
         <is>
-          <t>EVRG</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B714" t="n">
@@ -7571,7 +7571,7 @@
     <row r="715">
       <c r="A715" s="1" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>IRM</t>
         </is>
       </c>
       <c r="B715" t="n">
@@ -7581,7 +7581,7 @@
     <row r="716">
       <c r="A716" s="1" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>R</t>
         </is>
       </c>
       <c r="B716" t="n">
@@ -7591,7 +7591,7 @@
     <row r="717">
       <c r="A717" s="1" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>PPG</t>
         </is>
       </c>
       <c r="B717" t="n">
@@ -7601,7 +7601,7 @@
     <row r="718">
       <c r="A718" s="1" t="inlineStr">
         <is>
-          <t>EXPE</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="B718" t="n">
@@ -7611,7 +7611,7 @@
     <row r="719">
       <c r="A719" s="1" t="inlineStr">
         <is>
-          <t>ETR</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="B719" t="n">
@@ -7621,7 +7621,7 @@
     <row r="720">
       <c r="A720" s="1" t="inlineStr">
         <is>
-          <t>EXR</t>
+          <t>BSX</t>
         </is>
       </c>
       <c r="B720" t="n">
@@ -7631,7 +7631,7 @@
     <row r="721">
       <c r="A721" s="1" t="inlineStr">
         <is>
-          <t>FANG</t>
+          <t>STT</t>
         </is>
       </c>
       <c r="B721" t="n">
@@ -7641,7 +7641,7 @@
     <row r="722">
       <c r="A722" s="1" t="inlineStr">
         <is>
-          <t>FAST</t>
+          <t>TGT</t>
         </is>
       </c>
       <c r="B722" t="n">
@@ -7651,7 +7651,7 @@
     <row r="723">
       <c r="A723" s="1" t="inlineStr">
         <is>
-          <t>FBHS</t>
+          <t>SBAC</t>
         </is>
       </c>
       <c r="B723" t="n">
@@ -7661,7 +7661,7 @@
     <row r="724">
       <c r="A724" s="1" t="inlineStr">
         <is>
-          <t>FCPT</t>
+          <t>LVS</t>
         </is>
       </c>
       <c r="B724" t="n">
@@ -7671,7 +7671,7 @@
     <row r="725">
       <c r="A725" s="1" t="inlineStr">
         <is>
-          <t>FCX</t>
+          <t>TRV</t>
         </is>
       </c>
       <c r="B725" t="n">
@@ -7681,7 +7681,7 @@
     <row r="726">
       <c r="A726" s="1" t="inlineStr">
         <is>
-          <t>FDO</t>
+          <t>TTWO</t>
         </is>
       </c>
       <c r="B726" t="n">
@@ -7691,7 +7691,7 @@
     <row r="727">
       <c r="A727" s="1" t="inlineStr">
         <is>
-          <t>FDS</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B727" t="n">
@@ -7701,7 +7701,7 @@
     <row r="728">
       <c r="A728" s="1" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>OGN</t>
         </is>
       </c>
       <c r="B728" t="n">
@@ -7711,7 +7711,7 @@
     <row r="729">
       <c r="A729" s="1" t="inlineStr">
         <is>
-          <t>FDX</t>
+          <t>LUV</t>
         </is>
       </c>
       <c r="B729" t="n">
@@ -7721,7 +7721,7 @@
     <row r="730">
       <c r="A730" s="1" t="inlineStr">
         <is>
-          <t>ESS</t>
+          <t>LHX</t>
         </is>
       </c>
       <c r="B730" t="n">
@@ -7731,7 +7731,7 @@
     <row r="731">
       <c r="A731" s="1" t="inlineStr">
         <is>
-          <t>EQT</t>
+          <t>DRI</t>
         </is>
       </c>
       <c r="B731" t="n">
@@ -7741,7 +7741,7 @@
     <row r="732">
       <c r="A732" s="1" t="inlineStr">
         <is>
-          <t>DXCM</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B732" t="n">
@@ -7751,7 +7751,7 @@
     <row r="733">
       <c r="A733" s="1" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="B733" t="n">
@@ -7761,7 +7761,7 @@
     <row r="734">
       <c r="A734" s="1" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="B734" t="n">
@@ -7771,7 +7771,7 @@
     <row r="735">
       <c r="A735" s="1" t="inlineStr">
         <is>
-          <t>ECL</t>
+          <t>AOS</t>
         </is>
       </c>
       <c r="B735" t="n">
@@ -7781,7 +7781,7 @@
     <row r="736">
       <c r="A736" s="1" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="B736" t="n">
@@ -7791,7 +7791,7 @@
     <row r="737">
       <c r="A737" s="1" t="inlineStr">
         <is>
-          <t>EIX</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="B737" t="n">
@@ -7801,7 +7801,7 @@
     <row r="738">
       <c r="A738" s="1" t="inlineStr">
         <is>
-          <t>EKDKQ</t>
+          <t>HBI</t>
         </is>
       </c>
       <c r="B738" t="n">
@@ -7811,7 +7811,7 @@
     <row r="739">
       <c r="A739" s="1" t="inlineStr">
         <is>
-          <t>ERIE</t>
+          <t>CARR</t>
         </is>
       </c>
       <c r="B739" t="n">
@@ -7821,7 +7821,7 @@
     <row r="740">
       <c r="A740" s="1" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>MCHP</t>
         </is>
       </c>
       <c r="B740" t="n">
@@ -7831,7 +7831,7 @@
     <row r="741">
       <c r="A741" s="1" t="inlineStr">
         <is>
-          <t>ENDP</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="B741" t="n">
@@ -7841,7 +7841,7 @@
     <row r="742">
       <c r="A742" s="1" t="inlineStr">
         <is>
-          <t>ENPH</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="B742" t="n">
@@ -7851,7 +7851,7 @@
     <row r="743">
       <c r="A743" s="1" t="inlineStr">
         <is>
-          <t>EOG</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="B743" t="n">
@@ -7861,7 +7861,7 @@
     <row r="744">
       <c r="A744" s="1" t="inlineStr">
         <is>
-          <t>EP</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B744" t="n">
@@ -7871,7 +7871,7 @@
     <row r="745">
       <c r="A745" s="1" t="inlineStr">
         <is>
-          <t>EPAM</t>
+          <t>HES</t>
         </is>
       </c>
       <c r="B745" t="n">
@@ -7881,7 +7881,7 @@
     <row r="746">
       <c r="A746" s="1" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>HNZ</t>
         </is>
       </c>
       <c r="B746" t="n">
@@ -7891,7 +7891,7 @@
     <row r="747">
       <c r="A747" s="1" t="inlineStr">
         <is>
-          <t>EQR</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="B747" t="n">
@@ -7901,7 +7901,7 @@
     <row r="748">
       <c r="A748" s="1" t="inlineStr">
         <is>
-          <t>EMC</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B748" t="n">
@@ -7911,7 +7911,7 @@
     <row r="749">
       <c r="A749" s="1" t="inlineStr">
         <is>
-          <t>FE</t>
+          <t>WAB</t>
         </is>
       </c>
       <c r="B749" t="n">
@@ -7921,7 +7921,7 @@
     <row r="750">
       <c r="A750" s="1" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B750" t="n">
@@ -7931,7 +7931,7 @@
     <row r="751">
       <c r="A751" s="1" t="inlineStr">
         <is>
-          <t>FHN</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="B751" t="n">
@@ -7941,7 +7941,7 @@
     <row r="752">
       <c r="A752" s="1" t="inlineStr">
         <is>
-          <t>GHC</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="B752" t="n">
@@ -7951,7 +7951,7 @@
     <row r="753">
       <c r="A753" s="1" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>AKAM</t>
         </is>
       </c>
       <c r="B753" t="n">
@@ -7961,7 +7961,7 @@
     <row r="754">
       <c r="A754" s="1" t="inlineStr">
         <is>
-          <t>GME</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B754" t="n">
@@ -7971,7 +7971,7 @@
     <row r="755">
       <c r="A755" s="1" t="inlineStr">
         <is>
-          <t>GNRC</t>
+          <t>PCAR</t>
         </is>
       </c>
       <c r="B755" t="n">
@@ -7981,7 +7981,7 @@
     <row r="756">
       <c r="A756" s="1" t="inlineStr">
         <is>
-          <t>GNW</t>
+          <t>CSGP</t>
         </is>
       </c>
       <c r="B756" t="n">
@@ -7991,7 +7991,7 @@
     <row r="757">
       <c r="A757" s="1" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>COTY</t>
         </is>
       </c>
       <c r="B757" t="n">
@@ -8001,7 +8001,7 @@
     <row r="758">
       <c r="A758" s="1" t="inlineStr">
         <is>
-          <t>GPC</t>
+          <t>NWL</t>
         </is>
       </c>
       <c r="B758" t="n">
@@ -8011,7 +8011,7 @@
     <row r="759">
       <c r="A759" s="1" t="inlineStr">
         <is>
-          <t>GGP</t>
+          <t>VIAV</t>
         </is>
       </c>
       <c r="B759" t="n">
@@ -8021,7 +8021,7 @@
     <row r="760">
       <c r="A760" s="1" t="inlineStr">
         <is>
-          <t>GPN</t>
+          <t>PHM</t>
         </is>
       </c>
       <c r="B760" t="n">
@@ -8031,7 +8031,7 @@
     <row r="761">
       <c r="A761" s="1" t="inlineStr">
         <is>
-          <t>GR</t>
+          <t>RMD</t>
         </is>
       </c>
       <c r="B761" t="n">
@@ -8041,7 +8041,7 @@
     <row r="762">
       <c r="A762" s="1" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>XRAY</t>
         </is>
       </c>
       <c r="B762" t="n">
@@ -8051,7 +8051,7 @@
     <row r="763">
       <c r="A763" s="1" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>NSC</t>
         </is>
       </c>
       <c r="B763" t="n">
@@ -8061,7 +8061,7 @@
     <row r="764">
       <c r="A764" s="1" t="inlineStr">
         <is>
-          <t>GWW</t>
+          <t>PNW</t>
         </is>
       </c>
       <c r="B764" t="n">
@@ -8071,7 +8071,7 @@
     <row r="765">
       <c r="A765" s="1" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B765" t="n">
@@ -8081,7 +8081,7 @@
     <row r="766">
       <c r="A766" s="1" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>OI</t>
         </is>
       </c>
       <c r="B766" t="n">
@@ -8091,7 +8091,7 @@
     <row r="767">
       <c r="A767" s="1" t="inlineStr">
         <is>
-          <t>HBAN</t>
+          <t>DLR</t>
         </is>
       </c>
       <c r="B767" t="n">
@@ -8101,7 +8101,7 @@
     <row r="768">
       <c r="A768" s="1" t="inlineStr">
         <is>
-          <t>GPS</t>
+          <t>OKE</t>
         </is>
       </c>
       <c r="B768" t="n">
@@ -8111,7 +8111,7 @@
     <row r="769">
       <c r="A769" s="1" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>LKQ</t>
         </is>
       </c>
       <c r="B769" t="n">
@@ -8121,7 +8121,7 @@
     <row r="770">
       <c r="A770" s="1" t="inlineStr">
         <is>
-          <t>GEHC</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B770" t="n">
@@ -8131,7 +8131,7 @@
     <row r="771">
       <c r="A771" s="1" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>AMG</t>
         </is>
       </c>
       <c r="B771" t="n">
@@ -8141,7 +8141,7 @@
     <row r="772">
       <c r="A772" s="1" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>WBA</t>
         </is>
       </c>
       <c r="B772" t="n">
@@ -8151,7 +8151,7 @@
     <row r="773">
       <c r="A773" s="1" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B773" t="n">
@@ -8161,7 +8161,7 @@
     <row r="774">
       <c r="A774" s="1" t="inlineStr">
         <is>
-          <t>FII</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="B774" t="n">
@@ -8171,7 +8171,7 @@
     <row r="775">
       <c r="A775" s="1" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>WST</t>
         </is>
       </c>
       <c r="B775" t="n">
@@ -8181,7 +8181,7 @@
     <row r="776">
       <c r="A776" s="1" t="inlineStr">
         <is>
-          <t>FITB</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="B776" t="n">
@@ -8191,7 +8191,7 @@
     <row r="777">
       <c r="A777" s="1" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="B777" t="n">
@@ -8201,7 +8201,7 @@
     <row r="778">
       <c r="A778" s="1" t="inlineStr">
         <is>
-          <t>FLT</t>
+          <t>BXP</t>
         </is>
       </c>
       <c r="B778" t="n">
@@ -8211,7 +8211,7 @@
     <row r="779">
       <c r="A779" s="1" t="inlineStr">
         <is>
-          <t>FMC</t>
+          <t>NBR</t>
         </is>
       </c>
       <c r="B779" t="n">
@@ -8221,7 +8221,7 @@
     <row r="780">
       <c r="A780" s="1" t="inlineStr">
         <is>
-          <t>FOSL</t>
+          <t>SOLV</t>
         </is>
       </c>
       <c r="B780" t="n">
@@ -8231,7 +8231,7 @@
     <row r="781">
       <c r="A781" s="1" t="inlineStr">
         <is>
-          <t>FOX</t>
+          <t>LNT</t>
         </is>
       </c>
       <c r="B781" t="n">
@@ -8241,7 +8241,7 @@
     <row r="782">
       <c r="A782" s="1" t="inlineStr">
         <is>
-          <t>FOXA</t>
+          <t>ARE</t>
         </is>
       </c>
       <c r="B782" t="n">
@@ -8251,7 +8251,7 @@
     <row r="783">
       <c r="A783" s="1" t="inlineStr">
         <is>
-          <t>FRC</t>
+          <t>ACGL</t>
         </is>
       </c>
       <c r="B783" t="n">
@@ -8261,7 +8261,7 @@
     <row r="784">
       <c r="A784" s="1" t="inlineStr">
         <is>
-          <t>FRT</t>
+          <t>WHR</t>
         </is>
       </c>
       <c r="B784" t="n">
@@ -8271,7 +8271,7 @@
     <row r="785">
       <c r="A785" s="1" t="inlineStr">
         <is>
-          <t>FRX</t>
+          <t>ALB</t>
         </is>
       </c>
       <c r="B785" t="n">
@@ -8281,7 +8281,7 @@
     <row r="786">
       <c r="A786" s="1" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>VNO</t>
         </is>
       </c>
       <c r="B786" t="n">
@@ -8291,7 +8291,7 @@
     <row r="787">
       <c r="A787" s="1" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>MGM</t>
         </is>
       </c>
       <c r="B787" t="n">
@@ -8301,7 +8301,7 @@
     <row r="788">
       <c r="A788" s="1" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B788" t="n">
@@ -8311,7 +8311,7 @@
     <row r="789">
       <c r="A789" s="1" t="inlineStr">
         <is>
-          <t>MHK</t>
+          <t>AAP</t>
         </is>
       </c>
       <c r="B789" t="n">
@@ -8321,10 +8321,230 @@
     <row r="790">
       <c r="A790" s="1" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>TDC</t>
         </is>
       </c>
       <c r="B790" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" s="1" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="B791" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" s="1" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="B792" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" s="1" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="B793" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" s="1" t="inlineStr">
+        <is>
+          <t>PBG</t>
+        </is>
+      </c>
+      <c r="B794" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" s="1" t="inlineStr">
+        <is>
+          <t>ADI</t>
+        </is>
+      </c>
+      <c r="B795" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" s="1" t="inlineStr">
+        <is>
+          <t>CPT</t>
+        </is>
+      </c>
+      <c r="B796" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" s="1" t="inlineStr">
+        <is>
+          <t>VTRS</t>
+        </is>
+      </c>
+      <c r="B797" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" s="1" t="inlineStr">
+        <is>
+          <t>DLTR</t>
+        </is>
+      </c>
+      <c r="B798" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" s="1" t="inlineStr">
+        <is>
+          <t>TECH</t>
+        </is>
+      </c>
+      <c r="B799" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" s="1" t="inlineStr">
+        <is>
+          <t>ATO</t>
+        </is>
+      </c>
+      <c r="B800" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" s="1" t="inlineStr">
+        <is>
+          <t>FDX</t>
+        </is>
+      </c>
+      <c r="B801" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" s="1" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="B802" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" s="1" t="inlineStr">
+        <is>
+          <t>ETN</t>
+        </is>
+      </c>
+      <c r="B803" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" s="1" t="inlineStr">
+        <is>
+          <t>BRO</t>
+        </is>
+      </c>
+      <c r="B804" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" s="1" t="inlineStr">
+        <is>
+          <t>CHRW</t>
+        </is>
+      </c>
+      <c r="B805" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" s="1" t="inlineStr">
+        <is>
+          <t>APO</t>
+        </is>
+      </c>
+      <c r="B806" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" s="1" t="inlineStr">
+        <is>
+          <t>INTU</t>
+        </is>
+      </c>
+      <c r="B807" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" s="1" t="inlineStr">
+        <is>
+          <t>AME</t>
+        </is>
+      </c>
+      <c r="B808" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" s="1" t="inlineStr">
+        <is>
+          <t>MAA</t>
+        </is>
+      </c>
+      <c r="B809" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" s="1" t="inlineStr">
+        <is>
+          <t>IPGP</t>
+        </is>
+      </c>
+      <c r="B810" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" s="1" t="inlineStr">
+        <is>
+          <t>FTI</t>
+        </is>
+      </c>
+      <c r="B811" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" s="1" t="inlineStr">
+        <is>
+          <t>WRB</t>
+        </is>
+      </c>
+      <c r="B812" t="n">
         <v>1</v>
       </c>
     </row>
